--- a/frontend/api-reference.xlsx
+++ b/frontend/api-reference.xlsx
@@ -10,7 +10,7 @@
     <sheet name="API" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API'!$A$4:$M$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API'!$A$4:$M$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:M143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2448,108 +2448,108 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Chat API</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/chat/message</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>cap_notice</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>{message,escalate_label,finish_label}|null</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>{"message":"…","escalate_label":"Передать вопрос человеку","finish_label":"Завершить чат"}</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>Мягкий лимит сообщений достигнут: показать предупреждение и две кнопки — эскалация (POST /escalate) сверху и завершение (POST /resolve) ниже — вместо suggestions/resolved. Чат остаётся открытым; на 2x лимита сессия закрывается принудительно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Chat API</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>GET /api/chat/session/{id}</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>Выход</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Клиент чата</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>Bearer &lt;session token&gt; (JWT HS256)</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>Бюджет chat-op:{ip} (300)</t>
         </is>
       </c>
-      <c r="L39" s="4" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>401 · 404 · 429</t>
         </is>
       </c>
-      <c r="M39" s="4" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>Возобновление диалога: статус и до 50 последних сообщений.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Chat API</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>GET /api/chat/session/{id}</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>Наш сервис</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>'open'|'resolved'|'escalated'</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr"/>
-      <c r="L40" s="7" t="inlineStr"/>
-      <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t>Только open допускает новые ходы; иначе 409.</t>
         </is>
       </c>
     </row>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>status</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>[{role,content,lang}]</t>
+          <t>'open'|'resolved'|'escalated'</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>[{"role":"user","content":"…"}]</t>
+          <t>open</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr"/>
@@ -2604,58 +2604,62 @@
       <c r="L41" s="7" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr">
         <is>
+          <t>Только open допускает новые ходы; иначе 409.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Chat API</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/chat/session/{id}</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>[{role,content,lang}]</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>[{"role":"user","content":"…"}]</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr"/>
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr">
+        <is>
           <t>role ∈ user|assistant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Chat API</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>POST /api/chat/escalate</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>Клиент чата</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;session token&gt; (JWT HS256)</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>Бюджет chat-op:{ip} (300)</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>401 · 404 · 409 · 429</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
-        <is>
-          <t>Явный запрос человека: жёсткая эскалация, сессия закрывается.</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2671,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>POST /api/chat/resolve</t>
+          <t>POST /api/chat/escalate</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2675,9 +2679,9 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -2696,76 +2700,68 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
+          <t>Бюджет chat-op:{ip} (300)</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>401 · 404 · 409 · 429</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>Явный запрос человека: жёсткая эскалация, сессия закрывается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Chat API</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>POST /api/chat/resolve</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Клиент чата</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;session token&gt; (JWT HS256)</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
           <t>Идемпотентно; не перекрывает уже эскалированную сессию</t>
         </is>
       </c>
-      <c r="L43" s="4" t="inlineStr">
+      <c r="L44" s="4" t="inlineStr">
         <is>
           <t>401 · 404 · 429</t>
         </is>
       </c>
-      <c r="M43" s="4" t="inlineStr">
+      <c r="M44" s="4" t="inlineStr">
         <is>
           <t>Игрок завершил чат.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Chat API</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Контракт: user_context / signed_context</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>Сайт / виджет</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>1048576</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>подпись HMAC-SHA256 секретом продукта</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr"/>
-      <c r="L44" s="7" t="inlineStr"/>
-      <c r="M44" s="7" t="inlineStr">
-        <is>
-          <t>Идентификатор игрока в казино. Белый список полей, которые видит модель. Всё остальное отбрасывается — расширение списка требует правки на нашей стороне.</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2793,7 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -2812,7 +2808,7 @@
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>Андрей Петров</t>
+          <t>1048576</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
@@ -2824,7 +2820,7 @@
       <c r="L45" s="7" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>Полное имя; из него берётся имя для приветствия.</t>
+          <t>Идентификатор игрока в казино. Белый список полей, которые видит модель. Всё остальное отбрасывается — расширение списка требует правки на нашей стороне.</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2852,7 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
@@ -2871,7 +2867,7 @@
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>player@example.com</t>
+          <t>Андрей Петров</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
@@ -2883,7 +2879,7 @@
       <c r="L46" s="7" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>Почта игрока.</t>
+          <t>Полное имя; из него берётся имя для приветствия.</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2911,7 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>activation_status</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -2930,7 +2926,7 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>player@example.com</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
@@ -2942,7 +2938,7 @@
       <c r="L47" s="7" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>Статус активации/верификации.</t>
+          <t>Почта игрока.</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2970,7 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>activation_status</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -2989,7 +2985,7 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
@@ -3001,7 +2997,7 @@
       <c r="L48" s="7" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>Страна.</t>
+          <t>Статус активации/верификации.</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3029,7 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>country</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -3048,7 +3044,7 @@
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>150.00 USDT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
@@ -3060,7 +3056,7 @@
       <c r="L49" s="7" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>Баланс строкой, вместе с валютой.</t>
+          <t>Страна.</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3088,7 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>vip_level</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
@@ -3107,7 +3103,7 @@
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>150.00 USDT</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
@@ -3119,7 +3115,7 @@
       <c r="L50" s="7" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>VIP-класс.</t>
+          <t>Баланс строкой, вместе с валютой.</t>
         </is>
       </c>
     </row>
@@ -3151,12 +3147,12 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>registration_date</t>
+          <t>vip_level</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>string (ISO-8601)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
@@ -3166,7 +3162,7 @@
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
@@ -3178,7 +3174,7 @@
       <c r="L51" s="7" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>Дата регистрации.</t>
+          <t>VIP-класс.</t>
         </is>
       </c>
     </row>
@@ -3210,38 +3206,34 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>iat</t>
+          <t>registration_date</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>int (unix seconds)</t>
+          <t>string (ISO-8601)</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>условно</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>1769606400</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>часть подписанного payload</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="inlineStr">
-        <is>
-          <t>Возраст токена ограничен 300 с</t>
-        </is>
-      </c>
+          <t>подпись HMAC-SHA256 секретом продукта</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr"/>
       <c r="L52" s="7" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>Момент выпуска подписи (антиреплей).</t>
+          <t>Дата регистрации.</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3265,7 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>exp</t>
+          <t>iat</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -3283,12 +3275,12 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>условно</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>1769606700</t>
+          <t>1769606400</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
@@ -3296,15 +3288,15 @@
           <t>часть подписанного payload</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>401 bad_handshake при истечении</t>
-        </is>
-      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>Возраст токена ограничен 300 с</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>Срок годности подписи.</t>
+          <t>Момент выпуска подписи (антиреплей).</t>
         </is>
       </c>
     </row>
@@ -3316,32 +3308,32 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Контракт: escalation</t>
+          <t>Контракт: user_context / signed_context</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Сайт / виджет</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>exp</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int (unix seconds)</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
@@ -3351,15 +3343,23 @@
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="J54" s="7" t="inlineStr"/>
+          <t>1769606700</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>часть подписанного payload</t>
+        </is>
+      </c>
       <c r="K54" s="7" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr"/>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>401 bad_handshake при истечении</t>
+        </is>
+      </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>Есть ли в этом ходе передача на человека.</t>
+          <t>Срок годности подписи.</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>final</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -3414,7 +3414,7 @@
       <c r="L55" s="7" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>true — сессия закрыта (дальше 409); false — карточка показана, диалог продолжается.</t>
+          <t>Есть ли в этом ходе передача на человека.</t>
         </is>
       </c>
     </row>
@@ -3446,22 +3446,22 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>final</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>условно</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>Передаю вас специалисту…</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr"/>
@@ -3469,7 +3469,7 @@
       <c r="L56" s="7" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>Текст карточки на языке ответа.</t>
+          <t>true — сессия закрыта (дальше 409); false — карточка показана, диалог продолжается.</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>button.label</t>
+          <t>message</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>Написать в поддержку</t>
+          <t>Передаю вас специалисту…</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr"/>
@@ -3524,7 +3524,7 @@
       <c r="L57" s="7" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>Подпись кнопки.</t>
+          <t>Текст карточки на языке ответа.</t>
         </is>
       </c>
     </row>
@@ -3556,12 +3556,12 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>button.url</t>
+          <t>button.label</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>string (URL)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>https://t.me/brand_bot?start=…</t>
+          <t>Написать в поддержку</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr"/>
@@ -3579,7 +3579,7 @@
       <c r="L58" s="7" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>Куда ведёт кнопка: статическая ссылка контакта или одноразовый диплинк в Telegram-бота.</t>
+          <t>Подпись кнопки.</t>
         </is>
       </c>
     </row>
@@ -3611,22 +3611,22 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>retention</t>
+          <t>button.url</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string (URL)</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>условно</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>https://t.me/brand_bot?start=…</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr"/>
@@ -3634,117 +3634,113 @@
       <c r="L59" s="7" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr">
         <is>
+          <t>Куда ведёт кнопка: статическая ссылка контакта или одноразовый диплинк в Telegram-бота.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Chat API</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Контракт: escalation</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>retention</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="inlineStr"/>
+      <c r="K60" s="7" t="inlineStr"/>
+      <c r="L60" s="7" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr">
+        <is>
           <t>Признак, что передача ведёт в Telegram-бота, а не на статическую ссылку.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Partner API</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>POST /partner/{product_id}/player-update</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>CRM казино</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr"/>
-      <c r="G60" s="5" t="inlineStr"/>
-      <c r="H60" s="4" t="inlineStr"/>
-      <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>Bearer &lt;handshake_secret продукта&gt;</t>
         </is>
       </c>
-      <c r="K60" s="4" t="inlineStr">
+      <c r="K61" s="4" t="inlineStr">
         <is>
           <t>Частичное обновление: поля со значением null не затираются · лимит partner:{ip}</t>
         </is>
       </c>
-      <c r="L60" s="4" t="inlineStr">
+      <c r="L61" s="4" t="inlineStr">
         <is>
           <t>401 unauthorized (единый ответ на все причины) · 429 rate_limited</t>
         </is>
       </c>
-      <c r="M60" s="4" t="inlineStr">
+      <c r="M61" s="4" t="inlineStr">
         <is>
           <t>Push профиля игрока из CRM в наш снапшот.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>Partner API</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>POST /partner/{product_id}/player-update</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>Заголовок</t>
-        </is>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>CRM казино</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>Authorization</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret&gt;</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I61" s="8" t="inlineStr">
-        <is>
-          <t>Bearer 8f2c…</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr"/>
-      <c r="L61" s="7" t="inlineStr"/>
-      <c r="M61" s="7" t="inlineStr">
-        <is>
-          <t>Тот же секрет продукта, что подписывает handshake.</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3757,7 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Заголовок</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -3776,12 +3772,12 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>player_id</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Bearer &lt;handshake_secret&gt;</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -3791,15 +3787,19 @@
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>1048576</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="inlineStr"/>
+          <t>Bearer 8f2c…</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
       <c r="K62" s="7" t="inlineStr"/>
       <c r="L62" s="7" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>Ключ игрока на стороне казино.</t>
+          <t>Тот же секрет продукта, что подписывает handshake.</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>player_id</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>Андрей Петров</t>
+          <t>1048576</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr"/>
@@ -3854,7 +3854,7 @@
       <c r="L63" s="7" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>Поле профиля. null = не менять.</t>
+          <t>Ключ игрока на стороне казино.</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>player@example.com</t>
+          <t>Андрей Петров</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>activation_status</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>player@example.com</t>
         </is>
       </c>
       <c r="J65" s="7" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>activation_status</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="J66" s="7" t="inlineStr"/>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>country</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>150.00 USDT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr"/>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>vip_level</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>150.00 USDT</t>
         </is>
       </c>
       <c r="J68" s="7" t="inlineStr"/>
@@ -4161,12 +4161,12 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>registration_date</t>
+          <t>vip_level</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>string (ISO-8601)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>last_login_at</t>
+          <t>registration_date</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28T10:15:00Z</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
       <c r="L70" s="7" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>Последний вход — сигнал активности.</t>
+          <t>Поле профиля. null = не менять.</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>last_played_at</t>
+          <t>last_login_at</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
@@ -4294,7 +4294,7 @@
       <c r="L71" s="7" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>Последняя игра.</t>
+          <t>Последний вход — сигнал активности.</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>last_deposit_at</t>
+          <t>last_played_at</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
@@ -4349,7 +4349,7 @@
       <c r="L72" s="7" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>Последний депозит.</t>
+          <t>Последняя игра.</t>
         </is>
       </c>
     </row>
@@ -4366,37 +4366,37 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D73" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>ok / updated</t>
+          <t>last_deposit_at</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>bool / bool</t>
+          <t>string (ISO-8601)</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>{"ok":true,"updated":true}</t>
+          <t>2026-07-28T10:15:00Z</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr"/>
@@ -4404,113 +4404,113 @@
       <c r="L73" s="7" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr">
         <is>
+          <t>Последний депозит.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>Partner API</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/player-update</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>ok / updated</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>bool / bool</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>{"ok":true,"updated":true}</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr"/>
+      <c r="K74" s="7" t="inlineStr"/>
+      <c r="L74" s="7" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr">
+        <is>
           <t>Признак приёма и факта изменения.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>Partner API</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>CRM казино</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr"/>
-      <c r="G74" s="5" t="inlineStr"/>
-      <c r="H74" s="4" t="inlineStr"/>
-      <c r="I74" s="5" t="inlineStr"/>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr"/>
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" s="5" t="inlineStr"/>
+      <c r="J75" s="4" t="inlineStr">
         <is>
           <t>Bearer &lt;handshake_secret продукта&gt;</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr">
+      <c r="K75" s="4" t="inlineStr">
         <is>
           <t>Идемпотентно по event_id (доставка at-least-once безопасна) · пакет до 500 событий · payload до 8 KiB · лимит partner:{ip}</t>
         </is>
       </c>
-      <c r="L74" s="4" t="inlineStr">
+      <c r="L75" s="4" t="inlineStr">
         <is>
           <t>401 · 413 batch_too_large · 422 invalid_event · 429</t>
         </is>
       </c>
-      <c r="M74" s="4" t="inlineStr">
+      <c r="M75" s="4" t="inlineStr">
         <is>
           <t>Канонический поток событий казино: кормит проактивного агента и обновляет сигналы активности игрока.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>Partner API</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>POST /partner/{product_id}/event</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>CRM казино</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>event_id</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>string (≤64)</t>
-        </is>
-      </c>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>evt_2026072801</t>
-        </is>
-      </c>
-      <c r="J75" s="7" t="inlineStr"/>
-      <c r="K75" s="7" t="inlineStr"/>
-      <c r="L75" s="7" t="inlineStr"/>
-      <c r="M75" s="7" t="inlineStr">
-        <is>
-          <t>Ключ идемпотентности. Повтор считается дубликатом, а не ошибкой.</t>
         </is>
       </c>
     </row>
@@ -4542,12 +4542,12 @@
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>event_name</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>string (из таксономии)</t>
+          <t>string (≤64)</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
@@ -4557,19 +4557,15 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>deposit_confirmed</t>
+          <t>evt_2026072801</t>
         </is>
       </c>
       <c r="J76" s="7" t="inlineStr"/>
       <c r="K76" s="7" t="inlineStr"/>
-      <c r="L76" s="7" t="inlineStr">
-        <is>
-          <t>422 invalid_event на неизвестное имя</t>
-        </is>
-      </c>
+      <c r="L76" s="7" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr">
         <is>
-          <t>Имя события. Таксономия — контракт, а не рекомендация; список ниже.</t>
+          <t>Ключ идемпотентности. Повтор считается дубликатом, а не ошибкой.</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4597,12 @@
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>player_id | user_id</t>
+          <t>event_name</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string (из таксономии)</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
@@ -4616,15 +4612,19 @@
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>1048576</t>
+          <t>deposit_confirmed</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr"/>
       <c r="K77" s="7" t="inlineStr"/>
-      <c r="L77" s="7" t="inlineStr"/>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>422 invalid_event на неизвестное имя</t>
+        </is>
+      </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>Игрок, к которому относится событие.</t>
+          <t>Имя события. Таксономия — контракт, а не рекомендация; список ниже.</t>
         </is>
       </c>
     </row>
@@ -4656,22 +4656,22 @@
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>tg_user_id</t>
+          <t>player_id | user_id</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>584210394</t>
+          <t>1048576</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr"/>
@@ -4679,7 +4679,7 @@
       <c r="L78" s="7" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr">
         <is>
-          <t>Явный получатель, когда один player_id связан с несколькими Telegram-аккаунтами.</t>
+          <t>Игрок, к которому относится событие.</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>tg_user_id</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>string (ISO-8601)</t>
+          <t>int</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28T10:15:00Z</t>
+          <t>584210394</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr"/>
@@ -4734,7 +4734,7 @@
       <c r="L79" s="7" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>Время события. Значение из будущего приводится к текущему моменту.</t>
+          <t>Явный получатель, когда один player_id связан с несколькими Telegram-аккаунтами.</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>event_version</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string (ISO-8601)</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2026-07-28T10:15:00Z</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr"/>
@@ -4789,7 +4789,7 @@
       <c r="L80" s="7" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr">
         <is>
-          <t>Версия схемы события на стороне отправителя.</t>
+          <t>Время события. Значение из будущего приводится к текущему моменту.</t>
         </is>
       </c>
     </row>
@@ -4821,12 +4821,12 @@
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>payload</t>
+          <t>event_version</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>object (≤8 KiB)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>{"amount":"50.00","currency":"USDT"}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J81" s="7" t="inlineStr"/>
@@ -4844,7 +4844,7 @@
       <c r="L81" s="7" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr">
         <is>
-          <t>Детали события; может нести и поля профиля — они обновят снапшот.</t>
+          <t>Версия схемы события на стороне отправителя.</t>
         </is>
       </c>
     </row>
@@ -4876,12 +4876,12 @@
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>events</t>
+          <t>payload</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>[object] (≤500)</t>
+          <t>object (≤8 KiB)</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>[{"event_id":"…","event_name":"…"}]</t>
+          <t>{"amount":"50.00","currency":"USDT"}</t>
         </is>
       </c>
       <c r="J82" s="7" t="inlineStr"/>
@@ -4899,7 +4899,7 @@
       <c r="L82" s="7" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr">
         <is>
-          <t>Пакетная форма. Взаимоисключима с плоскими полями выше.</t>
+          <t>Детали события; может нести и поля профиля — они обновят снапшот.</t>
         </is>
       </c>
     </row>
@@ -4916,37 +4916,37 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>stored / duplicates / invalid</t>
+          <t>events</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>int|bool</t>
+          <t>[object] (≤500)</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>{"ok":true,"stored":12,"duplicates":3}</t>
+          <t>[{"event_id":"…","event_name":"…"}]</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr"/>
@@ -4954,7 +4954,7 @@
       <c r="L83" s="7" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>Итог приёма: сколько принято, сколько дублей, сколько отвергнуто.</t>
+          <t>Пакетная форма. Взаимоисключима с плоскими полями выше.</t>
         </is>
       </c>
     </row>
@@ -4971,49 +4971,45 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>session_started</t>
+          <t>stored / duplicates / invalid</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>event_name · Сессия</t>
-        </is>
-      </c>
-      <c r="H84" s="7" t="inlineStr"/>
+          <t>int|bool</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"session_started"}</t>
-        </is>
-      </c>
-      <c r="J84" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K84" s="7" t="inlineStr">
-        <is>
-          <t>обновляет last_login_at</t>
-        </is>
-      </c>
+          <t>{"ok":true,"stored":12,"duplicates":3}</t>
+        </is>
+      </c>
+      <c r="J84" s="7" t="inlineStr"/>
+      <c r="K84" s="7" t="inlineStr"/>
       <c r="L84" s="7" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr">
         <is>
-          <t>Игрок начал сессию на сайте или в приложении.</t>
+          <t>Итог приёма: сколько принято, сколько дублей, сколько отвергнуто.</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5041,7 @@
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>session_ended</t>
+          <t>session_started</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
@@ -5056,7 +5052,7 @@
       <c r="H85" s="7" t="inlineStr"/>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"session_ended"}</t>
+          <t>{"event_name":"session_started"}</t>
         </is>
       </c>
       <c r="J85" s="7" t="inlineStr">
@@ -5072,7 +5068,7 @@
       <c r="L85" s="7" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>Игрок завершил сессию.</t>
+          <t>Игрок начал сессию на сайте или в приложении.</t>
         </is>
       </c>
     </row>
@@ -5104,18 +5100,18 @@
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>deposit_initiated</t>
+          <t>session_ended</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>event_name · Платежи</t>
+          <t>event_name · Сессия</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr"/>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"deposit_initiated"}</t>
+          <t>{"event_name":"session_ended"}</t>
         </is>
       </c>
       <c r="J86" s="7" t="inlineStr">
@@ -5125,13 +5121,13 @@
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>обновляет last_login_at</t>
         </is>
       </c>
       <c r="L86" s="7" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr">
         <is>
-          <t>Депозит начат, ещё не подтверждён.</t>
+          <t>Игрок завершил сессию.</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5159,7 @@
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>deposit_confirmed</t>
+          <t>deposit_initiated</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
@@ -5174,7 +5170,7 @@
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"deposit_confirmed"}</t>
+          <t>{"event_name":"deposit_initiated"}</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
@@ -5184,13 +5180,13 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>обновляет last_deposit_at</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>Депозит зачислен — сильнейший позитивный сигнал.</t>
+          <t>Депозит начат, ещё не подтверждён.</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5218,7 @@
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>deposit_failed</t>
+          <t>deposit_confirmed</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
@@ -5233,7 +5229,7 @@
       <c r="H88" s="7" t="inlineStr"/>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"deposit_failed"}</t>
+          <t>{"event_name":"deposit_confirmed"}</t>
         </is>
       </c>
       <c r="J88" s="7" t="inlineStr">
@@ -5243,13 +5239,13 @@
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>обновляет last_deposit_at</t>
         </is>
       </c>
       <c r="L88" s="7" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr">
         <is>
-          <t>Депозит не прошёл.</t>
+          <t>Депозит зачислен — сильнейший позитивный сигнал.</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5277,7 @@
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>withdrawal_settled</t>
+          <t>deposit_failed</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
@@ -5292,7 +5288,7 @@
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"withdrawal_settled"}</t>
+          <t>{"event_name":"deposit_failed"}</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
@@ -5308,7 +5304,7 @@
       <c r="L89" s="7" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>Вывод завершён.</t>
+          <t>Депозит не прошёл.</t>
         </is>
       </c>
     </row>
@@ -5340,18 +5336,18 @@
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>bet_settled</t>
+          <t>withdrawal_settled</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>event_name · Игра</t>
+          <t>event_name · Платежи</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr"/>
       <c r="I90" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bet_settled"}</t>
+          <t>{"event_name":"withdrawal_settled"}</t>
         </is>
       </c>
       <c r="J90" s="7" t="inlineStr">
@@ -5361,13 +5357,13 @@
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
-          <t>обновляет last_played_at</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L90" s="7" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr">
         <is>
-          <t>Ставка рассчитана. Сумма проигрыша за 24 ч влияет на тон коммуникации.</t>
+          <t>Вывод завершён.</t>
         </is>
       </c>
     </row>
@@ -5399,18 +5395,18 @@
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>bonus_granted</t>
+          <t>bet_settled</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>event_name · Бонусы</t>
+          <t>event_name · Игра</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr"/>
       <c r="I91" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_granted"}</t>
+          <t>{"event_name":"bet_settled"}</t>
         </is>
       </c>
       <c r="J91" s="7" t="inlineStr">
@@ -5420,13 +5416,13 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>обновляет last_played_at</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr">
         <is>
-          <t>Бонус начислен.</t>
+          <t>Ставка рассчитана. Сумма проигрыша за 24 ч влияет на тон коммуникации.</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5454,7 @@
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>bonus_claimed</t>
+          <t>bonus_granted</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
@@ -5469,7 +5465,7 @@
       <c r="H92" s="7" t="inlineStr"/>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_claimed"}</t>
+          <t>{"event_name":"bonus_granted"}</t>
         </is>
       </c>
       <c r="J92" s="7" t="inlineStr">
@@ -5485,7 +5481,7 @@
       <c r="L92" s="7" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>Бонус активирован игроком.</t>
+          <t>Бонус начислен.</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5513,7 @@
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>bonus_completed</t>
+          <t>bonus_claimed</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
@@ -5528,7 +5524,7 @@
       <c r="H93" s="7" t="inlineStr"/>
       <c r="I93" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_completed"}</t>
+          <t>{"event_name":"bonus_claimed"}</t>
         </is>
       </c>
       <c r="J93" s="7" t="inlineStr">
@@ -5544,7 +5540,7 @@
       <c r="L93" s="7" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr">
         <is>
-          <t>Отыгрыш завершён.</t>
+          <t>Бонус активирован игроком.</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5572,7 @@
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>bonus_expired</t>
+          <t>bonus_completed</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
@@ -5587,7 +5583,7 @@
       <c r="H94" s="7" t="inlineStr"/>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_expired"}</t>
+          <t>{"event_name":"bonus_completed"}</t>
         </is>
       </c>
       <c r="J94" s="7" t="inlineStr">
@@ -5603,7 +5599,7 @@
       <c r="L94" s="7" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr">
         <is>
-          <t>Бонус сгорел.</t>
+          <t>Отыгрыш завершён.</t>
         </is>
       </c>
     </row>
@@ -5635,18 +5631,18 @@
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>kyc_started</t>
+          <t>bonus_expired</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>event_name · Верификация</t>
+          <t>event_name · Бонусы</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"kyc_started"}</t>
+          <t>{"event_name":"bonus_expired"}</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr">
@@ -5662,7 +5658,7 @@
       <c r="L95" s="7" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>Верификация начата.</t>
+          <t>Бонус сгорел.</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5690,7 @@
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>kyc_approved</t>
+          <t>kyc_started</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
@@ -5705,7 +5701,7 @@
       <c r="H96" s="7" t="inlineStr"/>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"kyc_approved"}</t>
+          <t>{"event_name":"kyc_started"}</t>
         </is>
       </c>
       <c r="J96" s="7" t="inlineStr">
@@ -5721,7 +5717,7 @@
       <c r="L96" s="7" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr">
         <is>
-          <t>Верификация пройдена.</t>
+          <t>Верификация начата.</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5749,7 @@
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>kyc_rejected</t>
+          <t>kyc_approved</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
@@ -5764,7 +5760,7 @@
       <c r="H97" s="7" t="inlineStr"/>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"kyc_rejected"}</t>
+          <t>{"event_name":"kyc_approved"}</t>
         </is>
       </c>
       <c r="J97" s="7" t="inlineStr">
@@ -5780,7 +5776,7 @@
       <c r="L97" s="7" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>Верификация отклонена.</t>
+          <t>Верификация пройдена.</t>
         </is>
       </c>
     </row>
@@ -5812,18 +5808,18 @@
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>xp_granted</t>
+          <t>kyc_rejected</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>event_name · Лояльность</t>
+          <t>event_name · Верификация</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"xp_granted"}</t>
+          <t>{"event_name":"kyc_rejected"}</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr">
@@ -5839,7 +5835,7 @@
       <c r="L98" s="7" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr">
         <is>
-          <t>Начислен опыт.</t>
+          <t>Верификация отклонена.</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5867,7 @@
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>level_up</t>
+          <t>xp_granted</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
@@ -5882,7 +5878,7 @@
       <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"level_up"}</t>
+          <t>{"event_name":"xp_granted"}</t>
         </is>
       </c>
       <c r="J99" s="7" t="inlineStr">
@@ -5898,7 +5894,7 @@
       <c r="L99" s="7" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr">
         <is>
-          <t>Новый уровень.</t>
+          <t>Начислен опыт.</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5926,7 @@
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>class_up</t>
+          <t>level_up</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
@@ -5941,7 +5937,7 @@
       <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"class_up"}</t>
+          <t>{"event_name":"level_up"}</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr">
@@ -5957,7 +5953,7 @@
       <c r="L100" s="7" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr">
         <is>
-          <t>Новый класс / VIP-тир.</t>
+          <t>Новый уровень.</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5985,7 @@
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>downgrade</t>
+          <t>class_up</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -6000,7 +5996,7 @@
       <c r="H101" s="7" t="inlineStr"/>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"downgrade"}</t>
+          <t>{"event_name":"class_up"}</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
@@ -6016,7 +6012,7 @@
       <c r="L101" s="7" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>Понижение класса.</t>
+          <t>Новый класс / VIP-тир.</t>
         </is>
       </c>
     </row>
@@ -6048,18 +6044,18 @@
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>highlights_pack_opened</t>
+          <t>downgrade</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>event_name · Активности</t>
+          <t>event_name · Лояльность</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr"/>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"highlights_pack_opened"}</t>
+          <t>{"event_name":"downgrade"}</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
@@ -6075,7 +6071,7 @@
       <c r="L102" s="7" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr">
         <is>
-          <t>Открыт пак/кейс.</t>
+          <t>Понижение класса.</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6103,7 @@
       </c>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>highlights_pack_completed</t>
+          <t>highlights_pack_opened</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr">
@@ -6118,7 +6114,7 @@
       <c r="H103" s="7" t="inlineStr"/>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"highlights_pack_completed"}</t>
+          <t>{"event_name":"highlights_pack_opened"}</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -6134,7 +6130,7 @@
       <c r="L103" s="7" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr">
         <is>
-          <t>Пак завершён.</t>
+          <t>Открыт пак/кейс.</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6162,7 @@
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>check_in_done</t>
+          <t>highlights_pack_completed</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
@@ -6177,7 +6173,7 @@
       <c r="H104" s="7" t="inlineStr"/>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"check_in_done"}</t>
+          <t>{"event_name":"highlights_pack_completed"}</t>
         </is>
       </c>
       <c r="J104" s="7" t="inlineStr">
@@ -6193,7 +6189,7 @@
       <c r="L104" s="7" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr">
         <is>
-          <t>Ежедневный чек-ин выполнен.</t>
+          <t>Пак завершён.</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6221,7 @@
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>mission_completed</t>
+          <t>check_in_done</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
@@ -6236,7 +6232,7 @@
       <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"mission_completed"}</t>
+          <t>{"event_name":"check_in_done"}</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
@@ -6252,113 +6248,117 @@
       <c r="L105" s="7" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr">
         <is>
+          <t>Ежедневный чек-ин выполнен.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>Partner API</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/event</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>Событие</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>mission_completed</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>event_name · Активности</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="inlineStr"/>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>{"event_name":"mission_completed"}</t>
+        </is>
+      </c>
+      <c r="J106" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K106" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L106" s="7" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr">
+        <is>
           <t>Миссия или квест завершён.</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t>Telegram</t>
         </is>
       </c>
-      <c r="B106" s="5" t="inlineStr">
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>POST /api/retention/deeplink</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>Вход/Выход</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
+      <c r="E107" s="4" t="inlineStr">
         <is>
           <t>Сайт / виджет</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr"/>
-      <c r="G106" s="5" t="inlineStr"/>
-      <c r="H106" s="4" t="inlineStr"/>
-      <c r="I106" s="5" t="inlineStr"/>
-      <c r="J106" s="4" t="inlineStr">
+      <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="4" t="inlineStr"/>
+      <c r="I107" s="5" t="inlineStr"/>
+      <c r="J107" s="4" t="inlineStr">
         <is>
           <t>нет (публичный) + лимит по IP</t>
         </is>
       </c>
-      <c r="K106" s="4" t="inlineStr">
+      <c r="K107" s="4" t="inlineStr">
         <is>
           <t>Нонс одноразовый, живёт 120 с (настраивается)</t>
         </is>
       </c>
-      <c r="L106" s="4" t="inlineStr">
+      <c r="L107" s="4" t="inlineStr">
         <is>
           <t>403 bad_widget_key | retention_disabled · 409 no_bot · 401 bad_handshake · 429</t>
         </is>
       </c>
-      <c r="M106" s="4" t="inlineStr">
+      <c r="M107" s="4" t="inlineStr">
         <is>
           <t>Сайт получает одноразовую ссылку в Telegram-бота с профилем игрока.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="7" t="inlineStr">
-        <is>
-          <t>Telegram</t>
-        </is>
-      </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>POST /api/retention/deeplink</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D107" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>Сайт / виджет</t>
-        </is>
-      </c>
-      <c r="F107" s="8" t="inlineStr">
-        <is>
-          <t>widget_key</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr">
-        <is>
-          <t>string (wk_…)</t>
-        </is>
-      </c>
-      <c r="H107" s="7" t="inlineStr">
-        <is>
-          <t>условно</t>
-        </is>
-      </c>
-      <c r="I107" s="8" t="inlineStr">
-        <is>
-          <t>wk_7f3a…</t>
-        </is>
-      </c>
-      <c r="J107" s="7" t="inlineStr"/>
-      <c r="K107" s="7" t="inlineStr"/>
-      <c r="L107" s="7" t="inlineStr"/>
-      <c r="M107" s="7" t="inlineStr">
-        <is>
-          <t>Продукт, чей бот открывать.</t>
         </is>
       </c>
     </row>
@@ -6390,12 +6390,12 @@
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
-          <t>signed_context</t>
+          <t>widget_key</t>
         </is>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>string (подпись)</t>
+          <t>string (wk_…)</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>eyJpZCI6…​.QkFTRTY0</t>
+          <t>wk_7f3a…</t>
         </is>
       </c>
       <c r="J108" s="7" t="inlineStr"/>
@@ -6413,7 +6413,7 @@
       <c r="L108" s="7" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr">
         <is>
-          <t>Профиль игрока — те же поля и та же подпись, что в Chat API.</t>
+          <t>Продукт, чей бот открывать.</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>escalation</t>
+          <t>signed_context</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string (подпись)</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>условно</t>
         </is>
       </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>eyJpZCI6…​.QkFTRTY0</t>
         </is>
       </c>
       <c r="J109" s="7" t="inlineStr"/>
@@ -6468,7 +6468,7 @@
       <c r="L109" s="7" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr">
         <is>
-          <t>true — точка входа «к менеджеру».</t>
+          <t>Профиль игрока — те же поля и та же подпись, что в Chat API.</t>
         </is>
       </c>
     </row>
@@ -6500,12 +6500,12 @@
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
-          <t>lang</t>
+          <t>escalation</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>string (код или локаль)</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>ru</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J110" s="7" t="inlineStr"/>
@@ -6523,7 +6523,7 @@
       <c r="L110" s="7" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr">
         <is>
-          <t>Язык, в котором откроется бот.</t>
+          <t>true — точка входа «к менеджеру».</t>
         </is>
       </c>
     </row>
@@ -6540,37 +6540,37 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Сайт / виджет</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>deep_link</t>
+          <t>lang</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>string (URL)</t>
+          <t>string (код или локаль)</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>https://t.me/brand_bot?start=Ax7…</t>
+          <t>ru</t>
         </is>
       </c>
       <c r="J111" s="7" t="inlineStr"/>
@@ -6578,7 +6578,7 @@
       <c r="L111" s="7" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr">
         <is>
-          <t>Ссылка для кнопки. Нонс погашается при первом /start.</t>
+          <t>Язык, в котором откроется бот.</t>
         </is>
       </c>
     </row>
@@ -6610,12 +6610,12 @@
       </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
-          <t>nonce</t>
+          <t>deep_link</t>
         </is>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string (URL)</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>Ax7kQ…</t>
+          <t>https://t.me/brand_bot?start=Ax7…</t>
         </is>
       </c>
       <c r="J112" s="7" t="inlineStr"/>
@@ -6633,113 +6633,113 @@
       <c r="L112" s="7" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr">
         <is>
+          <t>Ссылка для кнопки. Нонс погашается при первом /start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/retention/deeplink</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>nonce</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H113" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>Ax7kQ…</t>
+        </is>
+      </c>
+      <c r="J113" s="7" t="inlineStr"/>
+      <c r="K113" s="7" t="inlineStr"/>
+      <c r="L113" s="7" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr">
+        <is>
           <t>Тот же одноразовый токен отдельным полем.</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
         <is>
           <t>Telegram</t>
         </is>
       </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>POST /telegram/webhook/{secret}</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
         <is>
           <t>Telegram</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr"/>
-      <c r="G113" s="5" t="inlineStr"/>
-      <c r="H113" s="4" t="inlineStr"/>
-      <c r="I113" s="5" t="inlineStr"/>
-      <c r="J113" s="4" t="inlineStr">
+      <c r="F114" s="5" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr"/>
+      <c r="H114" s="4" t="inlineStr"/>
+      <c r="I114" s="5" t="inlineStr"/>
+      <c r="J114" s="4" t="inlineStr">
         <is>
           <t>путь = webhook-токен продукта (роутинг) + заголовок X-Telegram-Bot-Api-Secret-Token</t>
         </is>
       </c>
-      <c r="K113" s="4" t="inlineStr">
+      <c r="K114" s="4" t="inlineStr">
         <is>
           <t>Всегда быстрый 200 (иначе Telegram ретраит); ход ИИ выполняется в фоне</t>
         </is>
       </c>
-      <c r="L113" s="4" t="inlineStr">
+      <c r="L114" s="4" t="inlineStr">
         <is>
           <t>403 bad_secret_token · неизвестный токен пути → тихий 200</t>
         </is>
       </c>
-      <c r="M113" s="4" t="inlineStr">
+      <c r="M114" s="4" t="inlineStr">
         <is>
           <t>Приём апдейтов Telegram — второй фасад над тем же ИИ-ядром.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="7" t="inlineStr">
-        <is>
-          <t>Telegram</t>
-        </is>
-      </c>
-      <c r="B114" s="8" t="inlineStr">
-        <is>
-          <t>POST /telegram/webhook/{secret}</t>
-        </is>
-      </c>
-      <c r="C114" s="7" t="inlineStr">
-        <is>
-          <t>Заголовок</t>
-        </is>
-      </c>
-      <c r="D114" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="inlineStr">
-        <is>
-          <t>Telegram</t>
-        </is>
-      </c>
-      <c r="F114" s="8" t="inlineStr">
-        <is>
-          <t>X-Telegram-Bot-Api-Secret-Token</t>
-        </is>
-      </c>
-      <c r="G114" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H114" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I114" s="8" t="inlineStr">
-        <is>
-          <t>b4c9…</t>
-        </is>
-      </c>
-      <c r="J114" s="7" t="inlineStr"/>
-      <c r="K114" s="7" t="inlineStr"/>
-      <c r="L114" s="7" t="inlineStr"/>
-      <c r="M114" s="7" t="inlineStr">
-        <is>
-          <t>Секрет, заданный при регистрации вебхука. Защищает от подделки апдейтов тем, кто узнал URL.</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Заголовок</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>X-Telegram-Bot-Api-Secret-Token</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>object (Telegram Bot API)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>{"update_id":1,"message":{…}}</t>
+          <t>b4c9…</t>
         </is>
       </c>
       <c r="J115" s="7" t="inlineStr"/>
@@ -6794,113 +6794,113 @@
       <c r="L115" s="7" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr">
         <is>
+          <t>Секрет, заданный при регистрации вебхука. Защищает от подделки апдейтов тем, кто узнал URL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>POST /telegram/webhook/{secret}</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>object (Telegram Bot API)</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>{"update_id":1,"message":{…}}</t>
+        </is>
+      </c>
+      <c r="J116" s="7" t="inlineStr"/>
+      <c r="K116" s="7" t="inlineStr"/>
+      <c r="L116" s="7" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr">
+        <is>
           <t>Стандартный формат Telegram.</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>Admin API</t>
         </is>
       </c>
-      <c r="B116" s="5" t="inlineStr">
+      <c r="B117" s="5" t="inlineStr">
         <is>
           <t>POST /admin/login</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D116" s="6" t="inlineStr">
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t>Вход/Выход</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
+      <c r="E117" s="4" t="inlineStr">
         <is>
           <t>Внешняя админка</t>
         </is>
       </c>
-      <c r="F116" s="5" t="inlineStr"/>
-      <c r="G116" s="5" t="inlineStr"/>
-      <c r="H116" s="4" t="inlineStr"/>
-      <c r="I116" s="5" t="inlineStr"/>
-      <c r="J116" s="4" t="inlineStr">
+      <c r="F117" s="5" t="inlineStr"/>
+      <c r="G117" s="5" t="inlineStr"/>
+      <c r="H117" s="4" t="inlineStr"/>
+      <c r="I117" s="5" t="inlineStr"/>
+      <c r="J117" s="4" t="inlineStr">
         <is>
           <t>нет (публичный)</t>
         </is>
       </c>
-      <c r="K116" s="4" t="inlineStr">
+      <c r="K117" s="4" t="inlineStr">
         <is>
           <t>Лимит попыток входа с IP</t>
         </is>
       </c>
-      <c r="L116" s="4" t="inlineStr">
+      <c r="L117" s="4" t="inlineStr">
         <is>
           <t>401 · 429</t>
         </is>
       </c>
-      <c r="M116" s="4" t="inlineStr">
+      <c r="M117" s="4" t="inlineStr">
         <is>
           <t>Вход человека-администратора: email + пароль → JWT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="7" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B117" s="8" t="inlineStr">
-        <is>
-          <t>POST /admin/login</t>
-        </is>
-      </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F117" s="8" t="inlineStr">
-        <is>
-          <t>email / password</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t>string / string</t>
-        </is>
-      </c>
-      <c r="H117" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I117" s="8" t="inlineStr">
-        <is>
-          <t>ops@brand.com</t>
-        </is>
-      </c>
-      <c r="J117" s="7" t="inlineStr"/>
-      <c r="K117" s="7" t="inlineStr"/>
-      <c r="L117" s="7" t="inlineStr"/>
-      <c r="M117" s="7" t="inlineStr">
-        <is>
-          <t>Учётная запись администратора.</t>
         </is>
       </c>
     </row>
@@ -6917,27 +6917,27 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D118" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Внешняя админка</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>email / password</t>
         </is>
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>string (JWT)</t>
+          <t>string / string</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>eyJhbGciOiJIUzI1NiJ9…</t>
+          <t>ops@brand.com</t>
         </is>
       </c>
       <c r="J118" s="7" t="inlineStr"/>
@@ -6955,7 +6955,7 @@
       <c r="L118" s="7" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr">
         <is>
-          <t>Админ-токен; продлевается сам при активной работе.</t>
+          <t>Учётная запись администратора.</t>
         </is>
       </c>
     </row>
@@ -6967,105 +6967,117 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
+          <t>POST /admin/login</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>string (JWT)</t>
+        </is>
+      </c>
+      <c r="H119" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I119" s="8" t="inlineStr">
+        <is>
+          <t>eyJhbGciOiJIUzI1NiJ9…</t>
+        </is>
+      </c>
+      <c r="J119" s="7" t="inlineStr"/>
+      <c r="K119" s="7" t="inlineStr"/>
+      <c r="L119" s="7" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr">
+        <is>
+          <t>Админ-токен; продлевается сам при активной работе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
           <t>* /admin/*</t>
         </is>
       </c>
-      <c r="C119" s="7" t="inlineStr">
+      <c r="C120" s="7" t="inlineStr">
         <is>
           <t>Заголовок</t>
         </is>
       </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
         <is>
           <t>Внешняя админка</t>
         </is>
       </c>
-      <c r="F119" s="8" t="inlineStr">
+      <c r="F120" s="8" t="inlineStr">
         <is>
           <t>Authorization</t>
         </is>
       </c>
-      <c r="G119" s="8" t="inlineStr">
+      <c r="G120" s="8" t="inlineStr">
         <is>
           <t>Bearer &lt;JWT&gt; | Bearer sak_…</t>
         </is>
       </c>
-      <c r="H119" s="7" t="inlineStr">
+      <c r="H120" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="I119" s="8" t="inlineStr">
+      <c r="I120" s="8" t="inlineStr">
         <is>
           <t>Bearer sak_9f2c…</t>
         </is>
       </c>
-      <c r="J119" s="7" t="inlineStr">
+      <c r="J120" s="7" t="inlineStr">
         <is>
           <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
         </is>
       </c>
-      <c r="K119" s="7" t="inlineStr">
+      <c r="K120" s="7" t="inlineStr">
         <is>
           <t>Сервисный ключ несёт ОДНУ роль в ОДНОМ скоупе (global/partner/product); деактивация действует со следующего запроса</t>
         </is>
       </c>
-      <c r="L119" s="7" t="inlineStr">
+      <c r="L120" s="7" t="inlineStr">
         <is>
           <t>401 unauthorized · 403 forbidden (вне скоупа)</t>
         </is>
       </c>
-      <c r="M119" s="7" t="inlineStr">
+      <c r="M120" s="7" t="inlineStr">
         <is>
           <t>Единая авторизация всего админ-контура. Для машин — ключ sak_…, который выдаётся человеком-админом и показывается ровно один раз.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>GET /admin/structure</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D120" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr"/>
-      <c r="G120" s="5" t="inlineStr"/>
-      <c r="H120" s="4" t="inlineStr"/>
-      <c r="I120" s="5" t="inlineStr"/>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K120" s="4" t="inlineStr"/>
-      <c r="L120" s="4" t="inlineStr"/>
-      <c r="M120" s="4" t="inlineStr">
-        <is>
-          <t>Дерево партнёров и продуктов — точка синхронизации справочников с внешними системами.</t>
         </is>
       </c>
     </row>
@@ -7077,7 +7089,7 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/me</t>
+          <t>GET /admin/structure</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -7108,7 +7120,7 @@
       <c r="L121" s="4" t="inlineStr"/>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>Кто вызывает и какие у него скоупы — для проверки прав на своей стороне.</t>
+          <t>Дерево партнёров и продуктов — точка синхронизации справочников с внешними системами.</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7132,7 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>POST /admin/partners, PUT /admin/partners/{id}</t>
+          <t>GET /admin/me</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -7128,9 +7140,9 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D122" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -7148,14 +7160,10 @@
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr"/>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>401 · 403</t>
-        </is>
-      </c>
+      <c r="L122" s="4" t="inlineStr"/>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>Заведение и правка партнёра.</t>
+          <t>Кто вызывает и какие у него скоупы — для проверки прав на своей стороне.</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7175,7 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>POST /admin/products</t>
+          <t>POST /admin/partners, PUT /admin/partners/{id}</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -7175,9 +7183,9 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -7194,78 +7202,66 @@
           <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
         </is>
       </c>
-      <c r="K123" s="4" t="inlineStr">
+      <c r="K123" s="4" t="inlineStr"/>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>401 · 403</t>
+        </is>
+      </c>
+      <c r="M123" s="4" t="inlineStr">
+        <is>
+          <t>Заведение и правка партнёра.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>POST /admin/products</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr"/>
+      <c r="H124" s="4" t="inlineStr"/>
+      <c r="I124" s="5" t="inlineStr"/>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K124" s="4" t="inlineStr">
         <is>
           <t>Создание продукта автоматически засевает рабочую конфигурацию</t>
         </is>
       </c>
-      <c r="L123" s="4" t="inlineStr">
+      <c r="L124" s="4" t="inlineStr">
         <is>
           <t>401 · 403</t>
         </is>
       </c>
-      <c r="M123" s="4" t="inlineStr">
+      <c r="M124" s="4" t="inlineStr">
         <is>
           <t>Заведение казино. В ответе — публичный widget_key для встраивания виджета.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="7" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B124" s="8" t="inlineStr">
-        <is>
-          <t>PUT /admin/products/{id}</t>
-        </is>
-      </c>
-      <c r="C124" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D124" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F124" s="8" t="inlineStr">
-        <is>
-          <t>name, active, site_url, turnstile_site_key</t>
-        </is>
-      </c>
-      <c r="G124" s="8" t="inlineStr">
-        <is>
-          <t>string / bool</t>
-        </is>
-      </c>
-      <c r="H124" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I124" s="8" t="inlineStr">
-        <is>
-          <t>{"site_url":"https://brand.com"}</t>
-        </is>
-      </c>
-      <c r="J124" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K124" s="7" t="inlineStr"/>
-      <c r="L124" s="7" t="inlineStr"/>
-      <c r="M124" s="7" t="inlineStr">
-        <is>
-          <t>Публичная конфигурация продукта.</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7273,7 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>PUT /admin/products/{id}/secrets</t>
+          <t>PUT /admin/products/{id}</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
@@ -7297,12 +7293,12 @@
       </c>
       <c r="F125" s="8" t="inlineStr">
         <is>
-          <t>openai_key_primary, openai_key_fallback, handshake_secret, telegram_bot_token, player_api_key, turnstile_secret</t>
+          <t>name, active, site_url, turnstile_site_key</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string / bool</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
@@ -7312,7 +7308,7 @@
       </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>{"handshake_secret":"…"}</t>
+          <t>{"site_url":"https://brand.com"}</t>
         </is>
       </c>
       <c r="J125" s="7" t="inlineStr">
@@ -7320,58 +7316,74 @@
           <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
         </is>
       </c>
-      <c r="K125" s="7" t="inlineStr">
-        <is>
-          <t>Только запись: наружу возвращаются лишь флаги «задан/не задан»</t>
-        </is>
-      </c>
+      <c r="K125" s="7" t="inlineStr"/>
       <c r="L125" s="7" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr">
         <is>
+          <t>Публичная конфигурация продукта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>PUT /admin/products/{id}/secrets</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F126" s="8" t="inlineStr">
+        <is>
+          <t>openai_key_primary, openai_key_fallback, handshake_secret, telegram_bot_token, player_api_key, turnstile_secret</t>
+        </is>
+      </c>
+      <c r="G126" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I126" s="8" t="inlineStr">
+        <is>
+          <t>{"handshake_secret":"…"}</t>
+        </is>
+      </c>
+      <c r="J126" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K126" s="7" t="inlineStr">
+        <is>
+          <t>Только запись: наружу возвращаются лишь флаги «задан/не задан»</t>
+        </is>
+      </c>
+      <c r="L126" s="7" t="inlineStr"/>
+      <c r="M126" s="7" t="inlineStr">
+        <is>
           <t>Секреты продукта. Хранятся зашифрованными; через API не читаются.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>POST /admin/products/{id}/widget-key</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F126" s="5" t="inlineStr"/>
-      <c r="G126" s="5" t="inlineStr"/>
-      <c r="H126" s="4" t="inlineStr"/>
-      <c r="I126" s="5" t="inlineStr"/>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K126" s="4" t="inlineStr"/>
-      <c r="L126" s="4" t="inlineStr"/>
-      <c r="M126" s="4" t="inlineStr">
-        <is>
-          <t>Ротация публичного ключа виджета.</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7395,7 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/overview, /timeseries, /by-topic, /by-language</t>
+          <t>POST /admin/products/{id}/widget-key</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -7391,9 +7403,9 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D127" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -7410,15 +7422,11 @@
           <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
         </is>
       </c>
-      <c r="K127" s="4" t="inlineStr">
-        <is>
-          <t>Параметры периода from/to, скоуп product_id</t>
-        </is>
-      </c>
+      <c r="K127" s="4" t="inlineStr"/>
       <c r="L127" s="4" t="inlineStr"/>
       <c r="M127" s="4" t="inlineStr">
         <is>
-          <t>Метрики поддержки для выгрузки во внешнюю аналитику.</t>
+          <t>Ротация публичного ключа виджета.</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7438,7 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/ai-costs</t>
+          <t>GET /admin/overview, /timeseries, /by-topic, /by-language</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -7459,13 +7467,13 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>Разрез по типу вызова: chat | agent | review | media</t>
+          <t>Параметры периода from/to, скоуп product_id</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr"/>
       <c r="M128" s="4" t="inlineStr">
         <is>
-          <t>Полные траты на ИИ — сумма сходится со счётом провайдера.</t>
+          <t>Метрики поддержки для выгрузки во внешнюю аналитику.</t>
         </is>
       </c>
     </row>
@@ -7477,7 +7485,7 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/sessions, /admin/session/{id}</t>
+          <t>GET /admin/ai-costs</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -7506,13 +7514,13 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>Пагинация page/page_size</t>
+          <t>Разрез по типу вызова: chat | agent | review | media</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr"/>
       <c r="M129" s="4" t="inlineStr">
         <is>
-          <t>Журнал диалогов и полная стенограмма с постоимостью — выгрузка в общее хранилище обращений.</t>
+          <t>Полные траты на ИИ — сумма сходится со счётом провайдера.</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7532,7 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/audit</t>
+          <t>GET /admin/sessions, /admin/session/{id}</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -7551,11 +7559,15 @@
           <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
         </is>
       </c>
-      <c r="K130" s="4" t="inlineStr"/>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>Пагинация page/page_size</t>
+        </is>
+      </c>
       <c r="L130" s="4" t="inlineStr"/>
       <c r="M130" s="4" t="inlineStr">
         <is>
-          <t>Аудит административных изменений — для общего SIEM/комплаенс-контура.</t>
+          <t>Журнал диалогов и полная стенограмма с постоимостью — выгрузка в общее хранилище обращений.</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7579,7 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/quality/overview, /admin/quality/reviews</t>
+          <t>GET /admin/audit</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -7598,7 +7610,7 @@
       <c r="L131" s="4" t="inlineStr"/>
       <c r="M131" s="4" t="inlineStr">
         <is>
-          <t>Оценки качества диалогов (1..5, теги, пробелы в базе знаний).</t>
+          <t>Аудит административных изменений — для общего SIEM/комплаенс-контура.</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7622,7 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/retention/overview, /funnel, /effectiveness</t>
+          <t>GET /admin/quality/overview, /admin/quality/reviews</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -7641,7 +7653,7 @@
       <c r="L132" s="4" t="inlineStr"/>
       <c r="M132" s="4" t="inlineStr">
         <is>
-          <t>Метрики Telegram-фасада: воронка и результативность касаний.</t>
+          <t>Оценки качества диалогов (1..5, теги, пробелы в базе знаний).</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7665,7 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>POST /admin/api-keys</t>
+          <t>GET /admin/retention/overview, /funnel, /effectiveness</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -7661,9 +7673,9 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -7677,22 +7689,14 @@
       <c r="I133" s="5" t="inlineStr"/>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>только человек-админ (ключом ключ не выпустить)</t>
-        </is>
-      </c>
-      <c r="K133" s="4" t="inlineStr">
-        <is>
-          <t>Открытый текст ключа возвращается РОВНО ОДИН РАЗ; хранится только хеш</t>
-        </is>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>401 · 403</t>
-        </is>
-      </c>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K133" s="4" t="inlineStr"/>
+      <c r="L133" s="4" t="inlineStr"/>
       <c r="M133" s="4" t="inlineStr">
         <is>
-          <t>Выпуск сервисного ключа sak_… для внешней системы.</t>
+          <t>Метрики Telegram-фасада: воронка и результативность касаний.</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7708,7 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/mcp/manifest</t>
+          <t>POST /admin/api-keys</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -7712,9 +7716,9 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D134" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -7728,14 +7732,22 @@
       <c r="I134" s="5" t="inlineStr"/>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K134" s="4" t="inlineStr"/>
-      <c r="L134" s="4" t="inlineStr"/>
+          <t>только человек-админ (ключом ключ не выпустить)</t>
+        </is>
+      </c>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>Открытый текст ключа возвращается РОВНО ОДИН РАЗ; хранится только хеш</t>
+        </is>
+      </c>
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>401 · 403</t>
+        </is>
+      </c>
       <c r="M134" s="4" t="inlineStr">
         <is>
-          <t>Машиночитаемое описание админ-инструментов (MCP) для агентских клиентов.</t>
+          <t>Выпуск сервисного ключа sak_… для внешней системы.</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7759,7 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>GET /openapi.json, /docs, /redoc</t>
+          <t>GET /admin/mcp/manifest</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -7771,34 +7783,26 @@
       <c r="I135" s="5" t="inlineStr"/>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>нет (публичный)</t>
-        </is>
-      </c>
-      <c r="K135" s="4" t="inlineStr">
-        <is>
-          <t>Отдаётся только если включено на деплое</t>
-        </is>
-      </c>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>404, когда выключено</t>
-        </is>
-      </c>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K135" s="4" t="inlineStr"/>
+      <c r="L135" s="4" t="inlineStr"/>
       <c r="M135" s="4" t="inlineStr">
         <is>
-          <t>Машиночитаемая схема всего API — для генерации клиентов.</t>
+          <t>Машиночитаемое описание админ-инструментов (MCP) для агентских клиентов.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>Исходящие</t>
+          <t>Admin API</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
+          <t>GET /openapi.json, /docs, /redoc</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -7813,7 +7817,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Внешняя админка</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr"/>
@@ -7822,77 +7826,73 @@
       <c r="I136" s="5" t="inlineStr"/>
       <c r="J136" s="4" t="inlineStr">
         <is>
+          <t>нет (публичный)</t>
+        </is>
+      </c>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>Отдаётся только если включено на деплое</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>404, когда выключено</t>
+        </is>
+      </c>
+      <c r="M136" s="4" t="inlineStr">
+        <is>
+          <t>Машиночитаемая схема всего API — для генерации клиентов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr"/>
+      <c r="G137" s="5" t="inlineStr"/>
+      <c r="H137" s="4" t="inlineStr"/>
+      <c r="I137" s="5" t="inlineStr"/>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
           <t>Bearer &lt;player_api_key продукта&gt;</t>
         </is>
       </c>
-      <c r="K136" s="4" t="inlineStr">
+      <c r="K137" s="4" t="inlineStr">
         <is>
           <t>Таймаут 8 с · срабатывает, когда снапшот старше часа · только публичные адреса (защита от SSRF, пиннинг IP)</t>
         </is>
       </c>
-      <c r="L136" s="4" t="inlineStr">
+      <c r="L137" s="4" t="inlineStr">
         <is>
           <t>Любая ошибка тиха: остаётся прежний снапшот</t>
         </is>
       </c>
-      <c r="M136" s="4" t="inlineStr">
+      <c r="M137" s="4" t="inlineStr">
         <is>
           <t>ЛЕНИВОЕ обновление профиля игрока перед ходом бота. Эндпойнт реализует ПАРТНЁР — это требование к чужой системе.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t>Исходящие</t>
-        </is>
-      </c>
-      <c r="B137" s="8" t="inlineStr">
-        <is>
-          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
-        </is>
-      </c>
-      <c r="C137" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D137" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="inlineStr">
-        <is>
-          <t>Наш сервис</t>
-        </is>
-      </c>
-      <c r="F137" s="8" t="inlineStr">
-        <is>
-          <t>player_id</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr">
-        <is>
-          <t>query string</t>
-        </is>
-      </c>
-      <c r="H137" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I137" s="8" t="inlineStr">
-        <is>
-          <t>1048576</t>
-        </is>
-      </c>
-      <c r="J137" s="7" t="inlineStr"/>
-      <c r="K137" s="7" t="inlineStr"/>
-      <c r="L137" s="7" t="inlineStr"/>
-      <c r="M137" s="7" t="inlineStr">
-        <is>
-          <t>Кого запрашиваем.</t>
         </is>
       </c>
     </row>
@@ -7909,37 +7909,37 @@
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D138" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F138" s="8" t="inlineStr">
         <is>
-          <t>full_name, email, activation_status, country, balance, vip_level, registration_date, last_login_at, last_played_at, last_deposit_at</t>
+          <t>player_id</t>
         </is>
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>JSON-объект</t>
+          <t>query string</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
-          <t>{"full_name":"Андрей","balance":"150.00 USDT"}</t>
+          <t>1048576</t>
         </is>
       </c>
       <c r="J138" s="7" t="inlineStr"/>
@@ -7947,54 +7947,62 @@
       <c r="L138" s="7" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr">
         <is>
+          <t>Кого запрашиваем.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t>full_name, email, activation_status, country, balance, vip_level, registration_date, last_login_at, last_played_at, last_deposit_at</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>JSON-объект</t>
+        </is>
+      </c>
+      <c r="H139" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I139" s="8" t="inlineStr">
+        <is>
+          <t>{"full_name":"Андрей","balance":"150.00 USDT"}</t>
+        </is>
+      </c>
+      <c r="J139" s="7" t="inlineStr"/>
+      <c r="K139" s="7" t="inlineStr"/>
+      <c r="L139" s="7" t="inlineStr"/>
+      <c r="M139" s="7" t="inlineStr">
+        <is>
           <t>Ожидаемый ответ партнёра. Лишние поля игнорируются — берётся тот же белый список, что и везде.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>Исходящие</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>Telegram Bot API</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D139" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>Наш сервис</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="inlineStr"/>
-      <c r="G139" s="5" t="inlineStr"/>
-      <c r="H139" s="4" t="inlineStr"/>
-      <c r="I139" s="5" t="inlineStr"/>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>токен бота продукта (хранится зашифрованным)</t>
-        </is>
-      </c>
-      <c r="K139" s="4" t="inlineStr">
-        <is>
-          <t>Ретраи; недоступный игрок помечается как unreachable</t>
-        </is>
-      </c>
-      <c r="L139" s="4" t="inlineStr"/>
-      <c r="M139" s="4" t="inlineStr">
-        <is>
-          <t>sendMessage / sendPhoto / sendVideo / getChatMember / setWebhook.</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8014,7 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>OpenAI API</t>
+          <t>Telegram Bot API</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -8030,30 +8038,77 @@
       <c r="I140" s="5" t="inlineStr"/>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>ключ продукта (1–2 шт.), иначе ключ деплоя</t>
+          <t>токен бота продукта (хранится зашифрованным)</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>Два ключа с автопереключением; предохранитель при сбое провайдера; таймауты по назначению вызова</t>
+          <t>Ретраи; недоступный игрок помечается как unreachable</t>
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr"/>
       <c r="M140" s="4" t="inlineStr">
         <is>
+          <t>sendMessage / sendPhoto / sendVideo / getChatMember / setWebhook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>OpenAI API</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D141" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr"/>
+      <c r="G141" s="5" t="inlineStr"/>
+      <c r="H141" s="4" t="inlineStr"/>
+      <c r="I141" s="5" t="inlineStr"/>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>ключ продукта (1–2 шт.), иначе ключ деплоя</t>
+        </is>
+      </c>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>Два ключа с автопереключением; предохранитель при сбое провайдера; таймауты по назначению вызова</t>
+        </is>
+      </c>
+      <c r="L141" s="4" t="inlineStr"/>
+      <c r="M141" s="4" t="inlineStr">
+        <is>
           <t>Генерация ответов и фоновые проходы. Каждый вызов логируется с атрибуцией расходов.</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Файл генерируется из кода: scripts/build_api_reference.py. Живая версия — /integration-reference на самом сервисе.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M140"/>
+  <autoFilter ref="A4:M141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/frontend/api-reference.xlsx
+++ b/frontend/api-reference.xlsx
@@ -2498,7 +2498,7 @@
       <c r="L39" s="7" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>Мягкий лимит сообщений достигнут: показать предупреждение и две кнопки — эскалация (POST /escalate) сверху и завершение (POST /resolve) ниже — вместо suggestions/resolved. Чат остаётся открытым; на 2x лимита сессия закрывается принудительно.</t>
+          <t>Мягкий лимит сообщений достигнут (или resolved на последних ~2 ходах перед ним): показать предупреждение и две кнопки — эскалация (POST /escalate) сверху и завершение (POST /resolve) ниже — вместо suggestions/resolved. Чат остаётся открытым; на 2x лимита сессия закрывается принудительно.</t>
         </is>
       </c>
     </row>

--- a/frontend/api-reference.xlsx
+++ b/frontend/api-reference.xlsx
@@ -10,7 +10,7 @@
     <sheet name="API" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API'!$A$4:$M$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API'!$A$4:$M$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:M143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2448,108 +2448,108 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Chat API</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/chat/message</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>cap_notice</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>{message,escalate_label,finish_label}|null</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>{"message":"…","escalate_label":"Передать вопрос человеку","finish_label":"Завершить чат"}</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>Мягкий лимит сообщений достигнут (или resolved на последних ~2 ходах перед ним): показать предупреждение и две кнопки — эскалация (POST /escalate) сверху и завершение (POST /resolve) ниже — вместо suggestions/resolved. Чат остаётся открытым; на 2x лимита сессия закрывается принудительно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Chat API</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>GET /api/chat/session/{id}</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>Выход</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Клиент чата</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>Bearer &lt;session token&gt; (JWT HS256)</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>Бюджет chat-op:{ip} (300)</t>
         </is>
       </c>
-      <c r="L39" s="4" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>401 · 404 · 429</t>
         </is>
       </c>
-      <c r="M39" s="4" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>Возобновление диалога: статус и до 50 последних сообщений.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Chat API</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>GET /api/chat/session/{id}</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>Наш сервис</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>'open'|'resolved'|'escalated'</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr"/>
-      <c r="L40" s="7" t="inlineStr"/>
-      <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t>Только open допускает новые ходы; иначе 409.</t>
         </is>
       </c>
     </row>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>history</t>
+          <t>status</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>[{role,content,lang}]</t>
+          <t>'open'|'resolved'|'escalated'</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>[{"role":"user","content":"…"}]</t>
+          <t>open</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr"/>
@@ -2604,58 +2604,62 @@
       <c r="L41" s="7" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr">
         <is>
+          <t>Только open допускает новые ходы; иначе 409.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Chat API</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/chat/session/{id}</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>[{role,content,lang}]</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>[{"role":"user","content":"…"}]</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr"/>
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr">
+        <is>
           <t>role ∈ user|assistant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Chat API</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>POST /api/chat/escalate</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>Клиент чата</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;session token&gt; (JWT HS256)</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>Бюджет chat-op:{ip} (300)</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>401 · 404 · 409 · 429</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
-        <is>
-          <t>Явный запрос человека: жёсткая эскалация, сессия закрывается.</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2671,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>POST /api/chat/resolve</t>
+          <t>POST /api/chat/escalate</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2675,9 +2679,9 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -2696,76 +2700,68 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
+          <t>Бюджет chat-op:{ip} (300)</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>401 · 404 · 409 · 429</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>Явный запрос человека: жёсткая эскалация, сессия закрывается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Chat API</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>POST /api/chat/resolve</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Клиент чата</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;session token&gt; (JWT HS256)</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
           <t>Идемпотентно; не перекрывает уже эскалированную сессию</t>
         </is>
       </c>
-      <c r="L43" s="4" t="inlineStr">
+      <c r="L44" s="4" t="inlineStr">
         <is>
           <t>401 · 404 · 429</t>
         </is>
       </c>
-      <c r="M43" s="4" t="inlineStr">
+      <c r="M44" s="4" t="inlineStr">
         <is>
           <t>Игрок завершил чат.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Chat API</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Контракт: user_context / signed_context</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>Сайт / виджет</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>1048576</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>подпись HMAC-SHA256 секретом продукта</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr"/>
-      <c r="L44" s="7" t="inlineStr"/>
-      <c r="M44" s="7" t="inlineStr">
-        <is>
-          <t>Идентификатор игрока в казино. Белый список полей, которые видит модель. Всё остальное отбрасывается — расширение списка требует правки на нашей стороне.</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2793,7 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -2812,7 +2808,7 @@
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>Андрей Петров</t>
+          <t>1048576</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
@@ -2824,7 +2820,7 @@
       <c r="L45" s="7" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>Полное имя; из него берётся имя для приветствия.</t>
+          <t>Идентификатор игрока в казино. Белый список полей, которые видит модель. Всё остальное отбрасывается — расширение списка требует правки на нашей стороне.</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2852,7 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
@@ -2871,7 +2867,7 @@
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>player@example.com</t>
+          <t>Андрей Петров</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
@@ -2883,7 +2879,7 @@
       <c r="L46" s="7" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>Почта игрока.</t>
+          <t>Полное имя; из него берётся имя для приветствия.</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2911,7 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>activation_status</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -2930,7 +2926,7 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>player@example.com</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
@@ -2942,7 +2938,7 @@
       <c r="L47" s="7" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>Статус активации/верификации.</t>
+          <t>Почта игрока.</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2970,7 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>activation_status</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -2989,7 +2985,7 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
@@ -3001,7 +2997,7 @@
       <c r="L48" s="7" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr">
         <is>
-          <t>Страна.</t>
+          <t>Статус активации/верификации.</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3029,7 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>country</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -3048,7 +3044,7 @@
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>150.00 USDT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
@@ -3060,7 +3056,7 @@
       <c r="L49" s="7" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>Баланс строкой, вместе с валютой.</t>
+          <t>Страна.</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3088,7 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>vip_level</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
@@ -3107,7 +3103,7 @@
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>150.00 USDT</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
@@ -3119,7 +3115,7 @@
       <c r="L50" s="7" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>VIP-класс.</t>
+          <t>Баланс строкой, вместе с валютой.</t>
         </is>
       </c>
     </row>
@@ -3151,12 +3147,12 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>registration_date</t>
+          <t>vip_level</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>string (ISO-8601)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
@@ -3166,7 +3162,7 @@
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
@@ -3178,7 +3174,7 @@
       <c r="L51" s="7" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>Дата регистрации.</t>
+          <t>VIP-класс.</t>
         </is>
       </c>
     </row>
@@ -3210,38 +3206,34 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>iat</t>
+          <t>registration_date</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>int (unix seconds)</t>
+          <t>string (ISO-8601)</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>условно</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>1769606400</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>часть подписанного payload</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="inlineStr">
-        <is>
-          <t>Возраст токена ограничен 300 с</t>
-        </is>
-      </c>
+          <t>подпись HMAC-SHA256 секретом продукта</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr"/>
       <c r="L52" s="7" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>Момент выпуска подписи (антиреплей).</t>
+          <t>Дата регистрации.</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3265,7 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>exp</t>
+          <t>iat</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -3283,12 +3275,12 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>условно</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>1769606700</t>
+          <t>1769606400</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
@@ -3296,15 +3288,15 @@
           <t>часть подписанного payload</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>401 bad_handshake при истечении</t>
-        </is>
-      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>Возраст токена ограничен 300 с</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>Срок годности подписи.</t>
+          <t>Момент выпуска подписи (антиреплей).</t>
         </is>
       </c>
     </row>
@@ -3316,32 +3308,32 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Контракт: escalation</t>
+          <t>Контракт: user_context / signed_context</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Сайт / виджет</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>exp</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int (unix seconds)</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
@@ -3351,15 +3343,23 @@
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="J54" s="7" t="inlineStr"/>
+          <t>1769606700</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>часть подписанного payload</t>
+        </is>
+      </c>
       <c r="K54" s="7" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr"/>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>401 bad_handshake при истечении</t>
+        </is>
+      </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>Есть ли в этом ходе передача на человека.</t>
+          <t>Срок годности подписи.</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>final</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -3414,7 +3414,7 @@
       <c r="L55" s="7" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>true — сессия закрыта (дальше 409); false — карточка показана, диалог продолжается.</t>
+          <t>Есть ли в этом ходе передача на человека.</t>
         </is>
       </c>
     </row>
@@ -3446,22 +3446,22 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>final</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>условно</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>Передаю вас специалисту…</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr"/>
@@ -3469,7 +3469,7 @@
       <c r="L56" s="7" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>Текст карточки на языке ответа.</t>
+          <t>true — сессия закрыта (дальше 409); false — карточка показана, диалог продолжается.</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>button.label</t>
+          <t>message</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>Написать в поддержку</t>
+          <t>Передаю вас специалисту…</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr"/>
@@ -3524,7 +3524,7 @@
       <c r="L57" s="7" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>Подпись кнопки.</t>
+          <t>Текст карточки на языке ответа.</t>
         </is>
       </c>
     </row>
@@ -3556,12 +3556,12 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>button.url</t>
+          <t>button.label</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>string (URL)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>https://t.me/brand_bot?start=…</t>
+          <t>Написать в поддержку</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr"/>
@@ -3579,7 +3579,7 @@
       <c r="L58" s="7" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>Куда ведёт кнопка: статическая ссылка контакта или одноразовый диплинк в Telegram-бота.</t>
+          <t>Подпись кнопки.</t>
         </is>
       </c>
     </row>
@@ -3611,22 +3611,22 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>retention</t>
+          <t>button.url</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string (URL)</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>условно</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>https://t.me/brand_bot?start=…</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr"/>
@@ -3634,117 +3634,113 @@
       <c r="L59" s="7" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr">
         <is>
+          <t>Куда ведёт кнопка: статическая ссылка контакта или одноразовый диплинк в Telegram-бота.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Chat API</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Контракт: escalation</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>retention</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="inlineStr"/>
+      <c r="K60" s="7" t="inlineStr"/>
+      <c r="L60" s="7" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr">
+        <is>
           <t>Признак, что передача ведёт в Telegram-бота, а не на статическую ссылку.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Partner API</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>POST /partner/{product_id}/player-update</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>CRM казино</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr"/>
-      <c r="G60" s="5" t="inlineStr"/>
-      <c r="H60" s="4" t="inlineStr"/>
-      <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>Bearer &lt;handshake_secret продукта&gt;</t>
         </is>
       </c>
-      <c r="K60" s="4" t="inlineStr">
+      <c r="K61" s="4" t="inlineStr">
         <is>
           <t>Частичное обновление: поля со значением null не затираются · лимит partner:{ip}</t>
         </is>
       </c>
-      <c r="L60" s="4" t="inlineStr">
+      <c r="L61" s="4" t="inlineStr">
         <is>
           <t>401 unauthorized (единый ответ на все причины) · 429 rate_limited</t>
         </is>
       </c>
-      <c r="M60" s="4" t="inlineStr">
+      <c r="M61" s="4" t="inlineStr">
         <is>
           <t>Push профиля игрока из CRM в наш снапшот.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>Partner API</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>POST /partner/{product_id}/player-update</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>Заголовок</t>
-        </is>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>CRM казино</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>Authorization</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret&gt;</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I61" s="8" t="inlineStr">
-        <is>
-          <t>Bearer 8f2c…</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr"/>
-      <c r="L61" s="7" t="inlineStr"/>
-      <c r="M61" s="7" t="inlineStr">
-        <is>
-          <t>Тот же секрет продукта, что подписывает handshake.</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3757,7 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Заголовок</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -3776,12 +3772,12 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>player_id</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Bearer &lt;handshake_secret&gt;</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -3791,15 +3787,19 @@
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>1048576</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="inlineStr"/>
+          <t>Bearer 8f2c…</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
       <c r="K62" s="7" t="inlineStr"/>
       <c r="L62" s="7" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>Ключ игрока на стороне казино.</t>
+          <t>Тот же секрет продукта, что подписывает handshake.</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>player_id</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>Андрей Петров</t>
+          <t>1048576</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr"/>
@@ -3854,7 +3854,7 @@
       <c r="L63" s="7" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>Поле профиля. null = не менять.</t>
+          <t>Ключ игрока на стороне казино.</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>player@example.com</t>
+          <t>Андрей Петров</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>activation_status</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>player@example.com</t>
         </is>
       </c>
       <c r="J65" s="7" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>activation_status</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="J66" s="7" t="inlineStr"/>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>country</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>150.00 USDT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr"/>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>vip_level</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>150.00 USDT</t>
         </is>
       </c>
       <c r="J68" s="7" t="inlineStr"/>
@@ -4161,12 +4161,12 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>registration_date</t>
+          <t>vip_level</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>string (ISO-8601)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>last_login_at</t>
+          <t>registration_date</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28T10:15:00Z</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
       <c r="L70" s="7" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>Последний вход — сигнал активности.</t>
+          <t>Поле профиля. null = не менять.</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>last_played_at</t>
+          <t>last_login_at</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
@@ -4294,7 +4294,7 @@
       <c r="L71" s="7" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>Последняя игра.</t>
+          <t>Последний вход — сигнал активности.</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>last_deposit_at</t>
+          <t>last_played_at</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
@@ -4349,7 +4349,7 @@
       <c r="L72" s="7" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>Последний депозит.</t>
+          <t>Последняя игра.</t>
         </is>
       </c>
     </row>
@@ -4366,37 +4366,37 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D73" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>ok / updated</t>
+          <t>last_deposit_at</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>bool / bool</t>
+          <t>string (ISO-8601)</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>{"ok":true,"updated":true}</t>
+          <t>2026-07-28T10:15:00Z</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr"/>
@@ -4404,113 +4404,113 @@
       <c r="L73" s="7" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr">
         <is>
+          <t>Последний депозит.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>Partner API</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/player-update</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>ok / updated</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>bool / bool</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>{"ok":true,"updated":true}</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr"/>
+      <c r="K74" s="7" t="inlineStr"/>
+      <c r="L74" s="7" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr">
+        <is>
           <t>Признак приёма и факта изменения.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>Partner API</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>CRM казино</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr"/>
-      <c r="G74" s="5" t="inlineStr"/>
-      <c r="H74" s="4" t="inlineStr"/>
-      <c r="I74" s="5" t="inlineStr"/>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr"/>
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" s="5" t="inlineStr"/>
+      <c r="J75" s="4" t="inlineStr">
         <is>
           <t>Bearer &lt;handshake_secret продукта&gt;</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr">
+      <c r="K75" s="4" t="inlineStr">
         <is>
           <t>Идемпотентно по event_id (доставка at-least-once безопасна) · пакет до 500 событий · payload до 8 KiB · лимит partner:{ip}</t>
         </is>
       </c>
-      <c r="L74" s="4" t="inlineStr">
+      <c r="L75" s="4" t="inlineStr">
         <is>
           <t>401 · 413 batch_too_large · 422 invalid_event · 429</t>
         </is>
       </c>
-      <c r="M74" s="4" t="inlineStr">
+      <c r="M75" s="4" t="inlineStr">
         <is>
           <t>Канонический поток событий казино: кормит проактивного агента и обновляет сигналы активности игрока.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>Partner API</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>POST /partner/{product_id}/event</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>CRM казино</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>event_id</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>string (≤64)</t>
-        </is>
-      </c>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>evt_2026072801</t>
-        </is>
-      </c>
-      <c r="J75" s="7" t="inlineStr"/>
-      <c r="K75" s="7" t="inlineStr"/>
-      <c r="L75" s="7" t="inlineStr"/>
-      <c r="M75" s="7" t="inlineStr">
-        <is>
-          <t>Ключ идемпотентности. Повтор считается дубликатом, а не ошибкой.</t>
         </is>
       </c>
     </row>
@@ -4542,12 +4542,12 @@
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>event_name</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>string (из таксономии)</t>
+          <t>string (≤64)</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
@@ -4557,19 +4557,15 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>deposit_confirmed</t>
+          <t>evt_2026072801</t>
         </is>
       </c>
       <c r="J76" s="7" t="inlineStr"/>
       <c r="K76" s="7" t="inlineStr"/>
-      <c r="L76" s="7" t="inlineStr">
-        <is>
-          <t>422 invalid_event на неизвестное имя</t>
-        </is>
-      </c>
+      <c r="L76" s="7" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr">
         <is>
-          <t>Имя события. Таксономия — контракт, а не рекомендация; список ниже.</t>
+          <t>Ключ идемпотентности. Повтор считается дубликатом, а не ошибкой.</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4597,12 @@
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>player_id | user_id</t>
+          <t>event_name</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string (из таксономии)</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
@@ -4616,15 +4612,19 @@
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>1048576</t>
+          <t>deposit_confirmed</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr"/>
       <c r="K77" s="7" t="inlineStr"/>
-      <c r="L77" s="7" t="inlineStr"/>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>422 invalid_event на неизвестное имя</t>
+        </is>
+      </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>Игрок, к которому относится событие.</t>
+          <t>Имя события. Таксономия — контракт, а не рекомендация; список ниже.</t>
         </is>
       </c>
     </row>
@@ -4656,22 +4656,22 @@
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>tg_user_id</t>
+          <t>player_id | user_id</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>584210394</t>
+          <t>1048576</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr"/>
@@ -4679,7 +4679,7 @@
       <c r="L78" s="7" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr">
         <is>
-          <t>Явный получатель, когда один player_id связан с несколькими Telegram-аккаунтами.</t>
+          <t>Игрок, к которому относится событие.</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>tg_user_id</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>string (ISO-8601)</t>
+          <t>int</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28T10:15:00Z</t>
+          <t>584210394</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr"/>
@@ -4734,7 +4734,7 @@
       <c r="L79" s="7" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>Время события. Значение из будущего приводится к текущему моменту.</t>
+          <t>Явный получатель, когда один player_id связан с несколькими Telegram-аккаунтами.</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>event_version</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string (ISO-8601)</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2026-07-28T10:15:00Z</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr"/>
@@ -4789,7 +4789,7 @@
       <c r="L80" s="7" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr">
         <is>
-          <t>Версия схемы события на стороне отправителя.</t>
+          <t>Время события. Значение из будущего приводится к текущему моменту.</t>
         </is>
       </c>
     </row>
@@ -4821,12 +4821,12 @@
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>payload</t>
+          <t>event_version</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>object (≤8 KiB)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>{"amount":"50.00","currency":"USDT"}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J81" s="7" t="inlineStr"/>
@@ -4844,7 +4844,7 @@
       <c r="L81" s="7" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr">
         <is>
-          <t>Детали события; может нести и поля профиля — они обновят снапшот.</t>
+          <t>Версия схемы события на стороне отправителя.</t>
         </is>
       </c>
     </row>
@@ -4876,12 +4876,12 @@
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>events</t>
+          <t>payload</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>[object] (≤500)</t>
+          <t>object (≤8 KiB)</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>[{"event_id":"…","event_name":"…"}]</t>
+          <t>{"amount":"50.00","currency":"USDT"}</t>
         </is>
       </c>
       <c r="J82" s="7" t="inlineStr"/>
@@ -4899,7 +4899,7 @@
       <c r="L82" s="7" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr">
         <is>
-          <t>Пакетная форма. Взаимоисключима с плоскими полями выше.</t>
+          <t>Детали события; может нести и поля профиля — они обновят снапшот.</t>
         </is>
       </c>
     </row>
@@ -4916,37 +4916,37 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>stored / duplicates / invalid</t>
+          <t>events</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>int|bool</t>
+          <t>[object] (≤500)</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>{"ok":true,"stored":12,"duplicates":3}</t>
+          <t>[{"event_id":"…","event_name":"…"}]</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr"/>
@@ -4954,7 +4954,7 @@
       <c r="L83" s="7" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>Итог приёма: сколько принято, сколько дублей, сколько отвергнуто.</t>
+          <t>Пакетная форма. Взаимоисключима с плоскими полями выше.</t>
         </is>
       </c>
     </row>
@@ -4971,49 +4971,45 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>session_started</t>
+          <t>stored / duplicates / invalid</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>event_name · Сессия</t>
-        </is>
-      </c>
-      <c r="H84" s="7" t="inlineStr"/>
+          <t>int|bool</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"session_started"}</t>
-        </is>
-      </c>
-      <c r="J84" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K84" s="7" t="inlineStr">
-        <is>
-          <t>обновляет last_login_at</t>
-        </is>
-      </c>
+          <t>{"ok":true,"stored":12,"duplicates":3}</t>
+        </is>
+      </c>
+      <c r="J84" s="7" t="inlineStr"/>
+      <c r="K84" s="7" t="inlineStr"/>
       <c r="L84" s="7" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr">
         <is>
-          <t>Игрок начал сессию на сайте или в приложении.</t>
+          <t>Итог приёма: сколько принято, сколько дублей, сколько отвергнуто.</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5041,7 @@
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>session_ended</t>
+          <t>session_started</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
@@ -5056,7 +5052,7 @@
       <c r="H85" s="7" t="inlineStr"/>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"session_ended"}</t>
+          <t>{"event_name":"session_started"}</t>
         </is>
       </c>
       <c r="J85" s="7" t="inlineStr">
@@ -5072,7 +5068,7 @@
       <c r="L85" s="7" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>Игрок завершил сессию.</t>
+          <t>Игрок начал сессию на сайте или в приложении.</t>
         </is>
       </c>
     </row>
@@ -5104,18 +5100,18 @@
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>deposit_initiated</t>
+          <t>session_ended</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>event_name · Платежи</t>
+          <t>event_name · Сессия</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr"/>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"deposit_initiated"}</t>
+          <t>{"event_name":"session_ended"}</t>
         </is>
       </c>
       <c r="J86" s="7" t="inlineStr">
@@ -5125,13 +5121,13 @@
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>обновляет last_login_at</t>
         </is>
       </c>
       <c r="L86" s="7" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr">
         <is>
-          <t>Депозит начат, ещё не подтверждён.</t>
+          <t>Игрок завершил сессию.</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5159,7 @@
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>deposit_confirmed</t>
+          <t>deposit_initiated</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
@@ -5174,7 +5170,7 @@
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"deposit_confirmed"}</t>
+          <t>{"event_name":"deposit_initiated"}</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
@@ -5184,13 +5180,13 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>обновляет last_deposit_at</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>Депозит зачислен — сильнейший позитивный сигнал.</t>
+          <t>Депозит начат, ещё не подтверждён.</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5218,7 @@
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>deposit_failed</t>
+          <t>deposit_confirmed</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
@@ -5233,7 +5229,7 @@
       <c r="H88" s="7" t="inlineStr"/>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"deposit_failed"}</t>
+          <t>{"event_name":"deposit_confirmed"}</t>
         </is>
       </c>
       <c r="J88" s="7" t="inlineStr">
@@ -5243,13 +5239,13 @@
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>обновляет last_deposit_at</t>
         </is>
       </c>
       <c r="L88" s="7" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr">
         <is>
-          <t>Депозит не прошёл.</t>
+          <t>Депозит зачислен — сильнейший позитивный сигнал.</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5277,7 @@
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>withdrawal_settled</t>
+          <t>deposit_failed</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
@@ -5292,7 +5288,7 @@
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"withdrawal_settled"}</t>
+          <t>{"event_name":"deposit_failed"}</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
@@ -5308,7 +5304,7 @@
       <c r="L89" s="7" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>Вывод завершён.</t>
+          <t>Депозит не прошёл.</t>
         </is>
       </c>
     </row>
@@ -5340,18 +5336,18 @@
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>bet_settled</t>
+          <t>withdrawal_settled</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>event_name · Игра</t>
+          <t>event_name · Платежи</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr"/>
       <c r="I90" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bet_settled"}</t>
+          <t>{"event_name":"withdrawal_settled"}</t>
         </is>
       </c>
       <c r="J90" s="7" t="inlineStr">
@@ -5361,13 +5357,13 @@
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
-          <t>обновляет last_played_at</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L90" s="7" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr">
         <is>
-          <t>Ставка рассчитана. Сумма проигрыша за 24 ч влияет на тон коммуникации.</t>
+          <t>Вывод завершён.</t>
         </is>
       </c>
     </row>
@@ -5399,18 +5395,18 @@
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>bonus_granted</t>
+          <t>bet_settled</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>event_name · Бонусы</t>
+          <t>event_name · Игра</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr"/>
       <c r="I91" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_granted"}</t>
+          <t>{"event_name":"bet_settled"}</t>
         </is>
       </c>
       <c r="J91" s="7" t="inlineStr">
@@ -5420,13 +5416,13 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>обновляет last_played_at</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr">
         <is>
-          <t>Бонус начислен.</t>
+          <t>Ставка рассчитана. Сумма проигрыша за 24 ч влияет на тон коммуникации.</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5454,7 @@
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>bonus_claimed</t>
+          <t>bonus_granted</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
@@ -5469,7 +5465,7 @@
       <c r="H92" s="7" t="inlineStr"/>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_claimed"}</t>
+          <t>{"event_name":"bonus_granted"}</t>
         </is>
       </c>
       <c r="J92" s="7" t="inlineStr">
@@ -5485,7 +5481,7 @@
       <c r="L92" s="7" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>Бонус активирован игроком.</t>
+          <t>Бонус начислен.</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5513,7 @@
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>bonus_completed</t>
+          <t>bonus_claimed</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
@@ -5528,7 +5524,7 @@
       <c r="H93" s="7" t="inlineStr"/>
       <c r="I93" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_completed"}</t>
+          <t>{"event_name":"bonus_claimed"}</t>
         </is>
       </c>
       <c r="J93" s="7" t="inlineStr">
@@ -5544,7 +5540,7 @@
       <c r="L93" s="7" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr">
         <is>
-          <t>Отыгрыш завершён.</t>
+          <t>Бонус активирован игроком.</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5572,7 @@
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>bonus_expired</t>
+          <t>bonus_completed</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
@@ -5587,7 +5583,7 @@
       <c r="H94" s="7" t="inlineStr"/>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_expired"}</t>
+          <t>{"event_name":"bonus_completed"}</t>
         </is>
       </c>
       <c r="J94" s="7" t="inlineStr">
@@ -5603,7 +5599,7 @@
       <c r="L94" s="7" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr">
         <is>
-          <t>Бонус сгорел.</t>
+          <t>Отыгрыш завершён.</t>
         </is>
       </c>
     </row>
@@ -5635,18 +5631,18 @@
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>kyc_started</t>
+          <t>bonus_expired</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>event_name · Верификация</t>
+          <t>event_name · Бонусы</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"kyc_started"}</t>
+          <t>{"event_name":"bonus_expired"}</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr">
@@ -5662,7 +5658,7 @@
       <c r="L95" s="7" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>Верификация начата.</t>
+          <t>Бонус сгорел.</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5690,7 @@
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>kyc_approved</t>
+          <t>kyc_started</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
@@ -5705,7 +5701,7 @@
       <c r="H96" s="7" t="inlineStr"/>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"kyc_approved"}</t>
+          <t>{"event_name":"kyc_started"}</t>
         </is>
       </c>
       <c r="J96" s="7" t="inlineStr">
@@ -5721,7 +5717,7 @@
       <c r="L96" s="7" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr">
         <is>
-          <t>Верификация пройдена.</t>
+          <t>Верификация начата.</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5749,7 @@
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>kyc_rejected</t>
+          <t>kyc_approved</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
@@ -5764,7 +5760,7 @@
       <c r="H97" s="7" t="inlineStr"/>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"kyc_rejected"}</t>
+          <t>{"event_name":"kyc_approved"}</t>
         </is>
       </c>
       <c r="J97" s="7" t="inlineStr">
@@ -5780,7 +5776,7 @@
       <c r="L97" s="7" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>Верификация отклонена.</t>
+          <t>Верификация пройдена.</t>
         </is>
       </c>
     </row>
@@ -5812,18 +5808,18 @@
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>xp_granted</t>
+          <t>kyc_rejected</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>event_name · Лояльность</t>
+          <t>event_name · Верификация</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"xp_granted"}</t>
+          <t>{"event_name":"kyc_rejected"}</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr">
@@ -5839,7 +5835,7 @@
       <c r="L98" s="7" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr">
         <is>
-          <t>Начислен опыт.</t>
+          <t>Верификация отклонена.</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5867,7 @@
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>level_up</t>
+          <t>xp_granted</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
@@ -5882,7 +5878,7 @@
       <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"level_up"}</t>
+          <t>{"event_name":"xp_granted"}</t>
         </is>
       </c>
       <c r="J99" s="7" t="inlineStr">
@@ -5898,7 +5894,7 @@
       <c r="L99" s="7" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr">
         <is>
-          <t>Новый уровень.</t>
+          <t>Начислен опыт.</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5926,7 @@
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>class_up</t>
+          <t>level_up</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
@@ -5941,7 +5937,7 @@
       <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"class_up"}</t>
+          <t>{"event_name":"level_up"}</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr">
@@ -5957,7 +5953,7 @@
       <c r="L100" s="7" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr">
         <is>
-          <t>Новый класс / VIP-тир.</t>
+          <t>Новый уровень.</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5985,7 @@
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>downgrade</t>
+          <t>class_up</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -6000,7 +5996,7 @@
       <c r="H101" s="7" t="inlineStr"/>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"downgrade"}</t>
+          <t>{"event_name":"class_up"}</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
@@ -6016,7 +6012,7 @@
       <c r="L101" s="7" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>Понижение класса.</t>
+          <t>Новый класс / VIP-тир.</t>
         </is>
       </c>
     </row>
@@ -6048,18 +6044,18 @@
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>highlights_pack_opened</t>
+          <t>downgrade</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>event_name · Активности</t>
+          <t>event_name · Лояльность</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr"/>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"highlights_pack_opened"}</t>
+          <t>{"event_name":"downgrade"}</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
@@ -6075,7 +6071,7 @@
       <c r="L102" s="7" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr">
         <is>
-          <t>Открыт пак/кейс.</t>
+          <t>Понижение класса.</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6103,7 @@
       </c>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>highlights_pack_completed</t>
+          <t>highlights_pack_opened</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr">
@@ -6118,7 +6114,7 @@
       <c r="H103" s="7" t="inlineStr"/>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"highlights_pack_completed"}</t>
+          <t>{"event_name":"highlights_pack_opened"}</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -6134,7 +6130,7 @@
       <c r="L103" s="7" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr">
         <is>
-          <t>Пак завершён.</t>
+          <t>Открыт пак/кейс.</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6162,7 @@
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>check_in_done</t>
+          <t>highlights_pack_completed</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
@@ -6177,7 +6173,7 @@
       <c r="H104" s="7" t="inlineStr"/>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"check_in_done"}</t>
+          <t>{"event_name":"highlights_pack_completed"}</t>
         </is>
       </c>
       <c r="J104" s="7" t="inlineStr">
@@ -6193,7 +6189,7 @@
       <c r="L104" s="7" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr">
         <is>
-          <t>Ежедневный чек-ин выполнен.</t>
+          <t>Пак завершён.</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6221,7 @@
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>mission_completed</t>
+          <t>check_in_done</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
@@ -6236,7 +6232,7 @@
       <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"mission_completed"}</t>
+          <t>{"event_name":"check_in_done"}</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
@@ -6252,113 +6248,117 @@
       <c r="L105" s="7" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr">
         <is>
+          <t>Ежедневный чек-ин выполнен.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>Partner API</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/event</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>Событие</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>mission_completed</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>event_name · Активности</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="inlineStr"/>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>{"event_name":"mission_completed"}</t>
+        </is>
+      </c>
+      <c r="J106" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K106" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L106" s="7" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr">
+        <is>
           <t>Миссия или квест завершён.</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t>Telegram</t>
         </is>
       </c>
-      <c r="B106" s="5" t="inlineStr">
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>POST /api/retention/deeplink</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>Вход/Выход</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
+      <c r="E107" s="4" t="inlineStr">
         <is>
           <t>Сайт / виджет</t>
         </is>
       </c>
-      <c r="F106" s="5" t="inlineStr"/>
-      <c r="G106" s="5" t="inlineStr"/>
-      <c r="H106" s="4" t="inlineStr"/>
-      <c r="I106" s="5" t="inlineStr"/>
-      <c r="J106" s="4" t="inlineStr">
+      <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="4" t="inlineStr"/>
+      <c r="I107" s="5" t="inlineStr"/>
+      <c r="J107" s="4" t="inlineStr">
         <is>
           <t>нет (публичный) + лимит по IP</t>
         </is>
       </c>
-      <c r="K106" s="4" t="inlineStr">
+      <c r="K107" s="4" t="inlineStr">
         <is>
           <t>Нонс одноразовый, живёт 120 с (настраивается)</t>
         </is>
       </c>
-      <c r="L106" s="4" t="inlineStr">
+      <c r="L107" s="4" t="inlineStr">
         <is>
           <t>403 bad_widget_key | retention_disabled · 409 no_bot · 401 bad_handshake · 429</t>
         </is>
       </c>
-      <c r="M106" s="4" t="inlineStr">
+      <c r="M107" s="4" t="inlineStr">
         <is>
           <t>Сайт получает одноразовую ссылку в Telegram-бота с профилем игрока.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="7" t="inlineStr">
-        <is>
-          <t>Telegram</t>
-        </is>
-      </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>POST /api/retention/deeplink</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D107" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>Сайт / виджет</t>
-        </is>
-      </c>
-      <c r="F107" s="8" t="inlineStr">
-        <is>
-          <t>widget_key</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr">
-        <is>
-          <t>string (wk_…)</t>
-        </is>
-      </c>
-      <c r="H107" s="7" t="inlineStr">
-        <is>
-          <t>условно</t>
-        </is>
-      </c>
-      <c r="I107" s="8" t="inlineStr">
-        <is>
-          <t>wk_7f3a…</t>
-        </is>
-      </c>
-      <c r="J107" s="7" t="inlineStr"/>
-      <c r="K107" s="7" t="inlineStr"/>
-      <c r="L107" s="7" t="inlineStr"/>
-      <c r="M107" s="7" t="inlineStr">
-        <is>
-          <t>Продукт, чей бот открывать.</t>
         </is>
       </c>
     </row>
@@ -6390,12 +6390,12 @@
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
-          <t>signed_context</t>
+          <t>widget_key</t>
         </is>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>string (подпись)</t>
+          <t>string (wk_…)</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>eyJpZCI6…​.QkFTRTY0</t>
+          <t>wk_7f3a…</t>
         </is>
       </c>
       <c r="J108" s="7" t="inlineStr"/>
@@ -6413,7 +6413,7 @@
       <c r="L108" s="7" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr">
         <is>
-          <t>Профиль игрока — те же поля и та же подпись, что в Chat API.</t>
+          <t>Продукт, чей бот открывать.</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>escalation</t>
+          <t>signed_context</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string (подпись)</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>условно</t>
         </is>
       </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>eyJpZCI6…​.QkFTRTY0</t>
         </is>
       </c>
       <c r="J109" s="7" t="inlineStr"/>
@@ -6468,7 +6468,7 @@
       <c r="L109" s="7" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr">
         <is>
-          <t>true — точка входа «к менеджеру».</t>
+          <t>Профиль игрока — те же поля и та же подпись, что в Chat API.</t>
         </is>
       </c>
     </row>
@@ -6500,12 +6500,12 @@
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
-          <t>lang</t>
+          <t>escalation</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>string (код или локаль)</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>ru</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J110" s="7" t="inlineStr"/>
@@ -6523,7 +6523,7 @@
       <c r="L110" s="7" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr">
         <is>
-          <t>Язык, в котором откроется бот.</t>
+          <t>true — точка входа «к менеджеру».</t>
         </is>
       </c>
     </row>
@@ -6540,37 +6540,37 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Сайт / виджет</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>deep_link</t>
+          <t>lang</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>string (URL)</t>
+          <t>string (код или локаль)</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>https://t.me/brand_bot?start=Ax7…</t>
+          <t>ru</t>
         </is>
       </c>
       <c r="J111" s="7" t="inlineStr"/>
@@ -6578,7 +6578,7 @@
       <c r="L111" s="7" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr">
         <is>
-          <t>Ссылка для кнопки. Нонс погашается при первом /start.</t>
+          <t>Язык, в котором откроется бот.</t>
         </is>
       </c>
     </row>
@@ -6610,12 +6610,12 @@
       </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
-          <t>nonce</t>
+          <t>deep_link</t>
         </is>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string (URL)</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>Ax7kQ…</t>
+          <t>https://t.me/brand_bot?start=Ax7…</t>
         </is>
       </c>
       <c r="J112" s="7" t="inlineStr"/>
@@ -6633,113 +6633,113 @@
       <c r="L112" s="7" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr">
         <is>
+          <t>Ссылка для кнопки. Нонс погашается при первом /start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/retention/deeplink</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>nonce</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H113" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>Ax7kQ…</t>
+        </is>
+      </c>
+      <c r="J113" s="7" t="inlineStr"/>
+      <c r="K113" s="7" t="inlineStr"/>
+      <c r="L113" s="7" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr">
+        <is>
           <t>Тот же одноразовый токен отдельным полем.</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
         <is>
           <t>Telegram</t>
         </is>
       </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>POST /telegram/webhook/{secret}</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
         <is>
           <t>Telegram</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr"/>
-      <c r="G113" s="5" t="inlineStr"/>
-      <c r="H113" s="4" t="inlineStr"/>
-      <c r="I113" s="5" t="inlineStr"/>
-      <c r="J113" s="4" t="inlineStr">
+      <c r="F114" s="5" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr"/>
+      <c r="H114" s="4" t="inlineStr"/>
+      <c r="I114" s="5" t="inlineStr"/>
+      <c r="J114" s="4" t="inlineStr">
         <is>
           <t>путь = webhook-токен продукта (роутинг) + заголовок X-Telegram-Bot-Api-Secret-Token</t>
         </is>
       </c>
-      <c r="K113" s="4" t="inlineStr">
+      <c r="K114" s="4" t="inlineStr">
         <is>
           <t>Всегда быстрый 200 (иначе Telegram ретраит); ход ИИ выполняется в фоне</t>
         </is>
       </c>
-      <c r="L113" s="4" t="inlineStr">
+      <c r="L114" s="4" t="inlineStr">
         <is>
           <t>403 bad_secret_token · неизвестный токен пути → тихий 200</t>
         </is>
       </c>
-      <c r="M113" s="4" t="inlineStr">
+      <c r="M114" s="4" t="inlineStr">
         <is>
           <t>Приём апдейтов Telegram — второй фасад над тем же ИИ-ядром.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="7" t="inlineStr">
-        <is>
-          <t>Telegram</t>
-        </is>
-      </c>
-      <c r="B114" s="8" t="inlineStr">
-        <is>
-          <t>POST /telegram/webhook/{secret}</t>
-        </is>
-      </c>
-      <c r="C114" s="7" t="inlineStr">
-        <is>
-          <t>Заголовок</t>
-        </is>
-      </c>
-      <c r="D114" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="inlineStr">
-        <is>
-          <t>Telegram</t>
-        </is>
-      </c>
-      <c r="F114" s="8" t="inlineStr">
-        <is>
-          <t>X-Telegram-Bot-Api-Secret-Token</t>
-        </is>
-      </c>
-      <c r="G114" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H114" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I114" s="8" t="inlineStr">
-        <is>
-          <t>b4c9…</t>
-        </is>
-      </c>
-      <c r="J114" s="7" t="inlineStr"/>
-      <c r="K114" s="7" t="inlineStr"/>
-      <c r="L114" s="7" t="inlineStr"/>
-      <c r="M114" s="7" t="inlineStr">
-        <is>
-          <t>Секрет, заданный при регистрации вебхука. Защищает от подделки апдейтов тем, кто узнал URL.</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Заголовок</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>X-Telegram-Bot-Api-Secret-Token</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>object (Telegram Bot API)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>{"update_id":1,"message":{…}}</t>
+          <t>b4c9…</t>
         </is>
       </c>
       <c r="J115" s="7" t="inlineStr"/>
@@ -6794,113 +6794,113 @@
       <c r="L115" s="7" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr">
         <is>
+          <t>Секрет, заданный при регистрации вебхука. Защищает от подделки апдейтов тем, кто узнал URL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>POST /telegram/webhook/{secret}</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>object (Telegram Bot API)</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>{"update_id":1,"message":{…}}</t>
+        </is>
+      </c>
+      <c r="J116" s="7" t="inlineStr"/>
+      <c r="K116" s="7" t="inlineStr"/>
+      <c r="L116" s="7" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr">
+        <is>
           <t>Стандартный формат Telegram.</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>Admin API</t>
         </is>
       </c>
-      <c r="B116" s="5" t="inlineStr">
+      <c r="B117" s="5" t="inlineStr">
         <is>
           <t>POST /admin/login</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D116" s="6" t="inlineStr">
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t>Вход/Выход</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
+      <c r="E117" s="4" t="inlineStr">
         <is>
           <t>Внешняя админка</t>
         </is>
       </c>
-      <c r="F116" s="5" t="inlineStr"/>
-      <c r="G116" s="5" t="inlineStr"/>
-      <c r="H116" s="4" t="inlineStr"/>
-      <c r="I116" s="5" t="inlineStr"/>
-      <c r="J116" s="4" t="inlineStr">
+      <c r="F117" s="5" t="inlineStr"/>
+      <c r="G117" s="5" t="inlineStr"/>
+      <c r="H117" s="4" t="inlineStr"/>
+      <c r="I117" s="5" t="inlineStr"/>
+      <c r="J117" s="4" t="inlineStr">
         <is>
           <t>нет (публичный)</t>
         </is>
       </c>
-      <c r="K116" s="4" t="inlineStr">
+      <c r="K117" s="4" t="inlineStr">
         <is>
           <t>Лимит попыток входа с IP</t>
         </is>
       </c>
-      <c r="L116" s="4" t="inlineStr">
+      <c r="L117" s="4" t="inlineStr">
         <is>
           <t>401 · 429</t>
         </is>
       </c>
-      <c r="M116" s="4" t="inlineStr">
+      <c r="M117" s="4" t="inlineStr">
         <is>
           <t>Вход человека-администратора: email + пароль → JWT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="7" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B117" s="8" t="inlineStr">
-        <is>
-          <t>POST /admin/login</t>
-        </is>
-      </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F117" s="8" t="inlineStr">
-        <is>
-          <t>email / password</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t>string / string</t>
-        </is>
-      </c>
-      <c r="H117" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I117" s="8" t="inlineStr">
-        <is>
-          <t>ops@brand.com</t>
-        </is>
-      </c>
-      <c r="J117" s="7" t="inlineStr"/>
-      <c r="K117" s="7" t="inlineStr"/>
-      <c r="L117" s="7" t="inlineStr"/>
-      <c r="M117" s="7" t="inlineStr">
-        <is>
-          <t>Учётная запись администратора.</t>
         </is>
       </c>
     </row>
@@ -6917,27 +6917,27 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D118" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Внешняя админка</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>email / password</t>
         </is>
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>string (JWT)</t>
+          <t>string / string</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>eyJhbGciOiJIUzI1NiJ9…</t>
+          <t>ops@brand.com</t>
         </is>
       </c>
       <c r="J118" s="7" t="inlineStr"/>
@@ -6955,7 +6955,7 @@
       <c r="L118" s="7" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr">
         <is>
-          <t>Админ-токен; продлевается сам при активной работе.</t>
+          <t>Учётная запись администратора.</t>
         </is>
       </c>
     </row>
@@ -6967,105 +6967,117 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
+          <t>POST /admin/login</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>string (JWT)</t>
+        </is>
+      </c>
+      <c r="H119" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I119" s="8" t="inlineStr">
+        <is>
+          <t>eyJhbGciOiJIUzI1NiJ9…</t>
+        </is>
+      </c>
+      <c r="J119" s="7" t="inlineStr"/>
+      <c r="K119" s="7" t="inlineStr"/>
+      <c r="L119" s="7" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr">
+        <is>
+          <t>Админ-токен; продлевается сам при активной работе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
           <t>* /admin/*</t>
         </is>
       </c>
-      <c r="C119" s="7" t="inlineStr">
+      <c r="C120" s="7" t="inlineStr">
         <is>
           <t>Заголовок</t>
         </is>
       </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
         <is>
           <t>Внешняя админка</t>
         </is>
       </c>
-      <c r="F119" s="8" t="inlineStr">
+      <c r="F120" s="8" t="inlineStr">
         <is>
           <t>Authorization</t>
         </is>
       </c>
-      <c r="G119" s="8" t="inlineStr">
+      <c r="G120" s="8" t="inlineStr">
         <is>
           <t>Bearer &lt;JWT&gt; | Bearer sak_…</t>
         </is>
       </c>
-      <c r="H119" s="7" t="inlineStr">
+      <c r="H120" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="I119" s="8" t="inlineStr">
+      <c r="I120" s="8" t="inlineStr">
         <is>
           <t>Bearer sak_9f2c…</t>
         </is>
       </c>
-      <c r="J119" s="7" t="inlineStr">
+      <c r="J120" s="7" t="inlineStr">
         <is>
           <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
         </is>
       </c>
-      <c r="K119" s="7" t="inlineStr">
+      <c r="K120" s="7" t="inlineStr">
         <is>
           <t>Сервисный ключ несёт ОДНУ роль в ОДНОМ скоупе (global/partner/product); деактивация действует со следующего запроса</t>
         </is>
       </c>
-      <c r="L119" s="7" t="inlineStr">
+      <c r="L120" s="7" t="inlineStr">
         <is>
           <t>401 unauthorized · 403 forbidden (вне скоупа)</t>
         </is>
       </c>
-      <c r="M119" s="7" t="inlineStr">
+      <c r="M120" s="7" t="inlineStr">
         <is>
           <t>Единая авторизация всего админ-контура. Для машин — ключ sak_…, который выдаётся человеком-админом и показывается ровно один раз.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>GET /admin/structure</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D120" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr"/>
-      <c r="G120" s="5" t="inlineStr"/>
-      <c r="H120" s="4" t="inlineStr"/>
-      <c r="I120" s="5" t="inlineStr"/>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K120" s="4" t="inlineStr"/>
-      <c r="L120" s="4" t="inlineStr"/>
-      <c r="M120" s="4" t="inlineStr">
-        <is>
-          <t>Дерево партнёров и продуктов — точка синхронизации справочников с внешними системами.</t>
         </is>
       </c>
     </row>
@@ -7077,7 +7089,7 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/me</t>
+          <t>GET /admin/structure</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -7108,7 +7120,7 @@
       <c r="L121" s="4" t="inlineStr"/>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>Кто вызывает и какие у него скоупы — для проверки прав на своей стороне.</t>
+          <t>Дерево партнёров и продуктов — точка синхронизации справочников с внешними системами.</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7132,7 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>POST /admin/partners, PUT /admin/partners/{id}</t>
+          <t>GET /admin/me</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -7128,9 +7140,9 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D122" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -7148,14 +7160,10 @@
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr"/>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>401 · 403</t>
-        </is>
-      </c>
+      <c r="L122" s="4" t="inlineStr"/>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>Заведение и правка партнёра.</t>
+          <t>Кто вызывает и какие у него скоупы — для проверки прав на своей стороне.</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7175,7 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>POST /admin/products</t>
+          <t>POST /admin/partners, PUT /admin/partners/{id}</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -7175,9 +7183,9 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -7194,78 +7202,66 @@
           <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
         </is>
       </c>
-      <c r="K123" s="4" t="inlineStr">
+      <c r="K123" s="4" t="inlineStr"/>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>401 · 403</t>
+        </is>
+      </c>
+      <c r="M123" s="4" t="inlineStr">
+        <is>
+          <t>Заведение и правка партнёра.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>POST /admin/products</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr"/>
+      <c r="H124" s="4" t="inlineStr"/>
+      <c r="I124" s="5" t="inlineStr"/>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K124" s="4" t="inlineStr">
         <is>
           <t>Создание продукта автоматически засевает рабочую конфигурацию</t>
         </is>
       </c>
-      <c r="L123" s="4" t="inlineStr">
+      <c r="L124" s="4" t="inlineStr">
         <is>
           <t>401 · 403</t>
         </is>
       </c>
-      <c r="M123" s="4" t="inlineStr">
+      <c r="M124" s="4" t="inlineStr">
         <is>
           <t>Заведение казино. В ответе — публичный widget_key для встраивания виджета.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="7" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B124" s="8" t="inlineStr">
-        <is>
-          <t>PUT /admin/products/{id}</t>
-        </is>
-      </c>
-      <c r="C124" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D124" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F124" s="8" t="inlineStr">
-        <is>
-          <t>name, active, site_url, turnstile_site_key</t>
-        </is>
-      </c>
-      <c r="G124" s="8" t="inlineStr">
-        <is>
-          <t>string / bool</t>
-        </is>
-      </c>
-      <c r="H124" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I124" s="8" t="inlineStr">
-        <is>
-          <t>{"site_url":"https://brand.com"}</t>
-        </is>
-      </c>
-      <c r="J124" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K124" s="7" t="inlineStr"/>
-      <c r="L124" s="7" t="inlineStr"/>
-      <c r="M124" s="7" t="inlineStr">
-        <is>
-          <t>Публичная конфигурация продукта.</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7273,7 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>PUT /admin/products/{id}/secrets</t>
+          <t>PUT /admin/products/{id}</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
@@ -7297,12 +7293,12 @@
       </c>
       <c r="F125" s="8" t="inlineStr">
         <is>
-          <t>openai_key_primary, openai_key_fallback, handshake_secret, telegram_bot_token, player_api_key, turnstile_secret</t>
+          <t>name, active, site_url, turnstile_site_key</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string / bool</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
@@ -7312,7 +7308,7 @@
       </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>{"handshake_secret":"…"}</t>
+          <t>{"site_url":"https://brand.com"}</t>
         </is>
       </c>
       <c r="J125" s="7" t="inlineStr">
@@ -7320,58 +7316,74 @@
           <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
         </is>
       </c>
-      <c r="K125" s="7" t="inlineStr">
-        <is>
-          <t>Только запись: наружу возвращаются лишь флаги «задан/не задан»</t>
-        </is>
-      </c>
+      <c r="K125" s="7" t="inlineStr"/>
       <c r="L125" s="7" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr">
         <is>
+          <t>Публичная конфигурация продукта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>PUT /admin/products/{id}/secrets</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F126" s="8" t="inlineStr">
+        <is>
+          <t>openai_key_primary, openai_key_fallback, handshake_secret, telegram_bot_token, player_api_key, turnstile_secret</t>
+        </is>
+      </c>
+      <c r="G126" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I126" s="8" t="inlineStr">
+        <is>
+          <t>{"handshake_secret":"…"}</t>
+        </is>
+      </c>
+      <c r="J126" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K126" s="7" t="inlineStr">
+        <is>
+          <t>Только запись: наружу возвращаются лишь флаги «задан/не задан»</t>
+        </is>
+      </c>
+      <c r="L126" s="7" t="inlineStr"/>
+      <c r="M126" s="7" t="inlineStr">
+        <is>
           <t>Секреты продукта. Хранятся зашифрованными; через API не читаются.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>POST /admin/products/{id}/widget-key</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F126" s="5" t="inlineStr"/>
-      <c r="G126" s="5" t="inlineStr"/>
-      <c r="H126" s="4" t="inlineStr"/>
-      <c r="I126" s="5" t="inlineStr"/>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K126" s="4" t="inlineStr"/>
-      <c r="L126" s="4" t="inlineStr"/>
-      <c r="M126" s="4" t="inlineStr">
-        <is>
-          <t>Ротация публичного ключа виджета.</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7395,7 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/overview, /timeseries, /by-topic, /by-language</t>
+          <t>POST /admin/products/{id}/widget-key</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -7391,9 +7403,9 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D127" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -7410,15 +7422,11 @@
           <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
         </is>
       </c>
-      <c r="K127" s="4" t="inlineStr">
-        <is>
-          <t>Параметры периода from/to, скоуп product_id</t>
-        </is>
-      </c>
+      <c r="K127" s="4" t="inlineStr"/>
       <c r="L127" s="4" t="inlineStr"/>
       <c r="M127" s="4" t="inlineStr">
         <is>
-          <t>Метрики поддержки для выгрузки во внешнюю аналитику.</t>
+          <t>Ротация публичного ключа виджета.</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7438,7 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/ai-costs</t>
+          <t>GET /admin/overview, /timeseries, /by-topic, /by-language</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -7459,13 +7467,13 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>Разрез по типу вызова: chat | agent | review | media</t>
+          <t>Параметры периода from/to, скоуп product_id</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr"/>
       <c r="M128" s="4" t="inlineStr">
         <is>
-          <t>Полные траты на ИИ — сумма сходится со счётом провайдера.</t>
+          <t>Метрики поддержки для выгрузки во внешнюю аналитику.</t>
         </is>
       </c>
     </row>
@@ -7477,7 +7485,7 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/sessions, /admin/session/{id}</t>
+          <t>GET /admin/ai-costs</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -7506,13 +7514,13 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>Пагинация page/page_size</t>
+          <t>Разрез по типу вызова: chat | agent | review | media</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr"/>
       <c r="M129" s="4" t="inlineStr">
         <is>
-          <t>Журнал диалогов и полная стенограмма с постоимостью — выгрузка в общее хранилище обращений.</t>
+          <t>Полные траты на ИИ — сумма сходится со счётом провайдера.</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7532,7 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/audit</t>
+          <t>GET /admin/sessions, /admin/session/{id}</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -7551,11 +7559,15 @@
           <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
         </is>
       </c>
-      <c r="K130" s="4" t="inlineStr"/>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>Пагинация page/page_size</t>
+        </is>
+      </c>
       <c r="L130" s="4" t="inlineStr"/>
       <c r="M130" s="4" t="inlineStr">
         <is>
-          <t>Аудит административных изменений — для общего SIEM/комплаенс-контура.</t>
+          <t>Журнал диалогов и полная стенограмма с постоимостью — выгрузка в общее хранилище обращений.</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7579,7 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/quality/overview, /admin/quality/reviews</t>
+          <t>GET /admin/audit</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -7598,7 +7610,7 @@
       <c r="L131" s="4" t="inlineStr"/>
       <c r="M131" s="4" t="inlineStr">
         <is>
-          <t>Оценки качества диалогов (1..5, теги, пробелы в базе знаний).</t>
+          <t>Аудит административных изменений — для общего SIEM/комплаенс-контура.</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7622,7 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/retention/overview, /funnel, /effectiveness</t>
+          <t>GET /admin/quality/overview, /admin/quality/reviews</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -7641,7 +7653,7 @@
       <c r="L132" s="4" t="inlineStr"/>
       <c r="M132" s="4" t="inlineStr">
         <is>
-          <t>Метрики Telegram-фасада: воронка и результативность касаний.</t>
+          <t>Оценки качества диалогов (1..5, теги, пробелы в базе знаний).</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7665,7 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>POST /admin/api-keys</t>
+          <t>GET /admin/retention/overview, /funnel, /effectiveness</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -7661,9 +7673,9 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -7677,22 +7689,14 @@
       <c r="I133" s="5" t="inlineStr"/>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>только человек-админ (ключом ключ не выпустить)</t>
-        </is>
-      </c>
-      <c r="K133" s="4" t="inlineStr">
-        <is>
-          <t>Открытый текст ключа возвращается РОВНО ОДИН РАЗ; хранится только хеш</t>
-        </is>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>401 · 403</t>
-        </is>
-      </c>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K133" s="4" t="inlineStr"/>
+      <c r="L133" s="4" t="inlineStr"/>
       <c r="M133" s="4" t="inlineStr">
         <is>
-          <t>Выпуск сервисного ключа sak_… для внешней системы.</t>
+          <t>Метрики Telegram-фасада: воронка и результативность касаний.</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7708,7 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/mcp/manifest</t>
+          <t>POST /admin/api-keys</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -7712,9 +7716,9 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D134" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -7728,14 +7732,22 @@
       <c r="I134" s="5" t="inlineStr"/>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K134" s="4" t="inlineStr"/>
-      <c r="L134" s="4" t="inlineStr"/>
+          <t>только человек-админ (ключом ключ не выпустить)</t>
+        </is>
+      </c>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>Открытый текст ключа возвращается РОВНО ОДИН РАЗ; хранится только хеш</t>
+        </is>
+      </c>
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>401 · 403</t>
+        </is>
+      </c>
       <c r="M134" s="4" t="inlineStr">
         <is>
-          <t>Машиночитаемое описание админ-инструментов (MCP) для агентских клиентов.</t>
+          <t>Выпуск сервисного ключа sak_… для внешней системы.</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7759,7 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>GET /openapi.json, /docs, /redoc</t>
+          <t>GET /admin/mcp/manifest</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -7771,34 +7783,26 @@
       <c r="I135" s="5" t="inlineStr"/>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>нет (публичный)</t>
-        </is>
-      </c>
-      <c r="K135" s="4" t="inlineStr">
-        <is>
-          <t>Отдаётся только если включено на деплое</t>
-        </is>
-      </c>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>404, когда выключено</t>
-        </is>
-      </c>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K135" s="4" t="inlineStr"/>
+      <c r="L135" s="4" t="inlineStr"/>
       <c r="M135" s="4" t="inlineStr">
         <is>
-          <t>Машиночитаемая схема всего API — для генерации клиентов.</t>
+          <t>Машиночитаемое описание админ-инструментов (MCP) для агентских клиентов.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>Исходящие</t>
+          <t>Admin API</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
+          <t>GET /openapi.json, /docs, /redoc</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -7813,7 +7817,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Внешняя админка</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr"/>
@@ -7822,77 +7826,73 @@
       <c r="I136" s="5" t="inlineStr"/>
       <c r="J136" s="4" t="inlineStr">
         <is>
+          <t>нет (публичный)</t>
+        </is>
+      </c>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>Отдаётся только если включено на деплое</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>404, когда выключено</t>
+        </is>
+      </c>
+      <c r="M136" s="4" t="inlineStr">
+        <is>
+          <t>Машиночитаемая схема всего API — для генерации клиентов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr"/>
+      <c r="G137" s="5" t="inlineStr"/>
+      <c r="H137" s="4" t="inlineStr"/>
+      <c r="I137" s="5" t="inlineStr"/>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
           <t>Bearer &lt;player_api_key продукта&gt;</t>
         </is>
       </c>
-      <c r="K136" s="4" t="inlineStr">
+      <c r="K137" s="4" t="inlineStr">
         <is>
           <t>Таймаут 8 с · срабатывает, когда снапшот старше часа · только публичные адреса (защита от SSRF, пиннинг IP)</t>
         </is>
       </c>
-      <c r="L136" s="4" t="inlineStr">
+      <c r="L137" s="4" t="inlineStr">
         <is>
           <t>Любая ошибка тиха: остаётся прежний снапшот</t>
         </is>
       </c>
-      <c r="M136" s="4" t="inlineStr">
+      <c r="M137" s="4" t="inlineStr">
         <is>
           <t>ЛЕНИВОЕ обновление профиля игрока перед ходом бота. Эндпойнт реализует ПАРТНЁР — это требование к чужой системе.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t>Исходящие</t>
-        </is>
-      </c>
-      <c r="B137" s="8" t="inlineStr">
-        <is>
-          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
-        </is>
-      </c>
-      <c r="C137" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D137" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="inlineStr">
-        <is>
-          <t>Наш сервис</t>
-        </is>
-      </c>
-      <c r="F137" s="8" t="inlineStr">
-        <is>
-          <t>player_id</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr">
-        <is>
-          <t>query string</t>
-        </is>
-      </c>
-      <c r="H137" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I137" s="8" t="inlineStr">
-        <is>
-          <t>1048576</t>
-        </is>
-      </c>
-      <c r="J137" s="7" t="inlineStr"/>
-      <c r="K137" s="7" t="inlineStr"/>
-      <c r="L137" s="7" t="inlineStr"/>
-      <c r="M137" s="7" t="inlineStr">
-        <is>
-          <t>Кого запрашиваем.</t>
         </is>
       </c>
     </row>
@@ -7909,37 +7909,37 @@
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D138" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F138" s="8" t="inlineStr">
         <is>
-          <t>full_name, email, activation_status, country, balance, vip_level, registration_date, last_login_at, last_played_at, last_deposit_at</t>
+          <t>player_id</t>
         </is>
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>JSON-объект</t>
+          <t>query string</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
-          <t>{"full_name":"Андрей","balance":"150.00 USDT"}</t>
+          <t>1048576</t>
         </is>
       </c>
       <c r="J138" s="7" t="inlineStr"/>
@@ -7947,54 +7947,62 @@
       <c r="L138" s="7" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr">
         <is>
+          <t>Кого запрашиваем.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t>full_name, email, activation_status, country, balance, vip_level, registration_date, last_login_at, last_played_at, last_deposit_at</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>JSON-объект</t>
+        </is>
+      </c>
+      <c r="H139" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I139" s="8" t="inlineStr">
+        <is>
+          <t>{"full_name":"Андрей","balance":"150.00 USDT"}</t>
+        </is>
+      </c>
+      <c r="J139" s="7" t="inlineStr"/>
+      <c r="K139" s="7" t="inlineStr"/>
+      <c r="L139" s="7" t="inlineStr"/>
+      <c r="M139" s="7" t="inlineStr">
+        <is>
           <t>Ожидаемый ответ партнёра. Лишние поля игнорируются — берётся тот же белый список, что и везде.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>Исходящие</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>Telegram Bot API</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D139" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>Наш сервис</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="inlineStr"/>
-      <c r="G139" s="5" t="inlineStr"/>
-      <c r="H139" s="4" t="inlineStr"/>
-      <c r="I139" s="5" t="inlineStr"/>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>токен бота продукта (хранится зашифрованным)</t>
-        </is>
-      </c>
-      <c r="K139" s="4" t="inlineStr">
-        <is>
-          <t>Ретраи; недоступный игрок помечается как unreachable</t>
-        </is>
-      </c>
-      <c r="L139" s="4" t="inlineStr"/>
-      <c r="M139" s="4" t="inlineStr">
-        <is>
-          <t>sendMessage / sendPhoto / sendVideo / getChatMember / setWebhook.</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8014,7 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>OpenAI API</t>
+          <t>Telegram Bot API</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -8030,30 +8038,77 @@
       <c r="I140" s="5" t="inlineStr"/>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>ключ продукта (1–2 шт.), иначе ключ деплоя</t>
+          <t>токен бота продукта (хранится зашифрованным)</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>Два ключа с автопереключением; предохранитель при сбое провайдера; таймауты по назначению вызова</t>
+          <t>Ретраи; недоступный игрок помечается как unreachable</t>
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr"/>
       <c r="M140" s="4" t="inlineStr">
         <is>
+          <t>sendMessage / sendPhoto / sendVideo / getChatMember / setWebhook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>OpenAI API</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D141" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr"/>
+      <c r="G141" s="5" t="inlineStr"/>
+      <c r="H141" s="4" t="inlineStr"/>
+      <c r="I141" s="5" t="inlineStr"/>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>ключ продукта (1–2 шт.), иначе ключ деплоя</t>
+        </is>
+      </c>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>Два ключа с автопереключением; предохранитель при сбое провайдера; таймауты по назначению вызова</t>
+        </is>
+      </c>
+      <c r="L141" s="4" t="inlineStr"/>
+      <c r="M141" s="4" t="inlineStr">
+        <is>
           <t>Генерация ответов и фоновые проходы. Каждый вызов логируется с атрибуцией расходов.</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Файл генерируется из кода: scripts/build_api_reference.py. Живая версия — /integration-reference на самом сервисе.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M140"/>
+  <autoFilter ref="A4:M141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/frontend/api-reference.xlsx
+++ b/frontend/api-reference.xlsx
@@ -10,7 +10,7 @@
     <sheet name="API" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API'!$A$4:$M$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API'!$A$4:$M$157</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M143"/>
+  <dimension ref="A1:M159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4464,19 +4464,19 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>Partner API</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>POST /partner/{product_id}/event</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/player-update</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -4484,33 +4484,37 @@
           <t>Вход</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>CRM казино</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr"/>
-      <c r="G75" s="5" t="inlineStr"/>
-      <c r="H75" s="4" t="inlineStr"/>
-      <c r="I75" s="5" t="inlineStr"/>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K75" s="4" t="inlineStr">
-        <is>
-          <t>Идемпотентно по event_id (доставка at-least-once безопасна) · пакет до 500 событий · payload до 8 KiB · лимит partner:{ip}</t>
-        </is>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>401 · 413 batch_too_large · 422 invalid_event · 429</t>
-        </is>
-      </c>
-      <c r="M75" s="4" t="inlineStr">
-        <is>
-          <t>Канонический поток событий казино: кормит проактивного агента и обновляет сигналы активности игрока.</t>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>rg_status</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>self_exclude</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr"/>
+      <c r="K75" s="7" t="inlineStr"/>
+      <c r="L75" s="7" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t>RG-статус игрока: ok | cool_off | rg_hold | self_exclude. Источник истины по самоисключению — платформа казино; self_exclude/rg_hold полностью блокируют проактив и бонусы. Слать при каждой смене + первичный бэкфилл.</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4526,7 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST /partner/{product_id}/player-update</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
@@ -4542,22 +4546,22 @@
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>rg_status_until</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>string (≤64)</t>
+          <t>string (ISO-8601)</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>evt_2026072801</t>
+          <t>2026-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="J76" s="7" t="inlineStr"/>
@@ -4565,7 +4569,7 @@
       <c r="L76" s="7" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr">
         <is>
-          <t>Ключ идемпотентности. Повтор считается дубликатом, а не ошибкой.</t>
+          <t>Срок cool_off (истёкший снимается автоматически).</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4581,7 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST /partner/{product_id}/player-update</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -4597,34 +4601,30 @@
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>event_name</t>
+          <t>marketing_consent</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>string (из таксономии)</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>deposit_confirmed</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr"/>
       <c r="K77" s="7" t="inlineStr"/>
-      <c r="L77" s="7" t="inlineStr">
-        <is>
-          <t>422 invalid_event на неизвестное имя</t>
-        </is>
-      </c>
+      <c r="L77" s="7" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>Имя события. Таксономия — контракт, а не рекомендация; список ниже.</t>
+          <t>Маркетинговое согласие (гейт для Tier-1 рынков).</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST /partner/{product_id}/player-update</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
@@ -4656,22 +4656,22 @@
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>player_id | user_id</t>
+          <t>rg_flags</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>1048576</t>
+          <t>{"escalating_bets":true}</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr"/>
@@ -4679,7 +4679,7 @@
       <c r="L78" s="7" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr">
         <is>
-          <t>Игрок, к которому относится событие.</t>
+          <t>Готовые поведенческие RG-флаги risk-движка казино.</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST /partner/{product_id}/player-update</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>tg_user_id</t>
+          <t>timezone</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
-          <t>584210394</t>
+          <t>Europe/Istanbul</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr"/>
@@ -4734,7 +4734,7 @@
       <c r="L79" s="7" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>Явный получатель, когда один player_id связан с несколькими Telegram-аккаунтами.</t>
+          <t>Локальная таймзона игрока (IANA или '+03:00'; geo-IP на стороне казино) — точность smart-send-time.</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST /partner/{product_id}/player-update</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>email_opt_in / email_verified / push_opt_in / push_available / in_app_available / sms_opt_in</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>string (ISO-8601)</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28T10:15:00Z</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr"/>
@@ -4789,24 +4789,24 @@
       <c r="L80" s="7" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr">
         <is>
-          <t>Время события. Значение из будущего приводится к текущему моменту.</t>
+          <t>Согласия и доступность каналов. Строгий opt-in: канал без согласия никогда не используется, даже как fallback.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="7" t="inlineStr">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>Partner API</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>POST /partner/{product_id}/event</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/delivery-status</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
@@ -4814,37 +4814,33 @@
           <t>Вход</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E81" s="4" t="inlineStr">
         <is>
           <t>CRM казино</t>
         </is>
       </c>
-      <c r="F81" s="8" t="inlineStr">
-        <is>
-          <t>event_version</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H81" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I81" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J81" s="7" t="inlineStr"/>
-      <c r="K81" s="7" t="inlineStr"/>
-      <c r="L81" s="7" t="inlineStr"/>
-      <c r="M81" s="7" t="inlineStr">
-        <is>
-          <t>Версия схемы события на стороне отправителя.</t>
+      <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" s="5" t="inlineStr"/>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>Идемпотентно; статус не движется назад · лимит partner:{ip}</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>401 unauthorized · 422 invalid_status · 429 rate_limited</t>
+        </is>
+      </c>
+      <c r="M81" s="4" t="inlineStr">
+        <is>
+          <t>Коллбек прогресса доставки заказа push/in-app, размещённого оркестратором (см. Исходящие: delivery-endpoint).</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4852,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST /partner/{product_id}/delivery-status</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
@@ -4876,22 +4872,22 @@
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>payload</t>
+          <t>delivery_id</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>object (≤8 KiB)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>{"amount":"50.00","currency":"USDT"}</t>
+          <t>dl_a1b2c3d4e5f6</t>
         </is>
       </c>
       <c r="J82" s="7" t="inlineStr"/>
@@ -4899,7 +4895,7 @@
       <c r="L82" s="7" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr">
         <is>
-          <t>Детали события; может нести и поля профиля — они обновят снапшот.</t>
+          <t>Наш ключ идемпотентности заказа доставки.</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4907,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST /partner/{product_id}/delivery-status</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -4931,22 +4927,22 @@
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>events</t>
+          <t>status</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>[object] (≤500)</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>[{"event_id":"…","event_name":"…"}]</t>
+          <t>delivered</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr"/>
@@ -4954,24 +4950,24 @@
       <c r="L83" s="7" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>Пакетная форма. Взаимоисключима с плоскими полями выше.</t>
+          <t>sent | delivered | opened | clicked | bounced.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="7" t="inlineStr">
-        <is>
-          <t>Partner API</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>POST /partner/{product_id}/event</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr">
-        <is>
-          <t>Поле ответа</t>
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>POST &lt;offer_grant_url&gt; (реализует казино)</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
@@ -4979,172 +4975,160 @@
           <t>Выход</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>Наш сервис</t>
         </is>
       </c>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>stored / duplicates / invalid</t>
-        </is>
-      </c>
-      <c r="G84" s="8" t="inlineStr">
-        <is>
-          <t>int|bool</t>
-        </is>
-      </c>
-      <c r="H84" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I84" s="8" t="inlineStr">
-        <is>
-          <t>{"ok":true,"stored":12,"duplicates":3}</t>
-        </is>
-      </c>
-      <c r="J84" s="7" t="inlineStr"/>
-      <c r="K84" s="7" t="inlineStr"/>
-      <c r="L84" s="7" t="inlineStr"/>
-      <c r="M84" s="7" t="inlineStr">
-        <is>
-          <t>Итог приёма: сколько принято, сколько дублей, сколько отвергнуто.</t>
+      <c r="F84" s="5" t="inlineStr"/>
+      <c r="G84" s="5" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="5" t="inlineStr"/>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;partner outbound key продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>Идемпотентно по offer_grant_id (повтор возвращает тот же результат, второй бонус не создаётся) · таймаут retention.offer_grant_timeout_sec</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>401 · 400 unsupported_offer_type · 422 player_not_found</t>
+        </is>
+      </c>
+      <c r="M84" s="4" t="inlineStr">
+        <is>
+          <t>Выдача бонуса по его ID из бонус-CMS казино (offer engine). URL задаётся per product в админке.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Partner API</t>
+          <t>Исходящие</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST &lt;offer_grant_url&gt; (реализует казино)</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>session_started</t>
+          <t>offer_grant_id</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>event_name · Сессия</t>
-        </is>
-      </c>
-      <c r="H85" s="7" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"session_started"}</t>
-        </is>
-      </c>
-      <c r="J85" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K85" s="7" t="inlineStr">
-        <is>
-          <t>обновляет last_login_at</t>
-        </is>
-      </c>
+          <t>og_a1b2c3d4e5f6</t>
+        </is>
+      </c>
+      <c r="J85" s="7" t="inlineStr"/>
+      <c r="K85" s="7" t="inlineStr"/>
       <c r="L85" s="7" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>Игрок начал сессию на сайте или в приложении.</t>
+          <t>Наш детерминированный ключ идемпотентности.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>Partner API</t>
+          <t>Исходящие</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST &lt;offer_grant_url&gt; (реализует казино)</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
-        </is>
-      </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>session_ended</t>
+          <t>player_id / bonus_id / offer_type / params</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>event_name · Сессия</t>
-        </is>
-      </c>
-      <c r="H86" s="7" t="inlineStr"/>
+          <t>string / string / string / object</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"session_ended"}</t>
-        </is>
-      </c>
-      <c r="J86" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K86" s="7" t="inlineStr">
-        <is>
-          <t>обновляет last_login_at</t>
-        </is>
-      </c>
+          <t>{"bonus_id":"BONUS-42"}</t>
+        </is>
+      </c>
+      <c r="J86" s="7" t="inlineStr"/>
+      <c r="K86" s="7" t="inlineStr"/>
       <c r="L86" s="7" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr">
         <is>
-          <t>Игрок завершил сессию.</t>
+          <t>Кому и какой бонус начислить (bonus_id — ID в бонус-CMS).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Partner API</t>
+          <t>Исходящие</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST &lt;offer_grant_url&gt; (реализует казино)</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле ответа</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
@@ -5159,169 +5143,153 @@
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>deposit_initiated</t>
+          <t>status</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>event_name · Платежи</t>
-        </is>
-      </c>
-      <c r="H87" s="7" t="inlineStr"/>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="I87" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"deposit_initiated"}</t>
-        </is>
-      </c>
-      <c r="J87" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K87" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>granted</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr"/>
+      <c r="K87" s="7" t="inlineStr"/>
       <c r="L87" s="7" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>Депозит начат, ещё не подтверждён.</t>
+          <t>granted | fraud_hold | duplicate | failed (+ partner_ref, credited_usd). Персона упоминает бонус ТОЛЬКО после granted.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t>Partner API</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>POST /partner/{product_id}/event</t>
-        </is>
-      </c>
-      <c r="C88" s="7" t="inlineStr">
-        <is>
-          <t>Событие</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>CRM казино</t>
-        </is>
-      </c>
-      <c r="F88" s="8" t="inlineStr">
-        <is>
-          <t>deposit_confirmed</t>
-        </is>
-      </c>
-      <c r="G88" s="8" t="inlineStr">
-        <is>
-          <t>event_name · Платежи</t>
-        </is>
-      </c>
-      <c r="H88" s="7" t="inlineStr"/>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t>{"event_name":"deposit_confirmed"}</t>
-        </is>
-      </c>
-      <c r="J88" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K88" s="7" t="inlineStr">
-        <is>
-          <t>обновляет last_deposit_at</t>
-        </is>
-      </c>
-      <c r="L88" s="7" t="inlineStr"/>
-      <c r="M88" s="7" t="inlineStr">
-        <is>
-          <t>Депозит зачислен — сильнейший позитивный сигнал.</t>
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>POST &lt;delivery_endpoint_url&gt; (реализует казино)</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr"/>
+      <c r="G88" s="5" t="inlineStr"/>
+      <c r="H88" s="4" t="inlineStr"/>
+      <c r="I88" s="5" t="inlineStr"/>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;partner outbound key продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>Идемпотентно по delivery_id · таймаут retention.push_delivery_timeout_sec · транзиентные ошибки ретраятся (1m/5m/30m), permanent — нет</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>permanent:true в ответе = ретраев не будет</t>
+        </is>
+      </c>
+      <c r="M88" s="4" t="inlineStr">
+        <is>
+          <t>Заказ делегированной доставки push/in-app: казино доставляет на устройство своей инфраструктурой и шлёт прогресс коллбеком delivery-status.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Partner API</t>
+          <t>Исходящие</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST &lt;delivery_endpoint_url&gt; (реализует казино)</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>deposit_failed</t>
+          <t>delivery_id / player_id / channel / title / body / cta_url / ttl_sec</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>event_name · Платежи</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr"/>
+          <t>string / string / enum / string / string / string / int</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"deposit_failed"}</t>
-        </is>
-      </c>
-      <c r="J89" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K89" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>{"channel":"push","ttl_sec":86400}</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr"/>
+      <c r="K89" s="7" t="inlineStr"/>
       <c r="L89" s="7" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>Депозит не прошёл.</t>
+          <t>Заказ доставки; channel: push | in_app.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>Partner API</t>
+          <t>Исходящие</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST &lt;delivery_endpoint_url&gt; (реализует казино)</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле ответа</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
@@ -5336,51 +5304,47 @@
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>withdrawal_settled</t>
+          <t>status</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>event_name · Платежи</t>
-        </is>
-      </c>
-      <c r="H90" s="7" t="inlineStr"/>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"withdrawal_settled"}</t>
-        </is>
-      </c>
-      <c r="J90" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K90" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="J90" s="7" t="inlineStr"/>
+      <c r="K90" s="7" t="inlineStr"/>
       <c r="L90" s="7" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr">
         <is>
-          <t>Вывод завершён.</t>
+          <t>sent | queued | delivered | failed (+ reason, permanent, provider_ref).</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="7" t="inlineStr">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>Partner API</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>Событие</t>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
@@ -5388,41 +5352,33 @@
           <t>Вход</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="E91" s="4" t="inlineStr">
         <is>
           <t>CRM казино</t>
         </is>
       </c>
-      <c r="F91" s="8" t="inlineStr">
-        <is>
-          <t>bet_settled</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr">
-        <is>
-          <t>event_name · Игра</t>
-        </is>
-      </c>
-      <c r="H91" s="7" t="inlineStr"/>
-      <c r="I91" s="8" t="inlineStr">
-        <is>
-          <t>{"event_name":"bet_settled"}</t>
-        </is>
-      </c>
-      <c r="J91" s="7" t="inlineStr">
+      <c r="F91" s="5" t="inlineStr"/>
+      <c r="G91" s="5" t="inlineStr"/>
+      <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" s="5" t="inlineStr"/>
+      <c r="J91" s="4" t="inlineStr">
         <is>
           <t>Bearer &lt;handshake_secret продукта&gt;</t>
         </is>
       </c>
-      <c r="K91" s="7" t="inlineStr">
-        <is>
-          <t>обновляет last_played_at</t>
-        </is>
-      </c>
-      <c r="L91" s="7" t="inlineStr"/>
-      <c r="M91" s="7" t="inlineStr">
-        <is>
-          <t>Ставка рассчитана. Сумма проигрыша за 24 ч влияет на тон коммуникации.</t>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>Идемпотентно по event_id (доставка at-least-once безопасна) · пакет до 500 событий · payload до 8 KiB · лимит partner:{ip}</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>401 · 413 batch_too_large · 422 invalid_event · 429</t>
+        </is>
+      </c>
+      <c r="M91" s="4" t="inlineStr">
+        <is>
+          <t>Канонический поток событий казино: кормит проактивного агента и обновляет сигналы активности игрока.</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5395,7 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
@@ -5454,34 +5410,30 @@
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>bonus_granted</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>event_name · Бонусы</t>
-        </is>
-      </c>
-      <c r="H92" s="7" t="inlineStr"/>
+          <t>string (≤64)</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_granted"}</t>
-        </is>
-      </c>
-      <c r="J92" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K92" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>evt_2026072801</t>
+        </is>
+      </c>
+      <c r="J92" s="7" t="inlineStr"/>
+      <c r="K92" s="7" t="inlineStr"/>
       <c r="L92" s="7" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>Бонус начислен.</t>
+          <t>Ключ идемпотентности. Повтор считается дубликатом, а не ошибкой.</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5450,7 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -5513,34 +5465,34 @@
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>bonus_claimed</t>
+          <t>event_name</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>event_name · Бонусы</t>
-        </is>
-      </c>
-      <c r="H93" s="7" t="inlineStr"/>
+          <t>string (из таксономии)</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="I93" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_claimed"}</t>
-        </is>
-      </c>
-      <c r="J93" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K93" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L93" s="7" t="inlineStr"/>
+          <t>deposit_confirmed</t>
+        </is>
+      </c>
+      <c r="J93" s="7" t="inlineStr"/>
+      <c r="K93" s="7" t="inlineStr"/>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>422 invalid_event на неизвестное имя</t>
+        </is>
+      </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
-          <t>Бонус активирован игроком.</t>
+          <t>Имя события. Таксономия — контракт, а не рекомендация; список ниже.</t>
         </is>
       </c>
     </row>
@@ -5557,7 +5509,7 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
@@ -5572,34 +5524,30 @@
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>bonus_completed</t>
+          <t>player_id | user_id</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>event_name · Бонусы</t>
-        </is>
-      </c>
-      <c r="H94" s="7" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_completed"}</t>
-        </is>
-      </c>
-      <c r="J94" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K94" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>1048576</t>
+        </is>
+      </c>
+      <c r="J94" s="7" t="inlineStr"/>
+      <c r="K94" s="7" t="inlineStr"/>
       <c r="L94" s="7" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr">
         <is>
-          <t>Отыгрыш завершён.</t>
+          <t>Игрок, к которому относится событие.</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5564,7 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -5631,34 +5579,30 @@
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>bonus_expired</t>
+          <t>tg_user_id</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>event_name · Бонусы</t>
-        </is>
-      </c>
-      <c r="H95" s="7" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="I95" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_expired"}</t>
-        </is>
-      </c>
-      <c r="J95" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K95" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>584210394</t>
+        </is>
+      </c>
+      <c r="J95" s="7" t="inlineStr"/>
+      <c r="K95" s="7" t="inlineStr"/>
       <c r="L95" s="7" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>Бонус сгорел.</t>
+          <t>Явный получатель, когда один player_id связан с несколькими Telegram-аккаунтами.</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5619,7 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
@@ -5690,34 +5634,30 @@
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>kyc_started</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>event_name · Верификация</t>
-        </is>
-      </c>
-      <c r="H96" s="7" t="inlineStr"/>
+          <t>string (ISO-8601)</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"kyc_started"}</t>
-        </is>
-      </c>
-      <c r="J96" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K96" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>2026-07-28T10:15:00Z</t>
+        </is>
+      </c>
+      <c r="J96" s="7" t="inlineStr"/>
+      <c r="K96" s="7" t="inlineStr"/>
       <c r="L96" s="7" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr">
         <is>
-          <t>Верификация начата.</t>
+          <t>Время события. Значение из будущего приводится к текущему моменту.</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5674,7 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
@@ -5749,34 +5689,30 @@
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>kyc_approved</t>
+          <t>event_version</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>event_name · Верификация</t>
-        </is>
-      </c>
-      <c r="H97" s="7" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"kyc_approved"}</t>
-        </is>
-      </c>
-      <c r="J97" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K97" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr"/>
+      <c r="K97" s="7" t="inlineStr"/>
       <c r="L97" s="7" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>Верификация пройдена.</t>
+          <t>Версия схемы события на стороне отправителя.</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5729,7 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
@@ -5808,34 +5744,30 @@
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>kyc_rejected</t>
+          <t>payload</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>event_name · Верификация</t>
-        </is>
-      </c>
-      <c r="H98" s="7" t="inlineStr"/>
+          <t>object (≤8 KiB)</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"kyc_rejected"}</t>
-        </is>
-      </c>
-      <c r="J98" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K98" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>{"amount":"50.00","currency":"USDT"}</t>
+        </is>
+      </c>
+      <c r="J98" s="7" t="inlineStr"/>
+      <c r="K98" s="7" t="inlineStr"/>
       <c r="L98" s="7" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr">
         <is>
-          <t>Верификация отклонена.</t>
+          <t>Детали события; может нести и поля профиля — они обновят снапшот.</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5784,7 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
@@ -5867,34 +5799,30 @@
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>xp_granted</t>
+          <t>events</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>event_name · Лояльность</t>
-        </is>
-      </c>
-      <c r="H99" s="7" t="inlineStr"/>
+          <t>[object] (≤500)</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"xp_granted"}</t>
-        </is>
-      </c>
-      <c r="J99" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K99" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>[{"event_id":"…","event_name":"…"}]</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr"/>
+      <c r="K99" s="7" t="inlineStr"/>
       <c r="L99" s="7" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr">
         <is>
-          <t>Начислен опыт.</t>
+          <t>Пакетная форма. Взаимоисключима с плоскими полями выше.</t>
         </is>
       </c>
     </row>
@@ -5911,49 +5839,45 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>level_up</t>
+          <t>stored / duplicates / invalid</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>event_name · Лояльность</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="inlineStr"/>
+          <t>int|bool</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"level_up"}</t>
-        </is>
-      </c>
-      <c r="J100" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K100" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>{"ok":true,"stored":12,"duplicates":3}</t>
+        </is>
+      </c>
+      <c r="J100" s="7" t="inlineStr"/>
+      <c r="K100" s="7" t="inlineStr"/>
       <c r="L100" s="7" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr">
         <is>
-          <t>Новый уровень.</t>
+          <t>Итог приёма: сколько принято, сколько дублей, сколько отвергнуто.</t>
         </is>
       </c>
     </row>
@@ -5985,18 +5909,18 @@
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>class_up</t>
+          <t>session_started</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>event_name · Лояльность</t>
+          <t>event_name · Сессия</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr"/>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"class_up"}</t>
+          <t>{"event_name":"session_started"}</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
@@ -6006,13 +5930,13 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>обновляет last_login_at</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>Новый класс / VIP-тир.</t>
+          <t>Игрок начал сессию на сайте или в приложении.</t>
         </is>
       </c>
     </row>
@@ -6044,18 +5968,18 @@
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>downgrade</t>
+          <t>session_ended</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>event_name · Лояльность</t>
+          <t>event_name · Сессия</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr"/>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"downgrade"}</t>
+          <t>{"event_name":"session_ended"}</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
@@ -6065,13 +5989,13 @@
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>обновляет last_login_at</t>
         </is>
       </c>
       <c r="L102" s="7" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr">
         <is>
-          <t>Понижение класса.</t>
+          <t>Игрок завершил сессию.</t>
         </is>
       </c>
     </row>
@@ -6103,18 +6027,18 @@
       </c>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>highlights_pack_opened</t>
+          <t>deposit_initiated</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>event_name · Активности</t>
+          <t>event_name · Платежи</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr"/>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"highlights_pack_opened"}</t>
+          <t>{"event_name":"deposit_initiated"}</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -6130,7 +6054,7 @@
       <c r="L103" s="7" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr">
         <is>
-          <t>Открыт пак/кейс.</t>
+          <t>Депозит начат, ещё не подтверждён.</t>
         </is>
       </c>
     </row>
@@ -6162,18 +6086,18 @@
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>highlights_pack_completed</t>
+          <t>deposit_confirmed</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>event_name · Активности</t>
+          <t>event_name · Платежи</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr"/>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"highlights_pack_completed"}</t>
+          <t>{"event_name":"deposit_confirmed"}</t>
         </is>
       </c>
       <c r="J104" s="7" t="inlineStr">
@@ -6183,13 +6107,13 @@
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>обновляет last_deposit_at</t>
         </is>
       </c>
       <c r="L104" s="7" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr">
         <is>
-          <t>Пак завершён.</t>
+          <t>Депозит зачислен — сильнейший позитивный сигнал.</t>
         </is>
       </c>
     </row>
@@ -6221,18 +6145,18 @@
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>check_in_done</t>
+          <t>deposit_failed</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>event_name · Активности</t>
+          <t>event_name · Платежи</t>
         </is>
       </c>
       <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"check_in_done"}</t>
+          <t>{"event_name":"deposit_failed"}</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
@@ -6248,7 +6172,7 @@
       <c r="L105" s="7" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr">
         <is>
-          <t>Ежедневный чек-ин выполнен.</t>
+          <t>Депозит не прошёл.</t>
         </is>
       </c>
     </row>
@@ -6280,18 +6204,18 @@
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>mission_completed</t>
+          <t>withdrawal_settled</t>
         </is>
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>event_name · Активности</t>
+          <t>event_name · Платежи</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr"/>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"mission_completed"}</t>
+          <t>{"event_name":"withdrawal_settled"}</t>
         </is>
       </c>
       <c r="J106" s="7" t="inlineStr">
@@ -6307,75 +6231,83 @@
       <c r="L106" s="7" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr">
         <is>
-          <t>Миссия или квест завершён.</t>
+          <t>Вывод завершён.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>Telegram</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>POST /api/retention/deeplink</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>Сайт / виджет</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr"/>
-      <c r="G107" s="5" t="inlineStr"/>
-      <c r="H107" s="4" t="inlineStr"/>
-      <c r="I107" s="5" t="inlineStr"/>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>нет (публичный) + лимит по IP</t>
-        </is>
-      </c>
-      <c r="K107" s="4" t="inlineStr">
-        <is>
-          <t>Нонс одноразовый, живёт 120 с (настраивается)</t>
-        </is>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>403 bad_widget_key | retention_disabled · 409 no_bot · 401 bad_handshake · 429</t>
-        </is>
-      </c>
-      <c r="M107" s="4" t="inlineStr">
-        <is>
-          <t>Сайт получает одноразовую ссылку в Telegram-бота с профилем игрока.</t>
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>Partner API</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/event</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>Событие</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>bet_settled</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>event_name · Игра</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr"/>
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t>{"event_name":"bet_settled"}</t>
+        </is>
+      </c>
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>обновляет last_played_at</t>
+        </is>
+      </c>
+      <c r="L107" s="7" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr">
+        <is>
+          <t>Ставка рассчитана. Сумма проигрыша за 24 ч влияет на тон коммуникации.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>POST /api/retention/deeplink</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Событие</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
@@ -6385,52 +6317,56 @@
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>Сайт / виджет</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
-          <t>widget_key</t>
+          <t>bonus_granted</t>
         </is>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>string (wk_…)</t>
-        </is>
-      </c>
-      <c r="H108" s="7" t="inlineStr">
-        <is>
-          <t>условно</t>
-        </is>
-      </c>
+          <t>event_name · Бонусы</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr"/>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>wk_7f3a…</t>
-        </is>
-      </c>
-      <c r="J108" s="7" t="inlineStr"/>
-      <c r="K108" s="7" t="inlineStr"/>
+          <t>{"event_name":"bonus_granted"}</t>
+        </is>
+      </c>
+      <c r="J108" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K108" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L108" s="7" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr">
         <is>
-          <t>Продукт, чей бот открывать.</t>
+          <t>Бонус начислен.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>POST /api/retention/deeplink</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Событие</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
@@ -6440,52 +6376,56 @@
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>Сайт / виджет</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>signed_context</t>
+          <t>bonus_claimed</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>string (подпись)</t>
-        </is>
-      </c>
-      <c r="H109" s="7" t="inlineStr">
-        <is>
-          <t>условно</t>
-        </is>
-      </c>
+          <t>event_name · Бонусы</t>
+        </is>
+      </c>
+      <c r="H109" s="7" t="inlineStr"/>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>eyJpZCI6…​.QkFTRTY0</t>
-        </is>
-      </c>
-      <c r="J109" s="7" t="inlineStr"/>
-      <c r="K109" s="7" t="inlineStr"/>
+          <t>{"event_name":"bonus_claimed"}</t>
+        </is>
+      </c>
+      <c r="J109" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K109" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L109" s="7" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr">
         <is>
-          <t>Профиль игрока — те же поля и та же подпись, что в Chat API.</t>
+          <t>Бонус активирован игроком.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>POST /api/retention/deeplink</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Событие</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
@@ -6495,52 +6435,56 @@
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>Сайт / виджет</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
-          <t>escalation</t>
+          <t>bonus_completed</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="H110" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
+          <t>event_name · Бонусы</t>
+        </is>
+      </c>
+      <c r="H110" s="7" t="inlineStr"/>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="J110" s="7" t="inlineStr"/>
-      <c r="K110" s="7" t="inlineStr"/>
+          <t>{"event_name":"bonus_completed"}</t>
+        </is>
+      </c>
+      <c r="J110" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K110" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L110" s="7" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr">
         <is>
-          <t>true — точка входа «к менеджеру».</t>
+          <t>Отыгрыш завершён.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>POST /api/retention/deeplink</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Событие</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
@@ -6550,162 +6494,174 @@
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>Сайт / виджет</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>lang</t>
+          <t>bonus_expired</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>string (код или локаль)</t>
-        </is>
-      </c>
-      <c r="H111" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
+          <t>event_name · Бонусы</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="inlineStr"/>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>ru</t>
-        </is>
-      </c>
-      <c r="J111" s="7" t="inlineStr"/>
-      <c r="K111" s="7" t="inlineStr"/>
+          <t>{"event_name":"bonus_expired"}</t>
+        </is>
+      </c>
+      <c r="J111" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K111" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L111" s="7" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr">
         <is>
-          <t>Язык, в котором откроется бот.</t>
+          <t>Бонус сгорел.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>POST /api/retention/deeplink</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D112" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Событие</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
-          <t>deep_link</t>
+          <t>kyc_started</t>
         </is>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>string (URL)</t>
-        </is>
-      </c>
-      <c r="H112" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>event_name · Верификация</t>
+        </is>
+      </c>
+      <c r="H112" s="7" t="inlineStr"/>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>https://t.me/brand_bot?start=Ax7…</t>
-        </is>
-      </c>
-      <c r="J112" s="7" t="inlineStr"/>
-      <c r="K112" s="7" t="inlineStr"/>
+          <t>{"event_name":"kyc_started"}</t>
+        </is>
+      </c>
+      <c r="J112" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K112" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L112" s="7" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr">
         <is>
-          <t>Ссылка для кнопки. Нонс погашается при первом /start.</t>
+          <t>Верификация начата.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>POST /api/retention/deeplink</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D113" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Событие</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>nonce</t>
+          <t>kyc_approved</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H113" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>event_name · Верификация</t>
+        </is>
+      </c>
+      <c r="H113" s="7" t="inlineStr"/>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>Ax7kQ…</t>
-        </is>
-      </c>
-      <c r="J113" s="7" t="inlineStr"/>
-      <c r="K113" s="7" t="inlineStr"/>
+          <t>{"event_name":"kyc_approved"}</t>
+        </is>
+      </c>
+      <c r="J113" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K113" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L113" s="7" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr">
         <is>
-          <t>Тот же одноразовый токен отдельным полем.</t>
+          <t>Верификация пройдена.</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
-        <is>
-          <t>Telegram</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>POST /telegram/webhook/{secret}</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>Partner API</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/event</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>Событие</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
@@ -6713,50 +6669,58 @@
           <t>Вход</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>Telegram</t>
-        </is>
-      </c>
-      <c r="F114" s="5" t="inlineStr"/>
-      <c r="G114" s="5" t="inlineStr"/>
-      <c r="H114" s="4" t="inlineStr"/>
-      <c r="I114" s="5" t="inlineStr"/>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>путь = webhook-токен продукта (роутинг) + заголовок X-Telegram-Bot-Api-Secret-Token</t>
-        </is>
-      </c>
-      <c r="K114" s="4" t="inlineStr">
-        <is>
-          <t>Всегда быстрый 200 (иначе Telegram ретраит); ход ИИ выполняется в фоне</t>
-        </is>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>403 bad_secret_token · неизвестный токен пути → тихий 200</t>
-        </is>
-      </c>
-      <c r="M114" s="4" t="inlineStr">
-        <is>
-          <t>Приём апдейтов Telegram — второй фасад над тем же ИИ-ядром.</t>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F114" s="8" t="inlineStr">
+        <is>
+          <t>kyc_rejected</t>
+        </is>
+      </c>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>event_name · Верификация</t>
+        </is>
+      </c>
+      <c r="H114" s="7" t="inlineStr"/>
+      <c r="I114" s="8" t="inlineStr">
+        <is>
+          <t>{"event_name":"kyc_rejected"}</t>
+        </is>
+      </c>
+      <c r="J114" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K114" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L114" s="7" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr">
+        <is>
+          <t>Верификация отклонена.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>POST /telegram/webhook/{secret}</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Заголовок</t>
+          <t>Событие</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
@@ -6766,52 +6730,56 @@
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>X-Telegram-Bot-Api-Secret-Token</t>
+          <t>xp_granted</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H115" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>event_name · Лояльность</t>
+        </is>
+      </c>
+      <c r="H115" s="7" t="inlineStr"/>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>b4c9…</t>
-        </is>
-      </c>
-      <c r="J115" s="7" t="inlineStr"/>
-      <c r="K115" s="7" t="inlineStr"/>
+          <t>{"event_name":"xp_granted"}</t>
+        </is>
+      </c>
+      <c r="J115" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K115" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L115" s="7" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr">
         <is>
-          <t>Секрет, заданный при регистрации вебхука. Защищает от подделки апдейтов тем, кто узнал URL.</t>
+          <t>Начислен опыт.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>POST /telegram/webhook/{secret}</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Событие</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
@@ -6821,103 +6789,115 @@
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
-          <t>update</t>
+          <t>level_up</t>
         </is>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>object (Telegram Bot API)</t>
-        </is>
-      </c>
-      <c r="H116" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>event_name · Лояльность</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr"/>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>{"update_id":1,"message":{…}}</t>
-        </is>
-      </c>
-      <c r="J116" s="7" t="inlineStr"/>
-      <c r="K116" s="7" t="inlineStr"/>
+          <t>{"event_name":"level_up"}</t>
+        </is>
+      </c>
+      <c r="J116" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K116" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L116" s="7" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr">
         <is>
-          <t>Стандартный формат Telegram.</t>
+          <t>Новый уровень.</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>POST /admin/login</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F117" s="5" t="inlineStr"/>
-      <c r="G117" s="5" t="inlineStr"/>
-      <c r="H117" s="4" t="inlineStr"/>
-      <c r="I117" s="5" t="inlineStr"/>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>нет (публичный)</t>
-        </is>
-      </c>
-      <c r="K117" s="4" t="inlineStr">
-        <is>
-          <t>Лимит попыток входа с IP</t>
-        </is>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>401 · 429</t>
-        </is>
-      </c>
-      <c r="M117" s="4" t="inlineStr">
-        <is>
-          <t>Вход человека-администратора: email + пароль → JWT.</t>
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>Partner API</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/event</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>Событие</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>class_up</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>event_name · Лояльность</t>
+        </is>
+      </c>
+      <c r="H117" s="7" t="inlineStr"/>
+      <c r="I117" s="8" t="inlineStr">
+        <is>
+          <t>{"event_name":"class_up"}</t>
+        </is>
+      </c>
+      <c r="J117" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K117" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L117" s="7" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr">
+        <is>
+          <t>Новый класс / VIP-тир.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>Admin API</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>POST /admin/login</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Событие</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
@@ -6927,107 +6907,115 @@
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>Внешняя админка</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
-          <t>email / password</t>
+          <t>downgrade</t>
         </is>
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>string / string</t>
-        </is>
-      </c>
-      <c r="H118" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>event_name · Лояльность</t>
+        </is>
+      </c>
+      <c r="H118" s="7" t="inlineStr"/>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>ops@brand.com</t>
-        </is>
-      </c>
-      <c r="J118" s="7" t="inlineStr"/>
-      <c r="K118" s="7" t="inlineStr"/>
+          <t>{"event_name":"downgrade"}</t>
+        </is>
+      </c>
+      <c r="J118" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K118" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L118" s="7" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr">
         <is>
-          <t>Учётная запись администратора.</t>
+          <t>Понижение класса.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>Admin API</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>POST /admin/login</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D119" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Событие</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F119" s="8" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>highlights_pack_opened</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>string (JWT)</t>
-        </is>
-      </c>
-      <c r="H119" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>event_name · Активности</t>
+        </is>
+      </c>
+      <c r="H119" s="7" t="inlineStr"/>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>eyJhbGciOiJIUzI1NiJ9…</t>
-        </is>
-      </c>
-      <c r="J119" s="7" t="inlineStr"/>
-      <c r="K119" s="7" t="inlineStr"/>
+          <t>{"event_name":"highlights_pack_opened"}</t>
+        </is>
+      </c>
+      <c r="J119" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K119" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L119" s="7" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr">
         <is>
-          <t>Админ-токен; продлевается сам при активной работе.</t>
+          <t>Открыт пак/кейс.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>Admin API</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>* /admin/*</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>Заголовок</t>
+          <t>Событие</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
@@ -7037,145 +7025,169 @@
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>Внешняя админка</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F120" s="8" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>highlights_pack_completed</t>
         </is>
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>Bearer &lt;JWT&gt; | Bearer sak_…</t>
-        </is>
-      </c>
-      <c r="H120" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>event_name · Активности</t>
+        </is>
+      </c>
+      <c r="H120" s="7" t="inlineStr"/>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>Bearer sak_9f2c…</t>
+          <t>{"event_name":"highlights_pack_completed"}</t>
         </is>
       </c>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
         </is>
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>Сервисный ключ несёт ОДНУ роль в ОДНОМ скоупе (global/partner/product); деактивация действует со следующего запроса</t>
-        </is>
-      </c>
-      <c r="L120" s="7" t="inlineStr">
-        <is>
-          <t>401 unauthorized · 403 forbidden (вне скоупа)</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L120" s="7" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr">
         <is>
-          <t>Единая авторизация всего админ-контура. Для машин — ключ sak_…, который выдаётся человеком-админом и показывается ровно один раз.</t>
+          <t>Пак завершён.</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>GET /admin/structure</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D121" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F121" s="5" t="inlineStr"/>
-      <c r="G121" s="5" t="inlineStr"/>
-      <c r="H121" s="4" t="inlineStr"/>
-      <c r="I121" s="5" t="inlineStr"/>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K121" s="4" t="inlineStr"/>
-      <c r="L121" s="4" t="inlineStr"/>
-      <c r="M121" s="4" t="inlineStr">
-        <is>
-          <t>Дерево партнёров и продуктов — точка синхронизации справочников с внешними системами.</t>
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>Partner API</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/event</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>Событие</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>check_in_done</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>event_name · Активности</t>
+        </is>
+      </c>
+      <c r="H121" s="7" t="inlineStr"/>
+      <c r="I121" s="8" t="inlineStr">
+        <is>
+          <t>{"event_name":"check_in_done"}</t>
+        </is>
+      </c>
+      <c r="J121" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K121" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L121" s="7" t="inlineStr"/>
+      <c r="M121" s="7" t="inlineStr">
+        <is>
+          <t>Ежедневный чек-ин выполнен.</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>GET /admin/me</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D122" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F122" s="5" t="inlineStr"/>
-      <c r="G122" s="5" t="inlineStr"/>
-      <c r="H122" s="4" t="inlineStr"/>
-      <c r="I122" s="5" t="inlineStr"/>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K122" s="4" t="inlineStr"/>
-      <c r="L122" s="4" t="inlineStr"/>
-      <c r="M122" s="4" t="inlineStr">
-        <is>
-          <t>Кто вызывает и какие у него скоупы — для проверки прав на своей стороне.</t>
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>Partner API</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/event</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>Событие</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F122" s="8" t="inlineStr">
+        <is>
+          <t>mission_completed</t>
+        </is>
+      </c>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>event_name · Активности</t>
+        </is>
+      </c>
+      <c r="H122" s="7" t="inlineStr"/>
+      <c r="I122" s="8" t="inlineStr">
+        <is>
+          <t>{"event_name":"mission_completed"}</t>
+        </is>
+      </c>
+      <c r="J122" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K122" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L122" s="7" t="inlineStr"/>
+      <c r="M122" s="7" t="inlineStr">
+        <is>
+          <t>Миссия или квест завершён.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>Admin API</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>POST /admin/partners, PUT /admin/partners/{id}</t>
+          <t>POST /api/retention/deeplink</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -7183,14 +7195,14 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D123" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Внешняя админка</t>
+          <t>Сайт / виджет</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr"/>
@@ -7199,81 +7211,89 @@
       <c r="I123" s="5" t="inlineStr"/>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K123" s="4" t="inlineStr"/>
+          <t>нет (публичный) + лимит по IP</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>Нонс одноразовый, живёт 120 с (настраивается)</t>
+        </is>
+      </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>401 · 403</t>
+          <t>403 bad_widget_key | retention_disabled · 409 no_bot · 401 bad_handshake · 429</t>
         </is>
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>Заведение и правка партнёра.</t>
+          <t>Сайт получает одноразовую ссылку в Telegram-бота с профилем игрока.</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>POST /admin/products</t>
-        </is>
-      </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="inlineStr"/>
-      <c r="G124" s="5" t="inlineStr"/>
-      <c r="H124" s="4" t="inlineStr"/>
-      <c r="I124" s="5" t="inlineStr"/>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K124" s="4" t="inlineStr">
-        <is>
-          <t>Создание продукта автоматически засевает рабочую конфигурацию</t>
-        </is>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>401 · 403</t>
-        </is>
-      </c>
-      <c r="M124" s="4" t="inlineStr">
-        <is>
-          <t>Заведение казино. В ответе — публичный widget_key для встраивания виджета.</t>
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/retention/deeplink</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>Сайт / виджет</t>
+        </is>
+      </c>
+      <c r="F124" s="8" t="inlineStr">
+        <is>
+          <t>widget_key</t>
+        </is>
+      </c>
+      <c r="G124" s="8" t="inlineStr">
+        <is>
+          <t>string (wk_…)</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t>условно</t>
+        </is>
+      </c>
+      <c r="I124" s="8" t="inlineStr">
+        <is>
+          <t>wk_7f3a…</t>
+        </is>
+      </c>
+      <c r="J124" s="7" t="inlineStr"/>
+      <c r="K124" s="7" t="inlineStr"/>
+      <c r="L124" s="7" t="inlineStr"/>
+      <c r="M124" s="7" t="inlineStr">
+        <is>
+          <t>Продукт, чей бот открывать.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>Admin API</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>PUT /admin/products/{id}</t>
+          <t>POST /api/retention/deeplink</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
@@ -7288,51 +7308,47 @@
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>Внешняя админка</t>
+          <t>Сайт / виджет</t>
         </is>
       </c>
       <c r="F125" s="8" t="inlineStr">
         <is>
-          <t>name, active, site_url, turnstile_site_key</t>
+          <t>signed_context</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>string / bool</t>
+          <t>string (подпись)</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>условно</t>
         </is>
       </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>{"site_url":"https://brand.com"}</t>
-        </is>
-      </c>
-      <c r="J125" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
+          <t>eyJpZCI6…​.QkFTRTY0</t>
+        </is>
+      </c>
+      <c r="J125" s="7" t="inlineStr"/>
       <c r="K125" s="7" t="inlineStr"/>
       <c r="L125" s="7" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr">
         <is>
-          <t>Публичная конфигурация продукта.</t>
+          <t>Профиль игрока — те же поля и та же подпись, что в Chat API.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>Admin API</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>PUT /admin/products/{id}/secrets</t>
+          <t>POST /api/retention/deeplink</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
@@ -7347,17 +7363,17 @@
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>Внешняя админка</t>
+          <t>Сайт / виджет</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr">
         <is>
-          <t>openai_key_primary, openai_key_fallback, handshake_secret, telegram_bot_token, player_api_key, turnstile_secret</t>
+          <t>escalation</t>
         </is>
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
@@ -7367,83 +7383,87 @@
       </c>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>{"handshake_secret":"…"}</t>
-        </is>
-      </c>
-      <c r="J126" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K126" s="7" t="inlineStr">
-        <is>
-          <t>Только запись: наружу возвращаются лишь флаги «задан/не задан»</t>
-        </is>
-      </c>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J126" s="7" t="inlineStr"/>
+      <c r="K126" s="7" t="inlineStr"/>
       <c r="L126" s="7" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr">
         <is>
-          <t>Секреты продукта. Хранятся зашифрованными; через API не читаются.</t>
+          <t>true — точка входа «к менеджеру».</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>POST /admin/products/{id}/widget-key</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F127" s="5" t="inlineStr"/>
-      <c r="G127" s="5" t="inlineStr"/>
-      <c r="H127" s="4" t="inlineStr"/>
-      <c r="I127" s="5" t="inlineStr"/>
-      <c r="J127" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K127" s="4" t="inlineStr"/>
-      <c r="L127" s="4" t="inlineStr"/>
-      <c r="M127" s="4" t="inlineStr">
-        <is>
-          <t>Ротация публичного ключа виджета.</t>
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/retention/deeplink</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>Сайт / виджет</t>
+        </is>
+      </c>
+      <c r="F127" s="8" t="inlineStr">
+        <is>
+          <t>lang</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>string (код или локаль)</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I127" s="8" t="inlineStr">
+        <is>
+          <t>ru</t>
+        </is>
+      </c>
+      <c r="J127" s="7" t="inlineStr"/>
+      <c r="K127" s="7" t="inlineStr"/>
+      <c r="L127" s="7" t="inlineStr"/>
+      <c r="M127" s="7" t="inlineStr">
+        <is>
+          <t>Язык, в котором откроется бот.</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>GET /admin/overview, /timeseries, /by-topic, /by-language</t>
-        </is>
-      </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/retention/deeplink</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
@@ -7451,46 +7471,54 @@
           <t>Выход</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F128" s="5" t="inlineStr"/>
-      <c r="G128" s="5" t="inlineStr"/>
-      <c r="H128" s="4" t="inlineStr"/>
-      <c r="I128" s="5" t="inlineStr"/>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K128" s="4" t="inlineStr">
-        <is>
-          <t>Параметры периода from/to, скоуп product_id</t>
-        </is>
-      </c>
-      <c r="L128" s="4" t="inlineStr"/>
-      <c r="M128" s="4" t="inlineStr">
-        <is>
-          <t>Метрики поддержки для выгрузки во внешнюю аналитику.</t>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F128" s="8" t="inlineStr">
+        <is>
+          <t>deep_link</t>
+        </is>
+      </c>
+      <c r="G128" s="8" t="inlineStr">
+        <is>
+          <t>string (URL)</t>
+        </is>
+      </c>
+      <c r="H128" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I128" s="8" t="inlineStr">
+        <is>
+          <t>https://t.me/brand_bot?start=Ax7…</t>
+        </is>
+      </c>
+      <c r="J128" s="7" t="inlineStr"/>
+      <c r="K128" s="7" t="inlineStr"/>
+      <c r="L128" s="7" t="inlineStr"/>
+      <c r="M128" s="7" t="inlineStr">
+        <is>
+          <t>Ссылка для кнопки. Нонс погашается при первом /start.</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>GET /admin/ai-costs</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/retention/deeplink</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
@@ -7498,41 +7526,49 @@
           <t>Выход</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F129" s="5" t="inlineStr"/>
-      <c r="G129" s="5" t="inlineStr"/>
-      <c r="H129" s="4" t="inlineStr"/>
-      <c r="I129" s="5" t="inlineStr"/>
-      <c r="J129" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K129" s="4" t="inlineStr">
-        <is>
-          <t>Разрез по типу вызова: chat | agent | review | media</t>
-        </is>
-      </c>
-      <c r="L129" s="4" t="inlineStr"/>
-      <c r="M129" s="4" t="inlineStr">
-        <is>
-          <t>Полные траты на ИИ — сумма сходится со счётом провайдера.</t>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F129" s="8" t="inlineStr">
+        <is>
+          <t>nonce</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H129" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I129" s="8" t="inlineStr">
+        <is>
+          <t>Ax7kQ…</t>
+        </is>
+      </c>
+      <c r="J129" s="7" t="inlineStr"/>
+      <c r="K129" s="7" t="inlineStr"/>
+      <c r="L129" s="7" t="inlineStr"/>
+      <c r="M129" s="7" t="inlineStr">
+        <is>
+          <t>Тот же одноразовый токен отдельным полем.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>Admin API</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/sessions, /admin/session/{id}</t>
+          <t>POST /telegram/webhook/{secret}</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -7540,14 +7576,14 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D130" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>Внешняя админка</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr"/>
@@ -7556,104 +7592,132 @@
       <c r="I130" s="5" t="inlineStr"/>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+          <t>путь = webhook-токен продукта (роутинг) + заголовок X-Telegram-Bot-Api-Secret-Token</t>
         </is>
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>Пагинация page/page_size</t>
-        </is>
-      </c>
-      <c r="L130" s="4" t="inlineStr"/>
+          <t>Всегда быстрый 200 (иначе Telegram ретраит); ход ИИ выполняется в фоне</t>
+        </is>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>403 bad_secret_token · неизвестный токен пути → тихий 200</t>
+        </is>
+      </c>
       <c r="M130" s="4" t="inlineStr">
         <is>
-          <t>Журнал диалогов и полная стенограмма с постоимостью — выгрузка в общее хранилище обращений.</t>
+          <t>Приём апдейтов Telegram — второй фасад над тем же ИИ-ядром.</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>GET /admin/audit</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D131" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F131" s="5" t="inlineStr"/>
-      <c r="G131" s="5" t="inlineStr"/>
-      <c r="H131" s="4" t="inlineStr"/>
-      <c r="I131" s="5" t="inlineStr"/>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K131" s="4" t="inlineStr"/>
-      <c r="L131" s="4" t="inlineStr"/>
-      <c r="M131" s="4" t="inlineStr">
-        <is>
-          <t>Аудит административных изменений — для общего SIEM/комплаенс-контура.</t>
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
+          <t>POST /telegram/webhook/{secret}</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>Заголовок</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="F131" s="8" t="inlineStr">
+        <is>
+          <t>X-Telegram-Bot-Api-Secret-Token</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I131" s="8" t="inlineStr">
+        <is>
+          <t>b4c9…</t>
+        </is>
+      </c>
+      <c r="J131" s="7" t="inlineStr"/>
+      <c r="K131" s="7" t="inlineStr"/>
+      <c r="L131" s="7" t="inlineStr"/>
+      <c r="M131" s="7" t="inlineStr">
+        <is>
+          <t>Секрет, заданный при регистрации вебхука. Защищает от подделки апдейтов тем, кто узнал URL.</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>GET /admin/quality/overview, /admin/quality/reviews</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D132" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F132" s="5" t="inlineStr"/>
-      <c r="G132" s="5" t="inlineStr"/>
-      <c r="H132" s="4" t="inlineStr"/>
-      <c r="I132" s="5" t="inlineStr"/>
-      <c r="J132" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K132" s="4" t="inlineStr"/>
-      <c r="L132" s="4" t="inlineStr"/>
-      <c r="M132" s="4" t="inlineStr">
-        <is>
-          <t>Оценки качества диалогов (1..5, теги, пробелы в базе знаний).</t>
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>POST /telegram/webhook/{secret}</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="F132" s="8" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t>object (Telegram Bot API)</t>
+        </is>
+      </c>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>{"update_id":1,"message":{…}}</t>
+        </is>
+      </c>
+      <c r="J132" s="7" t="inlineStr"/>
+      <c r="K132" s="7" t="inlineStr"/>
+      <c r="L132" s="7" t="inlineStr"/>
+      <c r="M132" s="7" t="inlineStr">
+        <is>
+          <t>Стандартный формат Telegram.</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7729,7 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/retention/overview, /funnel, /effectiveness</t>
+          <t>POST /admin/login</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -7673,9 +7737,9 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D133" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -7689,171 +7753,211 @@
       <c r="I133" s="5" t="inlineStr"/>
       <c r="J133" s="4" t="inlineStr">
         <is>
+          <t>нет (публичный)</t>
+        </is>
+      </c>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>Лимит попыток входа с IP</t>
+        </is>
+      </c>
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>401 · 429</t>
+        </is>
+      </c>
+      <c r="M133" s="4" t="inlineStr">
+        <is>
+          <t>Вход человека-администратора: email + пароль → JWT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>POST /admin/login</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F134" s="8" t="inlineStr">
+        <is>
+          <t>email / password</t>
+        </is>
+      </c>
+      <c r="G134" s="8" t="inlineStr">
+        <is>
+          <t>string / string</t>
+        </is>
+      </c>
+      <c r="H134" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I134" s="8" t="inlineStr">
+        <is>
+          <t>ops@brand.com</t>
+        </is>
+      </c>
+      <c r="J134" s="7" t="inlineStr"/>
+      <c r="K134" s="7" t="inlineStr"/>
+      <c r="L134" s="7" t="inlineStr"/>
+      <c r="M134" s="7" t="inlineStr">
+        <is>
+          <t>Учётная запись администратора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
+          <t>POST /admin/login</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F135" s="8" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>string (JWT)</t>
+        </is>
+      </c>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I135" s="8" t="inlineStr">
+        <is>
+          <t>eyJhbGciOiJIUzI1NiJ9…</t>
+        </is>
+      </c>
+      <c r="J135" s="7" t="inlineStr"/>
+      <c r="K135" s="7" t="inlineStr"/>
+      <c r="L135" s="7" t="inlineStr"/>
+      <c r="M135" s="7" t="inlineStr">
+        <is>
+          <t>Админ-токен; продлевается сам при активной работе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>* /admin/*</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>Заголовок</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F136" s="8" t="inlineStr">
+        <is>
+          <t>Authorization</t>
+        </is>
+      </c>
+      <c r="G136" s="8" t="inlineStr">
+        <is>
+          <t>Bearer &lt;JWT&gt; | Bearer sak_…</t>
+        </is>
+      </c>
+      <c r="H136" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I136" s="8" t="inlineStr">
+        <is>
+          <t>Bearer sak_9f2c…</t>
+        </is>
+      </c>
+      <c r="J136" s="7" t="inlineStr">
+        <is>
           <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
         </is>
       </c>
-      <c r="K133" s="4" t="inlineStr"/>
-      <c r="L133" s="4" t="inlineStr"/>
-      <c r="M133" s="4" t="inlineStr">
-        <is>
-          <t>Метрики Telegram-фасада: воронка и результативность касаний.</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>POST /admin/api-keys</t>
-        </is>
-      </c>
-      <c r="C134" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr"/>
-      <c r="G134" s="5" t="inlineStr"/>
-      <c r="H134" s="4" t="inlineStr"/>
-      <c r="I134" s="5" t="inlineStr"/>
-      <c r="J134" s="4" t="inlineStr">
-        <is>
-          <t>только человек-админ (ключом ключ не выпустить)</t>
-        </is>
-      </c>
-      <c r="K134" s="4" t="inlineStr">
-        <is>
-          <t>Открытый текст ключа возвращается РОВНО ОДИН РАЗ; хранится только хеш</t>
-        </is>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>401 · 403</t>
-        </is>
-      </c>
-      <c r="M134" s="4" t="inlineStr">
-        <is>
-          <t>Выпуск сервисного ключа sak_… для внешней системы.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>GET /admin/mcp/manifest</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D135" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr"/>
-      <c r="G135" s="5" t="inlineStr"/>
-      <c r="H135" s="4" t="inlineStr"/>
-      <c r="I135" s="5" t="inlineStr"/>
-      <c r="J135" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K135" s="4" t="inlineStr"/>
-      <c r="L135" s="4" t="inlineStr"/>
-      <c r="M135" s="4" t="inlineStr">
-        <is>
-          <t>Машиночитаемое описание админ-инструментов (MCP) для агентских клиентов.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>GET /openapi.json, /docs, /redoc</t>
-        </is>
-      </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D136" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F136" s="5" t="inlineStr"/>
-      <c r="G136" s="5" t="inlineStr"/>
-      <c r="H136" s="4" t="inlineStr"/>
-      <c r="I136" s="5" t="inlineStr"/>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>нет (публичный)</t>
-        </is>
-      </c>
-      <c r="K136" s="4" t="inlineStr">
-        <is>
-          <t>Отдаётся только если включено на деплое</t>
-        </is>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>404, когда выключено</t>
-        </is>
-      </c>
-      <c r="M136" s="4" t="inlineStr">
-        <is>
-          <t>Машиночитаемая схема всего API — для генерации клиентов.</t>
+      <c r="K136" s="7" t="inlineStr">
+        <is>
+          <t>Сервисный ключ несёт ОДНУ роль в ОДНОМ скоупе (global/partner/product); деактивация действует со следующего запроса</t>
+        </is>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>401 unauthorized · 403 forbidden (вне скоупа)</t>
+        </is>
+      </c>
+      <c r="M136" s="7" t="inlineStr">
+        <is>
+          <t>Единая авторизация всего админ-контура. Для машин — ключ sak_…, который выдаётся человеком-админом и показывается ровно один раз.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>Исходящие</t>
+          <t>Admin API</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
+          <t>GET /admin/structure</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -7868,7 +7972,7 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Внешняя админка</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr"/>
@@ -7877,39 +7981,31 @@
       <c r="I137" s="5" t="inlineStr"/>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>Bearer &lt;player_api_key продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K137" s="4" t="inlineStr">
-        <is>
-          <t>Таймаут 8 с · срабатывает, когда снапшот старше часа · только публичные адреса (защита от SSRF, пиннинг IP)</t>
-        </is>
-      </c>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>Любая ошибка тиха: остаётся прежний снапшот</t>
-        </is>
-      </c>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K137" s="4" t="inlineStr"/>
+      <c r="L137" s="4" t="inlineStr"/>
       <c r="M137" s="4" t="inlineStr">
         <is>
-          <t>ЛЕНИВОЕ обновление профиля игрока перед ходом бота. Эндпойнт реализует ПАРТНЁР — это требование к чужой системе.</t>
+          <t>Дерево партнёров и продуктов — точка синхронизации справочников с внешними системами.</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>Исходящие</t>
-        </is>
-      </c>
-      <c r="B138" s="8" t="inlineStr">
-        <is>
-          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
-        </is>
-      </c>
-      <c r="C138" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>GET /admin/me</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
@@ -7917,54 +8013,42 @@
           <t>Выход</t>
         </is>
       </c>
-      <c r="E138" s="7" t="inlineStr">
-        <is>
-          <t>Наш сервис</t>
-        </is>
-      </c>
-      <c r="F138" s="8" t="inlineStr">
-        <is>
-          <t>player_id</t>
-        </is>
-      </c>
-      <c r="G138" s="8" t="inlineStr">
-        <is>
-          <t>query string</t>
-        </is>
-      </c>
-      <c r="H138" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I138" s="8" t="inlineStr">
-        <is>
-          <t>1048576</t>
-        </is>
-      </c>
-      <c r="J138" s="7" t="inlineStr"/>
-      <c r="K138" s="7" t="inlineStr"/>
-      <c r="L138" s="7" t="inlineStr"/>
-      <c r="M138" s="7" t="inlineStr">
-        <is>
-          <t>Кого запрашиваем.</t>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr"/>
+      <c r="G138" s="5" t="inlineStr"/>
+      <c r="H138" s="4" t="inlineStr"/>
+      <c r="I138" s="5" t="inlineStr"/>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K138" s="4" t="inlineStr"/>
+      <c r="L138" s="4" t="inlineStr"/>
+      <c r="M138" s="4" t="inlineStr">
+        <is>
+          <t>Кто вызывает и какие у него скоупы — для проверки прав на своей стороне.</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>Исходящие</t>
-        </is>
-      </c>
-      <c r="B139" s="8" t="inlineStr">
-        <is>
-          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
-        </is>
-      </c>
-      <c r="C139" s="7" t="inlineStr">
-        <is>
-          <t>Поле ответа</t>
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>POST /admin/partners, PUT /admin/partners/{id}</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
@@ -7972,49 +8056,41 @@
           <t>Вход</t>
         </is>
       </c>
-      <c r="E139" s="7" t="inlineStr">
-        <is>
-          <t>CRM казино</t>
-        </is>
-      </c>
-      <c r="F139" s="8" t="inlineStr">
-        <is>
-          <t>full_name, email, activation_status, country, balance, vip_level, registration_date, last_login_at, last_played_at, last_deposit_at</t>
-        </is>
-      </c>
-      <c r="G139" s="8" t="inlineStr">
-        <is>
-          <t>JSON-объект</t>
-        </is>
-      </c>
-      <c r="H139" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I139" s="8" t="inlineStr">
-        <is>
-          <t>{"full_name":"Андрей","balance":"150.00 USDT"}</t>
-        </is>
-      </c>
-      <c r="J139" s="7" t="inlineStr"/>
-      <c r="K139" s="7" t="inlineStr"/>
-      <c r="L139" s="7" t="inlineStr"/>
-      <c r="M139" s="7" t="inlineStr">
-        <is>
-          <t>Ожидаемый ответ партнёра. Лишние поля игнорируются — берётся тот же белый список, что и везде.</t>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr"/>
+      <c r="G139" s="5" t="inlineStr"/>
+      <c r="H139" s="4" t="inlineStr"/>
+      <c r="I139" s="5" t="inlineStr"/>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K139" s="4" t="inlineStr"/>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>401 · 403</t>
+        </is>
+      </c>
+      <c r="M139" s="4" t="inlineStr">
+        <is>
+          <t>Заведение и правка партнёра.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>Исходящие</t>
+          <t>Admin API</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Telegram Bot API</t>
+          <t>POST /admin/products</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -8022,14 +8098,14 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D140" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Внешняя админка</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr"/>
@@ -8038,77 +8114,869 @@
       <c r="I140" s="5" t="inlineStr"/>
       <c r="J140" s="4" t="inlineStr">
         <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>Создание продукта автоматически засевает рабочую конфигурацию</t>
+        </is>
+      </c>
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>401 · 403</t>
+        </is>
+      </c>
+      <c r="M140" s="4" t="inlineStr">
+        <is>
+          <t>Заведение казино. В ответе — публичный widget_key для встраивания виджета.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>PUT /admin/products/{id}</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>name, active, site_url, turnstile_site_key</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>string / bool</t>
+        </is>
+      </c>
+      <c r="H141" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I141" s="8" t="inlineStr">
+        <is>
+          <t>{"site_url":"https://brand.com"}</t>
+        </is>
+      </c>
+      <c r="J141" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K141" s="7" t="inlineStr"/>
+      <c r="L141" s="7" t="inlineStr"/>
+      <c r="M141" s="7" t="inlineStr">
+        <is>
+          <t>Публичная конфигурация продукта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>PUT /admin/products/{id}/secrets</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F142" s="8" t="inlineStr">
+        <is>
+          <t>openai_key_primary, openai_key_fallback, handshake_secret, telegram_bot_token, player_api_key, turnstile_secret</t>
+        </is>
+      </c>
+      <c r="G142" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H142" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I142" s="8" t="inlineStr">
+        <is>
+          <t>{"handshake_secret":"…"}</t>
+        </is>
+      </c>
+      <c r="J142" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K142" s="7" t="inlineStr">
+        <is>
+          <t>Только запись: наружу возвращаются лишь флаги «задан/не задан»</t>
+        </is>
+      </c>
+      <c r="L142" s="7" t="inlineStr"/>
+      <c r="M142" s="7" t="inlineStr">
+        <is>
+          <t>Секреты продукта. Хранятся зашифрованными; через API не читаются.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>POST /admin/products/{id}/widget-key</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr"/>
+      <c r="G143" s="5" t="inlineStr"/>
+      <c r="H143" s="4" t="inlineStr"/>
+      <c r="I143" s="5" t="inlineStr"/>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr"/>
+      <c r="L143" s="4" t="inlineStr"/>
+      <c r="M143" s="4" t="inlineStr">
+        <is>
+          <t>Ротация публичного ключа виджета.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>GET /admin/overview, /timeseries, /by-topic, /by-language</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr"/>
+      <c r="G144" s="5" t="inlineStr"/>
+      <c r="H144" s="4" t="inlineStr"/>
+      <c r="I144" s="5" t="inlineStr"/>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>Параметры периода from/to, скоуп product_id</t>
+        </is>
+      </c>
+      <c r="L144" s="4" t="inlineStr"/>
+      <c r="M144" s="4" t="inlineStr">
+        <is>
+          <t>Метрики поддержки для выгрузки во внешнюю аналитику.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>GET /admin/ai-costs</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr"/>
+      <c r="G145" s="5" t="inlineStr"/>
+      <c r="H145" s="4" t="inlineStr"/>
+      <c r="I145" s="5" t="inlineStr"/>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>Разрез по типу вызова: chat | agent | review | media</t>
+        </is>
+      </c>
+      <c r="L145" s="4" t="inlineStr"/>
+      <c r="M145" s="4" t="inlineStr">
+        <is>
+          <t>Полные траты на ИИ — сумма сходится со счётом провайдера.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>GET /admin/sessions, /admin/session/{id}</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr"/>
+      <c r="G146" s="5" t="inlineStr"/>
+      <c r="H146" s="4" t="inlineStr"/>
+      <c r="I146" s="5" t="inlineStr"/>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>Пагинация page/page_size</t>
+        </is>
+      </c>
+      <c r="L146" s="4" t="inlineStr"/>
+      <c r="M146" s="4" t="inlineStr">
+        <is>
+          <t>Журнал диалогов и полная стенограмма с постоимостью — выгрузка в общее хранилище обращений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>GET /admin/audit</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D147" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr"/>
+      <c r="G147" s="5" t="inlineStr"/>
+      <c r="H147" s="4" t="inlineStr"/>
+      <c r="I147" s="5" t="inlineStr"/>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K147" s="4" t="inlineStr"/>
+      <c r="L147" s="4" t="inlineStr"/>
+      <c r="M147" s="4" t="inlineStr">
+        <is>
+          <t>Аудит административных изменений — для общего SIEM/комплаенс-контура.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>GET /admin/quality/overview, /admin/quality/reviews</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D148" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr"/>
+      <c r="G148" s="5" t="inlineStr"/>
+      <c r="H148" s="4" t="inlineStr"/>
+      <c r="I148" s="5" t="inlineStr"/>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr"/>
+      <c r="L148" s="4" t="inlineStr"/>
+      <c r="M148" s="4" t="inlineStr">
+        <is>
+          <t>Оценки качества диалогов (1..5, теги, пробелы в базе знаний).</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>GET /admin/retention/overview, /funnel, /effectiveness</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D149" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr"/>
+      <c r="G149" s="5" t="inlineStr"/>
+      <c r="H149" s="4" t="inlineStr"/>
+      <c r="I149" s="5" t="inlineStr"/>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K149" s="4" t="inlineStr"/>
+      <c r="L149" s="4" t="inlineStr"/>
+      <c r="M149" s="4" t="inlineStr">
+        <is>
+          <t>Метрики Telegram-фасада: воронка и результативность касаний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>POST /admin/api-keys</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr"/>
+      <c r="G150" s="5" t="inlineStr"/>
+      <c r="H150" s="4" t="inlineStr"/>
+      <c r="I150" s="5" t="inlineStr"/>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>только человек-админ (ключом ключ не выпустить)</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>Открытый текст ключа возвращается РОВНО ОДИН РАЗ; хранится только хеш</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>401 · 403</t>
+        </is>
+      </c>
+      <c r="M150" s="4" t="inlineStr">
+        <is>
+          <t>Выпуск сервисного ключа sak_… для внешней системы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>GET /admin/mcp/manifest</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D151" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr"/>
+      <c r="G151" s="5" t="inlineStr"/>
+      <c r="H151" s="4" t="inlineStr"/>
+      <c r="I151" s="5" t="inlineStr"/>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="inlineStr"/>
+      <c r="L151" s="4" t="inlineStr"/>
+      <c r="M151" s="4" t="inlineStr">
+        <is>
+          <t>Машиночитаемое описание админ-инструментов (MCP) для агентских клиентов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>GET /openapi.json, /docs, /redoc</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr"/>
+      <c r="G152" s="5" t="inlineStr"/>
+      <c r="H152" s="4" t="inlineStr"/>
+      <c r="I152" s="5" t="inlineStr"/>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>нет (публичный)</t>
+        </is>
+      </c>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>Отдаётся только если включено на деплое</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="inlineStr">
+        <is>
+          <t>404, когда выключено</t>
+        </is>
+      </c>
+      <c r="M152" s="4" t="inlineStr">
+        <is>
+          <t>Машиночитаемая схема всего API — для генерации клиентов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr"/>
+      <c r="G153" s="5" t="inlineStr"/>
+      <c r="H153" s="4" t="inlineStr"/>
+      <c r="I153" s="5" t="inlineStr"/>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;player_api_key продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>Таймаут 8 с · срабатывает, когда снапшот старше часа · только публичные адреса (защита от SSRF, пиннинг IP)</t>
+        </is>
+      </c>
+      <c r="L153" s="4" t="inlineStr">
+        <is>
+          <t>Любая ошибка тиха: остаётся прежний снапшот</t>
+        </is>
+      </c>
+      <c r="M153" s="4" t="inlineStr">
+        <is>
+          <t>ЛЕНИВОЕ обновление профиля игрока перед ходом бота. Эндпойнт реализует ПАРТНЁР — это требование к чужой системе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F154" s="8" t="inlineStr">
+        <is>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="G154" s="8" t="inlineStr">
+        <is>
+          <t>query string</t>
+        </is>
+      </c>
+      <c r="H154" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I154" s="8" t="inlineStr">
+        <is>
+          <t>1048576</t>
+        </is>
+      </c>
+      <c r="J154" s="7" t="inlineStr"/>
+      <c r="K154" s="7" t="inlineStr"/>
+      <c r="L154" s="7" t="inlineStr"/>
+      <c r="M154" s="7" t="inlineStr">
+        <is>
+          <t>Кого запрашиваем.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="inlineStr">
+        <is>
+          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F155" s="8" t="inlineStr">
+        <is>
+          <t>full_name, email, activation_status, country, balance, vip_level, registration_date, last_login_at, last_played_at, last_deposit_at</t>
+        </is>
+      </c>
+      <c r="G155" s="8" t="inlineStr">
+        <is>
+          <t>JSON-объект</t>
+        </is>
+      </c>
+      <c r="H155" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I155" s="8" t="inlineStr">
+        <is>
+          <t>{"full_name":"Андрей","balance":"150.00 USDT"}</t>
+        </is>
+      </c>
+      <c r="J155" s="7" t="inlineStr"/>
+      <c r="K155" s="7" t="inlineStr"/>
+      <c r="L155" s="7" t="inlineStr"/>
+      <c r="M155" s="7" t="inlineStr">
+        <is>
+          <t>Ожидаемый ответ партнёра. Лишние поля игнорируются — берётся тот же белый список, что и везде.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>Telegram Bot API</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr"/>
+      <c r="G156" s="5" t="inlineStr"/>
+      <c r="H156" s="4" t="inlineStr"/>
+      <c r="I156" s="5" t="inlineStr"/>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
           <t>токен бота продукта (хранится зашифрованным)</t>
         </is>
       </c>
-      <c r="K140" s="4" t="inlineStr">
+      <c r="K156" s="4" t="inlineStr">
         <is>
           <t>Ретраи; недоступный игрок помечается как unreachable</t>
         </is>
       </c>
-      <c r="L140" s="4" t="inlineStr"/>
-      <c r="M140" s="4" t="inlineStr">
+      <c r="L156" s="4" t="inlineStr"/>
+      <c r="M156" s="4" t="inlineStr">
         <is>
           <t>sendMessage / sendPhoto / sendVideo / getChatMember / setWebhook.</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="4" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
         <is>
           <t>Исходящие</t>
         </is>
       </c>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="B157" s="5" t="inlineStr">
         <is>
           <t>OpenAI API</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="C157" s="4" t="inlineStr">
         <is>
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D141" s="10" t="inlineStr">
+      <c r="D157" s="10" t="inlineStr">
         <is>
           <t>Выход</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
+      <c r="E157" s="4" t="inlineStr">
         <is>
           <t>Наш сервис</t>
         </is>
       </c>
-      <c r="F141" s="5" t="inlineStr"/>
-      <c r="G141" s="5" t="inlineStr"/>
-      <c r="H141" s="4" t="inlineStr"/>
-      <c r="I141" s="5" t="inlineStr"/>
-      <c r="J141" s="4" t="inlineStr">
+      <c r="F157" s="5" t="inlineStr"/>
+      <c r="G157" s="5" t="inlineStr"/>
+      <c r="H157" s="4" t="inlineStr"/>
+      <c r="I157" s="5" t="inlineStr"/>
+      <c r="J157" s="4" t="inlineStr">
         <is>
           <t>ключ продукта (1–2 шт.), иначе ключ деплоя</t>
         </is>
       </c>
-      <c r="K141" s="4" t="inlineStr">
+      <c r="K157" s="4" t="inlineStr">
         <is>
           <t>Два ключа с автопереключением; предохранитель при сбое провайдера; таймауты по назначению вызова</t>
         </is>
       </c>
-      <c r="L141" s="4" t="inlineStr"/>
-      <c r="M141" s="4" t="inlineStr">
+      <c r="L157" s="4" t="inlineStr"/>
+      <c r="M157" s="4" t="inlineStr">
         <is>
           <t>Генерация ответов и фоновые проходы. Каждый вызов логируется с атрибуцией расходов.</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Файл генерируется из кода: scripts/build_api_reference.py. Живая версия — /integration-reference на самом сервисе.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M141"/>
+  <autoFilter ref="A4:M157"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/frontend/api-reference.xlsx
+++ b/frontend/api-reference.xlsx
@@ -10,7 +10,7 @@
     <sheet name="API" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API'!$A$4:$M$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API'!$A$4:$M$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M159"/>
+  <dimension ref="A1:M172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -647,7 +647,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>429 rate_limited · 403 bad_widget_key | no_product | turnstile_failed · 401 bad_handshake · 411/413 кап тела (64 KiB)</t>
+          <t>429 rate_limited · 403 bad_widget_key | no_product | turnstile_failed · 401 bad_handshake · 411 length_required / 413 кап тела (настройка body_max_bytes, по умолч. 64 KiB; действует на ВСЕ ручки)</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>429 rate_limited · 403 bad_widget_key</t>
+          <t>429 rate_limited · 403 bad_widget_key | no_product</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -1380,37 +1380,37 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Сайт / виджет</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>widget_key</t>
+          <t>topics / lang / languages</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>query string</t>
+          <t>[{slug,title,order}] / string / [string]</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>условно</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>wk_7f3a…</t>
+          <t>{"topics":[…],"lang":"ru","languages":["en","ru"]}</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr"/>
@@ -1418,7 +1418,7 @@
       <c r="L19" s="7" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>Продукт, чей каталог отдать.</t>
+          <t>Каталог тем (other всегда последняя), язык заголовков и список поддерживаемых языков.</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>lang | locale</t>
+          <t>widget_key</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>условно</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>ru</t>
+          <t>wk_7f3a…</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr"/>
@@ -1473,113 +1473,113 @@
       <c r="L20" s="7" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr">
         <is>
+          <t>Продукт, чей каталог отдать.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Chat API</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/chat/topics</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Сайт / виджет</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>lang | locale</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>query string</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>ru</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
           <t>Язык заголовков тем.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Chat API</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>GET /api/chat/i18n</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>Выход</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Сайт / виджет</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>нет (публичный)</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Лимит catalogue:{ip} (600) · Cache-Control 60 с</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>429 · 403 bad_widget_key</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>429 · 403 bad_widget_key | no_product</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Строки интерфейса + публичный ключ Turnstile продукта. Позволяет менять тексты и капчу без редеплоя клиента.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Chat API</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>GET /api/chat/i18n</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>Наш сервис</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>strings</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>{lang: {key: string}}</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>{"ru":{"send":"Отправить"}}</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr"/>
-      <c r="K22" s="7" t="inlineStr"/>
-      <c r="L22" s="7" t="inlineStr"/>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>Копия интерфейса по языкам.</t>
         </is>
       </c>
     </row>
@@ -1611,22 +1611,22 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>turnstile_site_key</t>
+          <t>strings</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>string|null</t>
+          <t>{lang: {key: string}}</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>0x4AAA…</t>
+          <t>{"ru":{"send":"Отправить"}}</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr"/>
@@ -1634,58 +1634,62 @@
       <c r="L23" s="7" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr">
         <is>
+          <t>Копия интерфейса по языкам.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Chat API</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/chat/i18n</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>turnstile_site_key</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>string|null</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>0x4AAA…</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr"/>
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
           <t>Публичный ключ капчи продукта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Chat API</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>POST /api/chat/topic</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Клиент чата</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;session token&gt; (JWT HS256)</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Общий бюджет chat-op:{ip} (300) на все сессионные ручки кроме /message</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>401 unauthorized · 404 not_found · 409 session_closed · 400 bad_topic · 429</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>Выбор темы: подгружает базу знаний темы и сдвигает границу истории.</t>
         </is>
       </c>
     </row>
@@ -1697,32 +1701,32 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>POST /api/chat/topic</t>
+          <t>GET /api/chat/i18n</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Клиент чата</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>languages</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>[string]</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -1732,119 +1736,119 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>3f6d1c2e-…</t>
+          <t>["en","ru","es"]</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr"/>
       <c r="K25" s="7" t="inlineStr"/>
       <c r="L25" s="7" t="inlineStr"/>
-      <c r="M25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>Поддерживаемые языки продукта.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Chat API</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>POST /api/chat/topic</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Клиент чата</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;session token&gt; (JWT HS256)</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Общий бюджет chat-op:{ip} (300) на все сессионные ручки кроме /message</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>401 unauthorized · 404 not_found · 409 session_closed · 400 bad_topic · 429</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Выбор темы: подгружает базу знаний темы и сдвигает границу истории.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Chat API</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/chat/topic</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Поле запроса</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Клиент чата</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>topic_slug</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>withdrawals</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr"/>
-      <c r="K26" s="7" t="inlineStr"/>
-      <c r="L26" s="7" t="inlineStr"/>
-      <c r="M26" s="7" t="inlineStr">
-        <is>
-          <t>Slug из каталога тем.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Chat API</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>POST /api/chat/message</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Клиент чата</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;session token&gt; (JWT HS256)</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Порядок гейтов: токен → открытость сессии → лимит по IP → кулдаун → длина → пустое сообщение → инъекция → кап ходов → эскалация по ключевым словам → вызов модели</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>401 · 409 session_closed · 429 rate_limited | cooldown · 400 too_long | rejected</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>Один ход диалога. Пишется атомарно: сообщения + счётчик + лог вызова ИИ.</t>
-        </is>
-      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>3f6d1c2e-…</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr"/>
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -1854,7 +1858,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>POST /api/chat/message</t>
+          <t>POST /api/chat/topic</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -1874,12 +1878,12 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>session_id</t>
+          <t>topic_slug</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -1889,66 +1893,66 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>3f6d1c2e-…</t>
+          <t>withdrawals</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr"/>
       <c r="K28" s="7" t="inlineStr"/>
       <c r="L28" s="7" t="inlineStr"/>
-      <c r="M28" s="7" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>Slug из каталога тем.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Chat API</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>POST /api/chat/message</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Клиент чата</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>string (≤500 симв. по умолч.)</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>Как вывести деньги?</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr"/>
-      <c r="K29" s="7" t="inlineStr"/>
-      <c r="L29" s="7" t="inlineStr"/>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>Сообщение игрока. Предел — настройка продукта.</t>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;session token&gt; (JWT HS256)</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Порядок гейтов: токен → открытость сессии → лимит по IP → кулдаун → длина/пустое → малосодержательное (модельный ответ не зовётся, возвращается 200-подсказка) → инъекция → жёсткий потолок ходов (2x мягкого капа) → эскалация по ключевым словам → вызов модели</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>401 · 409 session_closed · 429 rate_limited | cooldown · 400 too_long | empty | rejected</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Один ход диалога. Пишется атомарно: сообщения + счётчик + лог вызова ИИ. ВАЖНО: модельно-независимые ответы (малосодержательное сообщение, жёсткий потолок) возвращают только {reply, lang, escalation, message_count} — остальные ключи ОТСУТСТВУЮТ, клиент обязан читать их опционально.</t>
         </is>
       </c>
     </row>
@@ -1980,32 +1984,28 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>closing</t>
+          <t>session_id</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>3f6d1c2e-…</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr"/>
       <c r="K30" s="7" t="inlineStr"/>
       <c r="L30" s="7" t="inlineStr"/>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>Игрок нажал «Проблема решена» — ход трактуется как прощание.</t>
-        </is>
-      </c>
+      <c r="M30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -2020,27 +2020,27 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Клиент чата</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>reply</t>
+          <t>text</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>string (Markdown-подмножество)</t>
+          <t>string (≤500 симв. по умолч.)</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>Вывод занимает до 24 часов…</t>
+          <t>Как вывести деньги?</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr"/>
@@ -2058,7 +2058,7 @@
       <c r="L31" s="7" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>Ответ. Поддерживаются **жирный**, *курсив*, `код`, ссылки, списки. Пустая строка = ход-маршрутизация или эскалация.</t>
+          <t>Сообщение игрока. Предел — настройка продукта.</t>
         </is>
       </c>
     </row>
@@ -2075,37 +2075,37 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Клиент чата</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>lang</t>
+          <t>closing</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>string (ISO 639-1)</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>ru</t>
+          <t>false</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
       <c r="L32" s="7" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr">
         <is>
-          <t>Язык ответа. Может меняться посреди диалога — интерфейс должен следовать.</t>
+          <t>Игрок нажал «Проблема решена» — ход трактуется как прощание.</t>
         </is>
       </c>
     </row>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>message_count</t>
+          <t>reply</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string (Markdown-подмножество)</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Вывод занимает до 24 часов…</t>
         </is>
       </c>
       <c r="J33" s="7" t="inlineStr"/>
@@ -2168,7 +2168,7 @@
       <c r="L33" s="7" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>Счётчик ходов; на пределе включается передача человеку.</t>
+          <t>Ответ. Поддерживаются **жирный**, *курсив*, `код`, ссылки, списки. Пустая строка = ход-маршрутизация или эскалация.</t>
         </is>
       </c>
     </row>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>escalation</t>
+          <t>lang</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>{active,final,message,button:{label,url},retention?}</t>
+          <t>string (ISO 639-1)</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>{"active":true,"final":true,…}</t>
+          <t>ru</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr"/>
@@ -2223,7 +2223,7 @@
       <c r="L34" s="7" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>Блок передачи на человека. Поля описаны отдельными строками ниже.</t>
+          <t>Язык ответа. Может меняться посреди диалога — интерфейс должен следовать.</t>
         </is>
       </c>
     </row>
@@ -2255,22 +2255,22 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>suggested_topic</t>
+          <t>message_count</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>{slug,title}|null</t>
+          <t>int</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>{"slug":"bonuses","title":"Бонусы"}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr"/>
@@ -2278,7 +2278,7 @@
       <c r="L35" s="7" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>ОБЯЗАТЕЛЬНАЯ клиентская логика: вызвать POST /topic и переспросить исходный вопрос. При этом reply пустой — без обработки чат «зависнет».</t>
+          <t>Счётчик ходов; на пределе включается передача человеку.</t>
         </is>
       </c>
     </row>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>suggestions</t>
+          <t>escalation</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>[string] (≤2)</t>
+          <t>{active,final,message,button:{label,url},retention?}</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>["Какие лимиты на вывод?"]</t>
+          <t>{"active":true,"final":true,…}</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr"/>
@@ -2333,7 +2333,7 @@
       <c r="L36" s="7" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>Уточняющие вопросы от лица игрока — кнопки в один тап.</t>
+          <t>Блок передачи на человека. Поля описаны отдельными строками ниже.</t>
         </is>
       </c>
     </row>
@@ -2365,12 +2365,12 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>closing_suggestion</t>
+          <t>suggested_topic</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>string|null</t>
+          <t>{slug,title}|null</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>Проблема решена.</t>
+          <t>{"slug":"bonuses","title":"Бонусы"}</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr"/>
@@ -2388,7 +2388,7 @@
       <c r="L37" s="7" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>Системная опция завершения: отправить ход с closing=true, затем /resolve.</t>
+          <t>ОБЯЗАТЕЛЬНАЯ клиентская логика: вызвать POST /topic и переспросить исходный вопрос. При этом reply пустой — без обработки чат «зависнет».</t>
         </is>
       </c>
     </row>
@@ -2420,22 +2420,22 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>[string] (≤2)</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>["Какие лимиты на вывод?"]</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
       <c r="L38" s="7" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>Вопрос выглядит закрытым — показать кнопку «завершить чат».</t>
+          <t>Уточняющие вопросы от лица игрока — кнопки в один тап.</t>
         </is>
       </c>
     </row>
@@ -2475,12 +2475,12 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>cap_notice</t>
+          <t>closing_suggestion</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>{message,escalate_label,finish_label}|null</t>
+          <t>string|null</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>{"message":"…","escalate_label":"Передать вопрос человеку","finish_label":"Завершить чат"}</t>
+          <t>Проблема решена.</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr"/>
@@ -2498,24 +2498,24 @@
       <c r="L39" s="7" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>Мягкий лимит сообщений достигнут (или resolved на последних ~2 ходах перед ним): показать предупреждение и две кнопки — эскалация (POST /escalate) сверху и завершение (POST /resolve) ниже — вместо suggestions/resolved. Чат остаётся открытым; на 2x лимита сессия закрывается принудительно.</t>
+          <t>Системная опция завершения: отправить ход с closing=true, затем /resolve.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Chat API</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>GET /api/chat/session/{id}</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/chat/message</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
@@ -2523,33 +2523,37 @@
           <t>Выход</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Клиент чата</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;session token&gt; (JWT HS256)</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>Бюджет chat-op:{ip} (300)</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>401 · 404 · 429</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>Возобновление диалога: статус и до 50 последних сообщений.</t>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>условно</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr"/>
+      <c r="K40" s="7" t="inlineStr"/>
+      <c r="L40" s="7" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>Вопрос выглядит закрытым — показать кнопку «завершить чат». В модельно-независимых ответах ключ отсутствует.</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2565,7 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>GET /api/chat/session/{id}</t>
+          <t>POST /api/chat/message</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -2581,22 +2585,22 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>cap_notice</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>'open'|'resolved'|'escalated'</t>
+          <t>{message,escalate_label,finish_label}|null</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>{"message":"…","escalate_label":"Передать вопрос человеку","finish_label":"Завершить чат"}</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr"/>
@@ -2604,164 +2608,168 @@
       <c r="L41" s="7" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr">
         <is>
+          <t>Мягкий лимит сообщений достигнут (или resolved на последних ~2 ходах перед ним): показать предупреждение и две кнопки — эскалация (POST /escalate) сверху и завершение (POST /resolve) ниже — вместо suggestions/resolved. Чат остаётся открытым; на 2x лимита сессия закрывается принудительно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Chat API</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>GET /api/chat/session/{id}</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Клиент чата</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;session token&gt; (JWT HS256)</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>Бюджет chat-op:{ip} (300)</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>401 · 404 · 429</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>Возобновление диалога: статус и до 50 последних сообщений.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Chat API</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>GET /api/chat/session/{id}</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>'open'|'resolved'|'escalated'</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr"/>
+      <c r="K43" s="7" t="inlineStr"/>
+      <c r="L43" s="7" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
           <t>Только open допускает новые ходы; иначе 409.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>Chat API</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>GET /api/chat/session/{id}</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>Поле ответа</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>Выход</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>Наш сервис</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>history</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>[{role,content,lang}]</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>[{"role":"user","content":"…"}]</t>
         </is>
       </c>
-      <c r="J42" s="7" t="inlineStr"/>
-      <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr"/>
-      <c r="M42" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr"/>
+      <c r="K44" s="7" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr">
         <is>
           <t>role ∈ user|assistant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Chat API</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>POST /api/chat/escalate</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Клиент чата</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr"/>
-      <c r="G43" s="5" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;session token&gt; (JWT HS256)</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>Бюджет chat-op:{ip} (300)</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>401 · 404 · 409 · 429</t>
-        </is>
-      </c>
-      <c r="M43" s="4" t="inlineStr">
-        <is>
-          <t>Явный запрос человека: жёсткая эскалация, сессия закрывается.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Chat API</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>POST /api/chat/resolve</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Клиент чата</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;session token&gt; (JWT HS256)</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>Идемпотентно; не перекрывает уже эскалированную сессию</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>401 · 404 · 429</t>
-        </is>
-      </c>
-      <c r="M44" s="4" t="inlineStr">
-        <is>
-          <t>Игрок завершил чат.</t>
         </is>
       </c>
     </row>
@@ -2773,54 +2781,50 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Контракт: user_context / signed_context</t>
+          <t>GET /api/chat/session/{id}</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Сайт / виджет</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>session_id / escalated / lang / message_count</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>uuid / bool / string / int</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>1048576</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>подпись HMAC-SHA256 секретом продукта</t>
-        </is>
-      </c>
+          <t>{"escalated":false,"lang":"ru","message_count":4}</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr"/>
       <c r="K45" s="7" t="inlineStr"/>
       <c r="L45" s="7" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>Идентификатор игрока в казино. Белый список полей, которые видит модель. Всё остальное отбрасывается — расширение списка требует правки на нашей стороне.</t>
+          <t>Остальные поля возобновления: идентификатор, признак эскалации, язык сессии и счётчик ходов.</t>
         </is>
       </c>
     </row>
@@ -2832,130 +2836,118 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Контракт: user_context / signed_context</t>
+          <t>POST /api/chat/topic</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Сайт / виджет</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>Андрей Петров</t>
-        </is>
-      </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>подпись HMAC-SHA256 секретом продукта</t>
-        </is>
-      </c>
+          <t>{"ok":true}</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr"/>
       <c r="K46" s="7" t="inlineStr"/>
       <c r="L46" s="7" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>Полное имя; из него берётся имя для приветствия.</t>
+          <t>Подтверждение выбора темы.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Chat API</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>Контракт: user_context / signed_context</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>Сайт / виджет</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I47" s="8" t="inlineStr">
-        <is>
-          <t>player@example.com</t>
-        </is>
-      </c>
-      <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>подпись HMAC-SHA256 секретом продукта</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="inlineStr"/>
-      <c r="L47" s="7" t="inlineStr"/>
-      <c r="M47" s="7" t="inlineStr">
-        <is>
-          <t>Почта игрока.</t>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>POST /api/chat/escalate</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Клиент чата</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;session token&gt; (JWT HS256)</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>Бюджет chat-op:{ip} (300)</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>401 · 404 · 409 · 429</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>Явный запрос человека: жёсткая эскалация, сессия закрывается. Ответ — {escalation: {…}} (контракт escalation ниже).</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Chat API</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Контракт: user_context / signed_context</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>POST /api/chat/resolve</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
@@ -2963,41 +2955,33 @@
           <t>Вход</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>Сайт / виджет</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>activation_status</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I48" s="8" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="J48" s="7" t="inlineStr">
-        <is>
-          <t>подпись HMAC-SHA256 секретом продукта</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr"/>
-      <c r="L48" s="7" t="inlineStr"/>
-      <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>Статус активации/верификации.</t>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Клиент чата</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;session token&gt; (JWT HS256)</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>Идемпотентно; не перекрывает уже эскалированную сессию · бюджет chat-op:{ip} (300)</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>401 · 404 · 429</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>Игрок завершил чат. Ответ — {"ok":true,"status":"resolved"}.</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3013,7 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>id</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -3044,7 +3028,7 @@
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>1048576</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
@@ -3056,7 +3040,7 @@
       <c r="L49" s="7" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>Страна.</t>
+          <t>Идентификатор игрока в казино. Белый список полей, которые видит модель. Всё остальное отбрасывается — расширение списка требует правки на нашей стороне.</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3072,7 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
@@ -3103,7 +3087,7 @@
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>150.00 USDT</t>
+          <t>Андрей Петров</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
@@ -3115,7 +3099,7 @@
       <c r="L50" s="7" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>Баланс строкой, вместе с валютой.</t>
+          <t>Полное имя; из него берётся имя для приветствия.</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3131,7 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>vip_level</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -3162,7 +3146,7 @@
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>player@example.com</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
@@ -3174,7 +3158,7 @@
       <c r="L51" s="7" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>VIP-класс.</t>
+          <t>Почта игрока.</t>
         </is>
       </c>
     </row>
@@ -3206,12 +3190,12 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>registration_date</t>
+          <t>activation_status</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>string (ISO-8601)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
@@ -3221,7 +3205,7 @@
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
@@ -3233,7 +3217,7 @@
       <c r="L52" s="7" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>Дата регистрации.</t>
+          <t>Статус активации/верификации.</t>
         </is>
       </c>
     </row>
@@ -3265,38 +3249,34 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>iat</t>
+          <t>country</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>int (unix seconds)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>условно</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>1769606400</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>часть подписанного payload</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>Возраст токена ограничен 300 с</t>
-        </is>
-      </c>
+          <t>подпись HMAC-SHA256 секретом продукта</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr"/>
       <c r="L53" s="7" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>Момент выпуска подписи (антиреплей).</t>
+          <t>Страна.</t>
         </is>
       </c>
     </row>
@@ -3328,38 +3308,34 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>exp</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>int (unix seconds)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>1769606700</t>
+          <t>150.00 USDT</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>часть подписанного payload</t>
+          <t>подпись HMAC-SHA256 секретом продукта</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>401 bad_handshake при истечении</t>
-        </is>
-      </c>
+      <c r="L54" s="7" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>Срок годности подписи.</t>
+          <t>Баланс строкой, вместе с валютой.</t>
         </is>
       </c>
     </row>
@@ -3371,50 +3347,54 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Контракт: escalation</t>
+          <t>Контракт: user_context / signed_context</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Сайт / виджет</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>vip_level</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr"/>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>подпись HMAC-SHA256 секретом продукта</t>
+        </is>
+      </c>
       <c r="K55" s="7" t="inlineStr"/>
       <c r="L55" s="7" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>Есть ли в этом ходе передача на человека.</t>
+          <t>VIP-класс.</t>
         </is>
       </c>
     </row>
@@ -3426,50 +3406,54 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Контракт: escalation</t>
+          <t>Контракт: user_context / signed_context</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Сайт / виджет</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>final</t>
+          <t>registration_date</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string (ISO-8601)</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="inlineStr"/>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>подпись HMAC-SHA256 секретом продукта</t>
+        </is>
+      </c>
       <c r="K56" s="7" t="inlineStr"/>
       <c r="L56" s="7" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>true — сессия закрыта (дальше 409); false — карточка показана, диалог продолжается.</t>
+          <t>Дата регистрации.</t>
         </is>
       </c>
     </row>
@@ -3481,32 +3465,32 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Контракт: escalation</t>
+          <t>Контракт: user_context / signed_context</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Сайт / виджет</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>iat</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int (unix seconds)</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -3516,15 +3500,23 @@
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>Передаю вас специалисту…</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="inlineStr"/>
-      <c r="K57" s="7" t="inlineStr"/>
+          <t>1769606400</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>часть подписанного payload</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>Возраст токена ограничен 300 с</t>
+        </is>
+      </c>
       <c r="L57" s="7" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>Текст карточки на языке ответа.</t>
+          <t>Момент выпуска подписи (антиреплей).</t>
         </is>
       </c>
     </row>
@@ -3536,50 +3528,58 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Контракт: escalation</t>
+          <t>Контракт: user_context / signed_context</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Сайт / виджет</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>button.label</t>
+          <t>exp</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int (unix seconds)</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>условно</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>Написать в поддержку</t>
-        </is>
-      </c>
-      <c r="J58" s="7" t="inlineStr"/>
+          <t>1769606700</t>
+        </is>
+      </c>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>часть подписанного payload</t>
+        </is>
+      </c>
       <c r="K58" s="7" t="inlineStr"/>
-      <c r="L58" s="7" t="inlineStr"/>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>401 bad_handshake при истечении</t>
+        </is>
+      </c>
       <c r="M58" s="7" t="inlineStr">
         <is>
-          <t>Подпись кнопки.</t>
+          <t>Срок годности подписи.</t>
         </is>
       </c>
     </row>
@@ -3611,22 +3611,22 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>button.url</t>
+          <t>active</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>string (URL)</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>условно</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>https://t.me/brand_bot?start=…</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr"/>
@@ -3634,7 +3634,7 @@
       <c r="L59" s="7" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>Куда ведёт кнопка: статическая ссылка контакта или одноразовый диплинк в Telegram-бота.</t>
+          <t>Есть ли в этом ходе передача на человека.</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>retention</t>
+          <t>final</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
@@ -3689,164 +3689,164 @@
       <c r="L60" s="7" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr">
         <is>
-          <t>Признак, что передача ведёт в Telegram-бота, а не на статическую ссылку.</t>
+          <t>true — сессия закрыта (дальше 409); false — карточка показана, диалог продолжается.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>Partner API</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>POST /partner/{product_id}/player-update</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>CRM казино</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr"/>
-      <c r="G61" s="5" t="inlineStr"/>
-      <c r="H61" s="4" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K61" s="4" t="inlineStr">
-        <is>
-          <t>Частичное обновление: поля со значением null не затираются · лимит partner:{ip}</t>
-        </is>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>401 unauthorized (единый ответ на все причины) · 429 rate_limited</t>
-        </is>
-      </c>
-      <c r="M61" s="4" t="inlineStr">
-        <is>
-          <t>Push профиля игрока из CRM в наш снапшот.</t>
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Chat API</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Контракт: escalation</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>условно</t>
+        </is>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>Передаю вас специалисту…</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr"/>
+      <c r="K61" s="7" t="inlineStr"/>
+      <c r="L61" s="7" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t>Текст карточки на языке ответа.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>Partner API</t>
+          <t>Chat API</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/player-update</t>
+          <t>Контракт: escalation</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Заголовок</t>
-        </is>
-      </c>
-      <c r="D62" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>button.label</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>Bearer &lt;handshake_secret&gt;</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>условно</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>Bearer 8f2c…</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
+          <t>Написать в поддержку</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr"/>
       <c r="K62" s="7" t="inlineStr"/>
       <c r="L62" s="7" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>Тот же секрет продукта, что подписывает handshake.</t>
+          <t>Подпись кнопки.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Partner API</t>
+          <t>Chat API</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/player-update</t>
+          <t>Контракт: escalation</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>player_id</t>
+          <t>button.url</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string (URL)</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>условно</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>1048576</t>
+          <t>https://t.me/brand_bot?start=…</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr"/>
@@ -3854,44 +3854,44 @@
       <c r="L63" s="7" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>Ключ игрока на стороне казино.</t>
+          <t>Куда ведёт кнопка: статическая ссылка контакта или одноразовый диплинк в Telegram-бота.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>Partner API</t>
+          <t>Chat API</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/player-update</t>
+          <t>Контракт: escalation</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>retention</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>Андрей Петров</t>
+          <t>true</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr"/>
@@ -3909,24 +3909,24 @@
       <c r="L64" s="7" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>Поле профиля. null = не менять.</t>
+          <t>Признак, что передача ведёт в Telegram-бота, а не на статическую ссылку.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Partner API</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>POST /partner/{product_id}/player-update</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -3934,37 +3934,33 @@
           <t>Вход</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>CRM казино</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H65" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>player@example.com</t>
-        </is>
-      </c>
-      <c r="J65" s="7" t="inlineStr"/>
-      <c r="K65" s="7" t="inlineStr"/>
-      <c r="L65" s="7" t="inlineStr"/>
-      <c r="M65" s="7" t="inlineStr">
-        <is>
-          <t>Поле профиля. null = не менять.</t>
+      <c r="F65" s="5" t="inlineStr"/>
+      <c r="G65" s="5" t="inlineStr"/>
+      <c r="H65" s="4" t="inlineStr"/>
+      <c r="I65" s="5" t="inlineStr"/>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>Частичное обновление: поля со значением null не затираются · лимит partner:{ip}</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>401 unauthorized (единый ответ на все причины) · 422 invalid_rg_status · 429 rate_limited</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="inlineStr">
+        <is>
+          <t>Push профиля игрока из CRM в наш снапшот. Все вебхуки /partner/* лимитируются по IP ДО аутентификации.</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3977,7 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Заголовок</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -3996,30 +3992,34 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>activation_status</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Bearer &lt;handshake_secret&gt;</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="J66" s="7" t="inlineStr"/>
+          <t>Bearer 8f2c…</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
       <c r="K66" s="7" t="inlineStr"/>
       <c r="L66" s="7" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>Поле профиля. null = не менять.</t>
+          <t>Тот же секрет продукта, что подписывает handshake.</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>player_id</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>1048576</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       <c r="L67" s="7" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>Поле профиля. null = не менять.</t>
+          <t>Ключ игрока на стороне казино.</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>150.00 USDT</t>
+          <t>Андрей Петров</t>
         </is>
       </c>
       <c r="J68" s="7" t="inlineStr"/>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>vip_level</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>player@example.com</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr"/>
@@ -4216,12 +4216,12 @@
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>registration_date</t>
+          <t>activation_status</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>string (ISO-8601)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr"/>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>last_login_at</t>
+          <t>country</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>string (ISO-8601)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28T10:15:00Z</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr"/>
@@ -4294,7 +4294,7 @@
       <c r="L71" s="7" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>Последний вход — сигнал активности.</t>
+          <t>Поле профиля. null = не менять.</t>
         </is>
       </c>
     </row>
@@ -4326,12 +4326,12 @@
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>last_played_at</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>string (ISO-8601)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28T10:15:00Z</t>
+          <t>150.00 USDT</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr"/>
@@ -4349,7 +4349,7 @@
       <c r="L72" s="7" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>Последняя игра.</t>
+          <t>Поле профиля. null = не менять.</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>last_deposit_at</t>
+          <t>vip_level</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>string (ISO-8601)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="I73" s="8" t="inlineStr">
         <is>
-          <t>2026-07-28T10:15:00Z</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr"/>
@@ -4404,7 +4404,7 @@
       <c r="L73" s="7" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>Последний депозит.</t>
+          <t>Поле профиля. null = не менять.</t>
         </is>
       </c>
     </row>
@@ -4421,37 +4421,37 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D74" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>ok / updated</t>
+          <t>registration_date</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>bool / bool</t>
+          <t>string (ISO-8601)</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>{"ok":true,"updated":true}</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="J74" s="7" t="inlineStr"/>
@@ -4459,7 +4459,7 @@
       <c r="L74" s="7" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>Признак приёма и факта изменения.</t>
+          <t>Поле профиля. null = не менять.</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>rg_status</t>
+          <t>last_login_at</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string (ISO-8601)</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>self_exclude</t>
+          <t>2026-07-28T10:15:00Z</t>
         </is>
       </c>
       <c r="J75" s="7" t="inlineStr"/>
@@ -4514,7 +4514,7 @@
       <c r="L75" s="7" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>RG-статус игрока: ok | cool_off | rg_hold | self_exclude. Источник истины по самоисключению — платформа казино; self_exclude/rg_hold полностью блокируют проактив и бонусы. Слать при каждой смене + первичный бэкфилл.</t>
+          <t>Последний вход — сигнал активности.</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>rg_status_until</t>
+          <t>last_played_at</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>2026-10-01T00:00:00Z</t>
+          <t>2026-07-28T10:15:00Z</t>
         </is>
       </c>
       <c r="J76" s="7" t="inlineStr"/>
@@ -4569,7 +4569,7 @@
       <c r="L76" s="7" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr">
         <is>
-          <t>Срок cool_off (истёкший снимается автоматически).</t>
+          <t>Последняя игра.</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>marketing_consent</t>
+          <t>last_deposit_at</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string (ISO-8601)</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>2026-07-28T10:15:00Z</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr"/>
@@ -4624,7 +4624,7 @@
       <c r="L77" s="7" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>Маркетинговое согласие (гейт для Tier-1 рынков).</t>
+          <t>Последний депозит.</t>
         </is>
       </c>
     </row>
@@ -4641,37 +4641,37 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>rg_flags</t>
+          <t>ok / updated</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>bool / bool</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>{"escalating_bets":true}</t>
+          <t>{"ok":true,"updated":true}</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr"/>
@@ -4679,7 +4679,7 @@
       <c r="L78" s="7" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr">
         <is>
-          <t>Готовые поведенческие RG-флаги risk-движка казино.</t>
+          <t>Признак приёма и факта изменения.</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>timezone</t>
+          <t>rg_status</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="I79" s="8" t="inlineStr">
         <is>
-          <t>Europe/Istanbul</t>
+          <t>self_exclude</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr"/>
@@ -4734,7 +4734,7 @@
       <c r="L79" s="7" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>Локальная таймзона игрока (IANA или '+03:00'; geo-IP на стороне казино) — точность smart-send-time.</t>
+          <t>RG-статус игрока: ok | cool_off | rg_hold | self_exclude. Источник истины по самоисключению — платформа казино; self_exclude/rg_hold полностью блокируют проактив и бонусы. Слать при каждой смене + первичный бэкфилл.</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>email_opt_in / email_verified / push_opt_in / push_available / in_app_available / sms_opt_in</t>
+          <t>rg_status_until</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string (ISO-8601)</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>2026-10-01T00:00:00Z</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr"/>
@@ -4789,24 +4789,24 @@
       <c r="L80" s="7" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr">
         <is>
-          <t>Согласия и доступность каналов. Строгий opt-in: канал без согласия никогда не используется, даже как fallback.</t>
+          <t>Срок cool_off (истёкший снимается автоматически).</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>Partner API</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>POST /partner/{product_id}/delivery-status</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/player-update</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
@@ -4814,33 +4814,37 @@
           <t>Вход</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>CRM казино</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr"/>
-      <c r="G81" s="5" t="inlineStr"/>
-      <c r="H81" s="4" t="inlineStr"/>
-      <c r="I81" s="5" t="inlineStr"/>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K81" s="4" t="inlineStr">
-        <is>
-          <t>Идемпотентно; статус не движется назад · лимит partner:{ip}</t>
-        </is>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>401 unauthorized · 422 invalid_status · 429 rate_limited</t>
-        </is>
-      </c>
-      <c r="M81" s="4" t="inlineStr">
-        <is>
-          <t>Коллбек прогресса доставки заказа push/in-app, размещённого оркестратором (см. Исходящие: delivery-endpoint).</t>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>marketing_consent</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr"/>
+      <c r="K81" s="7" t="inlineStr"/>
+      <c r="L81" s="7" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>Маркетинговое согласие (гейт для Tier-1 рынков).</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4856,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/delivery-status</t>
+          <t>POST /partner/{product_id}/player-update</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
@@ -4872,22 +4876,22 @@
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>delivery_id</t>
+          <t>rg_flags</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>dl_a1b2c3d4e5f6</t>
+          <t>{"escalating_bets":true}</t>
         </is>
       </c>
       <c r="J82" s="7" t="inlineStr"/>
@@ -4895,7 +4899,7 @@
       <c r="L82" s="7" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr">
         <is>
-          <t>Наш ключ идемпотентности заказа доставки.</t>
+          <t>Готовые поведенческие RG-флаги risk-движка казино.</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4911,7 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/delivery-status</t>
+          <t>POST /partner/{product_id}/player-update</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -4927,22 +4931,22 @@
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>timezone</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>delivered</t>
+          <t>Europe/Istanbul</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr"/>
@@ -4950,70 +4954,74 @@
       <c r="L83" s="7" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>sent | delivered | opened | clicked | bounced.</t>
+          <t>Локальная таймзона игрока (IANA или '+03:00'; geo-IP на стороне казино) — точность smart-send-time.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>Исходящие</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>POST &lt;offer_grant_url&gt; (реализует казино)</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D84" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>Наш сервис</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr"/>
-      <c r="G84" s="5" t="inlineStr"/>
-      <c r="H84" s="4" t="inlineStr"/>
-      <c r="I84" s="5" t="inlineStr"/>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;partner outbound key продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K84" s="4" t="inlineStr">
-        <is>
-          <t>Идемпотентно по offer_grant_id (повтор возвращает тот же результат, второй бонус не создаётся) · таймаут retention.offer_grant_timeout_sec</t>
-        </is>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>401 · 400 unsupported_offer_type · 422 player_not_found</t>
-        </is>
-      </c>
-      <c r="M84" s="4" t="inlineStr">
-        <is>
-          <t>Выдача бонуса по его ID из бонус-CMS казино (offer engine). URL задаётся per product в админке.</t>
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>Partner API</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/player-update</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>email_opt_in / email_verified / push_opt_in / push_available / in_app_available / sms_opt_in</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J84" s="7" t="inlineStr"/>
+      <c r="K84" s="7" t="inlineStr"/>
+      <c r="L84" s="7" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr">
+        <is>
+          <t>Согласия и доступность каналов. Строгий opt-in: канал без согласия никогда не используется, даже как fallback. sms_opt_in принимается «на вырост» — sms-канала пока нет.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Исходящие</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>POST &lt;offer_grant_url&gt; (реализует казино)</t>
+          <t>POST /partner/{product_id}/player-update</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -5021,34 +5029,34 @@
           <t>Поле запроса</t>
         </is>
       </c>
-      <c r="D85" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>offer_grant_id</t>
+          <t>channel_prefs</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>og_a1b2c3d4e5f6</t>
+          <t>{"preferred":"email"}</t>
         </is>
       </c>
       <c r="J85" s="7" t="inlineStr"/>
@@ -5056,79 +5064,75 @@
       <c r="L85" s="7" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>Наш детерминированный ключ идемпотентности.</t>
+          <t>Предпочтения игрока по каналам (свободная структура казино); хранится рядом с согласиями.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="7" t="inlineStr">
-        <is>
-          <t>Исходящие</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>POST &lt;offer_grant_url&gt; (реализует казино)</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D86" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>Наш сервис</t>
-        </is>
-      </c>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>player_id / bonus_id / offer_type / params</t>
-        </is>
-      </c>
-      <c r="G86" s="8" t="inlineStr">
-        <is>
-          <t>string / string / string / object</t>
-        </is>
-      </c>
-      <c r="H86" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I86" s="8" t="inlineStr">
-        <is>
-          <t>{"bonus_id":"BONUS-42"}</t>
-        </is>
-      </c>
-      <c r="J86" s="7" t="inlineStr"/>
-      <c r="K86" s="7" t="inlineStr"/>
-      <c r="L86" s="7" t="inlineStr"/>
-      <c r="M86" s="7" t="inlineStr">
-        <is>
-          <t>Кому и какой бонус начислить (bonus_id — ID в бонус-CMS).</t>
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Partner API</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/delivery-status</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr"/>
+      <c r="G86" s="5" t="inlineStr"/>
+      <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" s="5" t="inlineStr"/>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>Идемпотентно; статус не движется назад · лимит partner:{ip}</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>401 unauthorized · 422 invalid_status · 429 rate_limited</t>
+        </is>
+      </c>
+      <c r="M86" s="4" t="inlineStr">
+        <is>
+          <t>Коллбек прогресса доставки заказа push/in-app, размещённого оркестратором (см. Исходящие: delivery-endpoint).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Исходящие</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>POST &lt;offer_grant_url&gt; (реализует казино)</t>
+          <t>POST /partner/{product_id}/delivery-status</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
@@ -5143,12 +5147,12 @@
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>delivery_id</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
@@ -5158,7 +5162,7 @@
       </c>
       <c r="I87" s="8" t="inlineStr">
         <is>
-          <t>granted</t>
+          <t>dl_a1b2c3d4e5f6</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr"/>
@@ -5166,113 +5170,113 @@
       <c r="L87" s="7" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>granted | fraud_hold | duplicate | failed (+ partner_ref, credited_usd). Персона упоминает бонус ТОЛЬКО после granted.</t>
+          <t>Наш ключ идемпотентности заказа доставки.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>Partner API</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/delivery-status</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>delivered</t>
+        </is>
+      </c>
+      <c r="J88" s="7" t="inlineStr"/>
+      <c r="K88" s="7" t="inlineStr"/>
+      <c r="L88" s="7" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr">
+        <is>
+          <t>queued | sending | sent | delivered | opened | clicked | bounced. Порядок монотонный: более ранний статус после более позднего игнорируется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>Исходящие</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>POST &lt;delivery_endpoint_url&gt; (реализует казино)</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>POST &lt;offer_grant_url&gt; (реализует казино)</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D88" s="10" t="inlineStr">
+      <c r="D89" s="10" t="inlineStr">
         <is>
           <t>Выход</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>Наш сервис</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr"/>
-      <c r="G88" s="5" t="inlineStr"/>
-      <c r="H88" s="4" t="inlineStr"/>
-      <c r="I88" s="5" t="inlineStr"/>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;partner outbound key продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K88" s="4" t="inlineStr">
-        <is>
-          <t>Идемпотентно по delivery_id · таймаут retention.push_delivery_timeout_sec · транзиентные ошибки ретраятся (1m/5m/30m), permanent — нет</t>
-        </is>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>permanent:true в ответе = ретраев не будет</t>
-        </is>
-      </c>
-      <c r="M88" s="4" t="inlineStr">
-        <is>
-          <t>Заказ делегированной доставки push/in-app: казино доставляет на устройство своей инфраструктурой и шлёт прогресс коллбеком delivery-status.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>Исходящие</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>POST &lt;delivery_endpoint_url&gt; (реализует казино)</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D89" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>Наш сервис</t>
-        </is>
-      </c>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>delivery_id / player_id / channel / title / body / cta_url / ttl_sec</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t>string / string / enum / string / string / string / int</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>{"channel":"push","ttl_sec":86400}</t>
-        </is>
-      </c>
-      <c r="J89" s="7" t="inlineStr"/>
-      <c r="K89" s="7" t="inlineStr"/>
-      <c r="L89" s="7" t="inlineStr"/>
-      <c r="M89" s="7" t="inlineStr">
-        <is>
-          <t>Заказ доставки; channel: push | in_app.</t>
+      <c r="F89" s="5" t="inlineStr"/>
+      <c r="G89" s="5" t="inlineStr"/>
+      <c r="H89" s="4" t="inlineStr"/>
+      <c r="I89" s="5" t="inlineStr"/>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;partner_out_key продукта&gt;; без ключа заголовок Authorization не отправляется</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>Идемпотентно по offer_grant_id (повтор возвращает тот же результат, второй бонус не создаётся) · таймаут retention.offer_grant_timeout_sec</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>Любой 4xx (кроме 429) = постоянная ошибка, без ретраев; 429 и 5xx — транзиентные, ретраятся</t>
+        </is>
+      </c>
+      <c r="M89" s="4" t="inlineStr">
+        <is>
+          <t>Выдача бонуса по его ID из бонус-CMS казино (offer engine). URL задаётся per product в админке (PUT /admin/retention/partner-endpoints).</t>
         </is>
       </c>
     </row>
@@ -5284,32 +5288,32 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>POST &lt;delivery_endpoint_url&gt; (реализует казино)</t>
+          <t>POST &lt;offer_grant_url&gt; (реализует казино)</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>offer_grant_id</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
@@ -5319,7 +5323,7 @@
       </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>og_a1b2c3d4e5f6</t>
         </is>
       </c>
       <c r="J90" s="7" t="inlineStr"/>
@@ -5327,75 +5331,79 @@
       <c r="L90" s="7" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr">
         <is>
-          <t>sent | queued | delivered | failed (+ reason, permanent, provider_ref).</t>
+          <t>Наш детерминированный ключ идемпотентности.</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>Partner API</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>POST /partner/{product_id}/event</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>CRM казино</t>
-        </is>
-      </c>
-      <c r="F91" s="5" t="inlineStr"/>
-      <c r="G91" s="5" t="inlineStr"/>
-      <c r="H91" s="4" t="inlineStr"/>
-      <c r="I91" s="5" t="inlineStr"/>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K91" s="4" t="inlineStr">
-        <is>
-          <t>Идемпотентно по event_id (доставка at-least-once безопасна) · пакет до 500 событий · payload до 8 KiB · лимит partner:{ip}</t>
-        </is>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>401 · 413 batch_too_large · 422 invalid_event · 429</t>
-        </is>
-      </c>
-      <c r="M91" s="4" t="inlineStr">
-        <is>
-          <t>Канонический поток событий казино: кормит проактивного агента и обновляет сигналы активности игрока.</t>
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>POST &lt;offer_grant_url&gt; (реализует казино)</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>player_id / bonus_id / offer_type / params</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>string / string / string / object</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>{"bonus_id":"BONUS-42"}</t>
+        </is>
+      </c>
+      <c r="J91" s="7" t="inlineStr"/>
+      <c r="K91" s="7" t="inlineStr"/>
+      <c r="L91" s="7" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr">
+        <is>
+          <t>Кому и какой бонус начислить (bonus_id — ID в бонус-CMS).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>Partner API</t>
+          <t>Исходящие</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST &lt;offer_grant_url&gt; (реализует казино)</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Поле ответа</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
@@ -5410,12 +5418,12 @@
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>string (≤64)</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
@@ -5425,7 +5433,7 @@
       </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>evt_2026072801</t>
+          <t>granted</t>
         </is>
       </c>
       <c r="J92" s="7" t="inlineStr"/>
@@ -5433,78 +5441,70 @@
       <c r="L92" s="7" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>Ключ идемпотентности. Повтор считается дубликатом, а не ошибкой.</t>
+          <t>granted | fraud_hold | duplicate | failed (+ partner_ref, credited_usd, reason). duplicate трактуется как granted; неизвестный статус — как failed. Персона упоминает бонус ТОЛЬКО после granted.</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>Partner API</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>POST /partner/{product_id}/event</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>CRM казино</t>
-        </is>
-      </c>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t>event_name</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>string (из таксономии)</t>
-        </is>
-      </c>
-      <c r="H93" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I93" s="8" t="inlineStr">
-        <is>
-          <t>deposit_confirmed</t>
-        </is>
-      </c>
-      <c r="J93" s="7" t="inlineStr"/>
-      <c r="K93" s="7" t="inlineStr"/>
-      <c r="L93" s="7" t="inlineStr">
-        <is>
-          <t>422 invalid_event на неизвестное имя</t>
-        </is>
-      </c>
-      <c r="M93" s="7" t="inlineStr">
-        <is>
-          <t>Имя события. Таксономия — контракт, а не рекомендация; список ниже.</t>
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>POST &lt;delivery_endpoint_url&gt; (реализует казино)</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr"/>
+      <c r="G93" s="5" t="inlineStr"/>
+      <c r="H93" s="4" t="inlineStr"/>
+      <c r="I93" s="5" t="inlineStr"/>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;partner_out_key продукта&gt;; без ключа заголовок Authorization не отправляется</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>Идемпотентно по delivery_id · таймаут retention.push_delivery_timeout_sec · транзиентные ошибки ретраятся (1m/5m/30m), permanent — нет</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>permanent:true в ответе = ретраев не будет</t>
+        </is>
+      </c>
+      <c r="M93" s="4" t="inlineStr">
+        <is>
+          <t>Заказ делегированной доставки push/in-app: казино доставляет на устройство своей инфраструктурой и шлёт прогресс коллбеком delivery-status.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>Partner API</t>
+          <t>Исходящие</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST &lt;delivery_endpoint_url&gt; (реализует казино)</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
@@ -5512,24 +5512,24 @@
           <t>Поле запроса</t>
         </is>
       </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>player_id | user_id</t>
+          <t>delivery_id / player_id / channel / title / body / cta_url / ttl_sec</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string / string / enum / string / string / string / int</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>1048576</t>
+          <t>{"channel":"push","ttl_sec":86400}</t>
         </is>
       </c>
       <c r="J94" s="7" t="inlineStr"/>
@@ -5547,24 +5547,24 @@
       <c r="L94" s="7" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr">
         <is>
-          <t>Игрок, к которому относится событие.</t>
+          <t>Заказ доставки; channel: push | in_app.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Partner API</t>
+          <t>Исходящие</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST &lt;delivery_endpoint_url&gt; (реализует казино)</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Поле ответа</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -5579,22 +5579,22 @@
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>tg_user_id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I95" s="8" t="inlineStr">
         <is>
-          <t>584210394</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr"/>
@@ -5602,74 +5602,70 @@
       <c r="L95" s="7" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>Явный получатель, когда один player_id связан с несколькими Telegram-аккаунтами.</t>
+          <t>sent | queued | delivered = успех; failed (+ reason, permanent, provider_ref). Ретраи только при включённой настройке retention.delivery_retry_enabled.</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t>Partner API</t>
-        </is>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>POST /partner/{product_id}/event</t>
-        </is>
-      </c>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>CRM казино</t>
-        </is>
-      </c>
-      <c r="F96" s="8" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="G96" s="8" t="inlineStr">
-        <is>
-          <t>string (ISO-8601)</t>
-        </is>
-      </c>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I96" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-28T10:15:00Z</t>
-        </is>
-      </c>
-      <c r="J96" s="7" t="inlineStr"/>
-      <c r="K96" s="7" t="inlineStr"/>
-      <c r="L96" s="7" t="inlineStr"/>
-      <c r="M96" s="7" t="inlineStr">
-        <is>
-          <t>Время события. Значение из будущего приводится к текущему моменту.</t>
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>POST https://api[-eu].customer.io/v1/send/email</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="5" t="inlineStr"/>
+      <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" s="5" t="inlineStr"/>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;email_api_key продукта&gt; (App API key, секрет продукта)</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>Регион us/eu — из конфигурации канала email · HTTP ≥400 = постоянная ошибка, кроме 429/500/502/503/504 (ретраи 1m/5m/30m)</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>no_email_api_key / no_email_address — постоянные, без ретраев</t>
+        </is>
+      </c>
+      <c r="M96" s="4" t="inlineStr">
+        <is>
+          <t>Email-канал мультиканального роутера: транзакционная отправка через Customer.io. Статусы провайдера прилетают тем же коллбеком delivery-status.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Partner API</t>
+          <t>Исходящие</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST https://api[-eu].customer.io/v1/send/email</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -5677,34 +5673,34 @@
           <t>Поле запроса</t>
         </is>
       </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>event_version</t>
+          <t>to / identifiers.id / subject / body / from? / transactional_message_id?</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string / string / string / string (HTML)</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>{"to":"player@example.com","identifiers":{"id":"1048576"}}</t>
         </is>
       </c>
       <c r="J97" s="7" t="inlineStr"/>
@@ -5712,24 +5708,24 @@
       <c r="L97" s="7" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>Версия схемы события на стороне отправителя.</t>
+          <t>from и transactional_message_id — из конфигурации канала email продукта.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>Partner API</t>
+          <t>Исходящие</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>POST /partner/{product_id}/event</t>
+          <t>POST https://api[-eu].customer.io/v1/send/email</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Поле ответа</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
@@ -5744,22 +5740,22 @@
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>payload</t>
+          <t>delivery_id</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>object (≤8 KiB)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>{"amount":"50.00","currency":"USDT"}</t>
+          <t>cio_01H…</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr"/>
@@ -5767,24 +5763,24 @@
       <c r="L98" s="7" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr">
         <is>
-          <t>Детали события; может нести и поля профиля — они обновят снапшот.</t>
+          <t>Референс провайдера; сохраняется как provider_ref доставки.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="7" t="inlineStr">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>Partner API</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
@@ -5792,37 +5788,33 @@
           <t>Вход</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="E99" s="4" t="inlineStr">
         <is>
           <t>CRM казино</t>
         </is>
       </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t>events</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t>[object] (≤500)</t>
-        </is>
-      </c>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I99" s="8" t="inlineStr">
-        <is>
-          <t>[{"event_id":"…","event_name":"…"}]</t>
-        </is>
-      </c>
-      <c r="J99" s="7" t="inlineStr"/>
-      <c r="K99" s="7" t="inlineStr"/>
-      <c r="L99" s="7" t="inlineStr"/>
-      <c r="M99" s="7" t="inlineStr">
-        <is>
-          <t>Пакетная форма. Взаимоисключима с плоскими полями выше.</t>
+      <c r="F99" s="5" t="inlineStr"/>
+      <c r="G99" s="5" t="inlineStr"/>
+      <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" s="5" t="inlineStr"/>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>Идемпотентно по event_id (доставка at-least-once безопасна) · пакет до 500 событий · payload до 8 KiB · лимит partner:{ip}</t>
+        </is>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>401 · 413 batch_too_large · 422 invalid_event · 429</t>
+        </is>
+      </c>
+      <c r="M99" s="4" t="inlineStr">
+        <is>
+          <t>Канонический поток событий казино: кормит проактивного агента и обновляет сигналы активности игрока.</t>
         </is>
       </c>
     </row>
@@ -5839,27 +5831,27 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D100" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>stored / duplicates / invalid</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>int|bool</t>
+          <t>string (≤64)</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
@@ -5869,7 +5861,7 @@
       </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>{"ok":true,"stored":12,"duplicates":3}</t>
+          <t>evt_2026072801</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr"/>
@@ -5877,7 +5869,7 @@
       <c r="L100" s="7" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr">
         <is>
-          <t>Итог приёма: сколько принято, сколько дублей, сколько отвергнуто.</t>
+          <t>Ключ идемпотентности. Повтор считается дубликатом, а не ошибкой.</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5886,7 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
@@ -5909,34 +5901,34 @@
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>session_started</t>
+          <t>event_name</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>event_name · Сессия</t>
-        </is>
-      </c>
-      <c r="H101" s="7" t="inlineStr"/>
+          <t>string (из таксономии)</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"session_started"}</t>
-        </is>
-      </c>
-      <c r="J101" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K101" s="7" t="inlineStr">
-        <is>
-          <t>обновляет last_login_at</t>
-        </is>
-      </c>
-      <c r="L101" s="7" t="inlineStr"/>
+          <t>deposit_confirmed</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr"/>
+      <c r="K101" s="7" t="inlineStr"/>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>422 invalid_event на неизвестное имя</t>
+        </is>
+      </c>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>Игрок начал сессию на сайте или в приложении.</t>
+          <t>Имя события. Таксономия — контракт, а не рекомендация; список ниже.</t>
         </is>
       </c>
     </row>
@@ -5953,7 +5945,7 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
@@ -5968,34 +5960,30 @@
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>session_ended</t>
+          <t>player_id | user_id</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>event_name · Сессия</t>
-        </is>
-      </c>
-      <c r="H102" s="7" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H102" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"session_ended"}</t>
-        </is>
-      </c>
-      <c r="J102" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K102" s="7" t="inlineStr">
-        <is>
-          <t>обновляет last_login_at</t>
-        </is>
-      </c>
+          <t>1048576</t>
+        </is>
+      </c>
+      <c r="J102" s="7" t="inlineStr"/>
+      <c r="K102" s="7" t="inlineStr"/>
       <c r="L102" s="7" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr">
         <is>
-          <t>Игрок завершил сессию.</t>
+          <t>Игрок, к которому относится событие.</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6000,7 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
@@ -6027,34 +6015,30 @@
       </c>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>deposit_initiated</t>
+          <t>tg_user_id</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>event_name · Платежи</t>
-        </is>
-      </c>
-      <c r="H103" s="7" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"deposit_initiated"}</t>
-        </is>
-      </c>
-      <c r="J103" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K103" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>584210394</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="inlineStr"/>
+      <c r="K103" s="7" t="inlineStr"/>
       <c r="L103" s="7" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr">
         <is>
-          <t>Депозит начат, ещё не подтверждён.</t>
+          <t>Явный получатель, когда один player_id связан с несколькими Telegram-аккаунтами.</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6055,7 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
@@ -6086,34 +6070,30 @@
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>deposit_confirmed</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>event_name · Платежи</t>
-        </is>
-      </c>
-      <c r="H104" s="7" t="inlineStr"/>
+          <t>string (ISO-8601)</t>
+        </is>
+      </c>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"deposit_confirmed"}</t>
-        </is>
-      </c>
-      <c r="J104" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K104" s="7" t="inlineStr">
-        <is>
-          <t>обновляет last_deposit_at</t>
-        </is>
-      </c>
+          <t>2026-07-28T10:15:00Z</t>
+        </is>
+      </c>
+      <c r="J104" s="7" t="inlineStr"/>
+      <c r="K104" s="7" t="inlineStr"/>
       <c r="L104" s="7" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr">
         <is>
-          <t>Депозит зачислен — сильнейший позитивный сигнал.</t>
+          <t>Время события (в пакетной/сырой форме принимается и алиас ts). Значение из будущего приводится к текущему моменту.</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6110,7 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
@@ -6145,34 +6125,30 @@
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>deposit_failed</t>
+          <t>event_version</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>event_name · Платежи</t>
-        </is>
-      </c>
-      <c r="H105" s="7" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"deposit_failed"}</t>
-        </is>
-      </c>
-      <c r="J105" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K105" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J105" s="7" t="inlineStr"/>
+      <c r="K105" s="7" t="inlineStr"/>
       <c r="L105" s="7" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr">
         <is>
-          <t>Депозит не прошёл.</t>
+          <t>Версия схемы события на стороне отправителя.</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6165,7 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
@@ -6204,34 +6180,30 @@
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>withdrawal_settled</t>
+          <t>payload</t>
         </is>
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>event_name · Платежи</t>
-        </is>
-      </c>
-      <c r="H106" s="7" t="inlineStr"/>
+          <t>object (≤8 KiB)</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"withdrawal_settled"}</t>
-        </is>
-      </c>
-      <c r="J106" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K106" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>{"amount":"50.00","currency":"USDT"}</t>
+        </is>
+      </c>
+      <c r="J106" s="7" t="inlineStr"/>
+      <c r="K106" s="7" t="inlineStr"/>
       <c r="L106" s="7" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr">
         <is>
-          <t>Вывод завершён.</t>
+          <t>Детали события; может нести и поля профиля — они обновят снапшот.</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6220,7 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
@@ -6263,34 +6235,30 @@
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>bet_settled</t>
+          <t>events</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>event_name · Игра</t>
-        </is>
-      </c>
-      <c r="H107" s="7" t="inlineStr"/>
+          <t>[object] (≤500)</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bet_settled"}</t>
-        </is>
-      </c>
-      <c r="J107" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K107" s="7" t="inlineStr">
-        <is>
-          <t>обновляет last_played_at</t>
-        </is>
-      </c>
+          <t>[{"event_id":"…","event_name":"…"}]</t>
+        </is>
+      </c>
+      <c r="J107" s="7" t="inlineStr"/>
+      <c r="K107" s="7" t="inlineStr"/>
       <c r="L107" s="7" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr">
         <is>
-          <t>Ставка рассчитана. Сумма проигрыша за 24 ч влияет на тон коммуникации.</t>
+          <t>Пакетная форма. Взаимоисключима с плоскими полями выше.</t>
         </is>
       </c>
     </row>
@@ -6307,49 +6275,45 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
-        </is>
-      </c>
-      <c r="D108" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
-          <t>bonus_granted</t>
+          <t>ok / stored / duplicates / errors</t>
         </is>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>event_name · Бонусы</t>
-        </is>
-      </c>
-      <c r="H108" s="7" t="inlineStr"/>
+          <t>bool / int / int / [{index,error}]</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_granted"}</t>
-        </is>
-      </c>
-      <c r="J108" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K108" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>{"ok":true,"stored":12,"duplicates":3,"errors":[]}</t>
+        </is>
+      </c>
+      <c r="J108" s="7" t="inlineStr"/>
+      <c r="K108" s="7" t="inlineStr"/>
       <c r="L108" s="7" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr">
         <is>
-          <t>Бонус начислен.</t>
+          <t>Ответ ПАКЕТНОЙ формы: сколько принято, сколько дублей и список отвергнутых с причинами.</t>
         </is>
       </c>
     </row>
@@ -6366,49 +6330,45 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>Событие</t>
-        </is>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>CRM казино</t>
+          <t>Наш сервис</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>bonus_claimed</t>
+          <t>ok / stored / duplicate / id</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>event_name · Бонусы</t>
-        </is>
-      </c>
-      <c r="H109" s="7" t="inlineStr"/>
+          <t>bool / bool / bool / int|null</t>
+        </is>
+      </c>
+      <c r="H109" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_claimed"}</t>
-        </is>
-      </c>
-      <c r="J109" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;handshake_secret продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K109" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>{"ok":true,"stored":true,"duplicate":false,"id":8412}</t>
+        </is>
+      </c>
+      <c r="J109" s="7" t="inlineStr"/>
+      <c r="K109" s="7" t="inlineStr"/>
       <c r="L109" s="7" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr">
         <is>
-          <t>Бонус активирован игроком.</t>
+          <t>Ответ ОДИНОЧНОЙ (плоской) формы — форма ответа отличается от пакетной.</t>
         </is>
       </c>
     </row>
@@ -6440,18 +6400,18 @@
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
-          <t>bonus_completed</t>
+          <t>session_started</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>event_name · Бонусы</t>
+          <t>event_name · Сессия</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr"/>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_completed"}</t>
+          <t>{"event_name":"session_started"}</t>
         </is>
       </c>
       <c r="J110" s="7" t="inlineStr">
@@ -6461,13 +6421,13 @@
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>обновляет last_login_at</t>
         </is>
       </c>
       <c r="L110" s="7" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr">
         <is>
-          <t>Отыгрыш завершён.</t>
+          <t>Игрок начал сессию на сайте или в приложении.</t>
         </is>
       </c>
     </row>
@@ -6499,18 +6459,18 @@
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>bonus_expired</t>
+          <t>session_ended</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>event_name · Бонусы</t>
+          <t>event_name · Сессия</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr"/>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"bonus_expired"}</t>
+          <t>{"event_name":"session_ended"}</t>
         </is>
       </c>
       <c r="J111" s="7" t="inlineStr">
@@ -6520,13 +6480,13 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>обновляет last_login_at</t>
         </is>
       </c>
       <c r="L111" s="7" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr">
         <is>
-          <t>Бонус сгорел.</t>
+          <t>Игрок завершил сессию.</t>
         </is>
       </c>
     </row>
@@ -6558,18 +6518,18 @@
       </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
-          <t>kyc_started</t>
+          <t>deposit_initiated</t>
         </is>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>event_name · Верификация</t>
+          <t>event_name · Платежи</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr"/>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"kyc_started"}</t>
+          <t>{"event_name":"deposit_initiated"}</t>
         </is>
       </c>
       <c r="J112" s="7" t="inlineStr">
@@ -6579,13 +6539,13 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>взводит таймер брошенной кассы</t>
         </is>
       </c>
       <c r="L112" s="7" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr">
         <is>
-          <t>Верификация начата.</t>
+          <t>Депозит начат, ещё не подтверждён. Таймер снимается событием deposit_confirmed; по истечении может стартовать journey «брошенная касса».</t>
         </is>
       </c>
     </row>
@@ -6617,18 +6577,18 @@
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>kyc_approved</t>
+          <t>deposit_confirmed</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>event_name · Верификация</t>
+          <t>event_name · Платежи</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr"/>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"kyc_approved"}</t>
+          <t>{"event_name":"deposit_confirmed"}</t>
         </is>
       </c>
       <c r="J113" s="7" t="inlineStr">
@@ -6638,13 +6598,13 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>обновляет last_deposit_at</t>
         </is>
       </c>
       <c r="L113" s="7" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr">
         <is>
-          <t>Верификация пройдена.</t>
+          <t>Депозит зачислен — сильнейший позитивный сигнал.</t>
         </is>
       </c>
     </row>
@@ -6676,18 +6636,18 @@
       </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
-          <t>kyc_rejected</t>
+          <t>deposit_failed</t>
         </is>
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>event_name · Верификация</t>
+          <t>event_name · Платежи</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr"/>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"kyc_rejected"}</t>
+          <t>{"event_name":"deposit_failed"}</t>
         </is>
       </c>
       <c r="J114" s="7" t="inlineStr">
@@ -6703,7 +6663,7 @@
       <c r="L114" s="7" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr">
         <is>
-          <t>Верификация отклонена.</t>
+          <t>Депозит не прошёл.</t>
         </is>
       </c>
     </row>
@@ -6735,18 +6695,18 @@
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>xp_granted</t>
+          <t>withdrawal_settled</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>event_name · Лояльность</t>
+          <t>event_name · Платежи</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr"/>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"xp_granted"}</t>
+          <t>{"event_name":"withdrawal_settled"}</t>
         </is>
       </c>
       <c r="J115" s="7" t="inlineStr">
@@ -6762,7 +6722,7 @@
       <c r="L115" s="7" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr">
         <is>
-          <t>Начислен опыт.</t>
+          <t>Вывод завершён.</t>
         </is>
       </c>
     </row>
@@ -6794,18 +6754,18 @@
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
-          <t>level_up</t>
+          <t>bet_settled</t>
         </is>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>event_name · Лояльность</t>
+          <t>event_name · Игра</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr"/>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"level_up"}</t>
+          <t>{"event_name":"bet_settled"}</t>
         </is>
       </c>
       <c r="J116" s="7" t="inlineStr">
@@ -6815,13 +6775,13 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>обновляет last_played_at</t>
         </is>
       </c>
       <c r="L116" s="7" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr">
         <is>
-          <t>Новый уровень.</t>
+          <t>Ставка рассчитана. Сумма проигрыша за 24 ч влияет на тон коммуникации.</t>
         </is>
       </c>
     </row>
@@ -6853,18 +6813,18 @@
       </c>
       <c r="F117" s="8" t="inlineStr">
         <is>
-          <t>class_up</t>
+          <t>bonus_granted</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>event_name · Лояльность</t>
+          <t>event_name · Бонусы</t>
         </is>
       </c>
       <c r="H117" s="7" t="inlineStr"/>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"class_up"}</t>
+          <t>{"event_name":"bonus_granted"}</t>
         </is>
       </c>
       <c r="J117" s="7" t="inlineStr">
@@ -6880,7 +6840,7 @@
       <c r="L117" s="7" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr">
         <is>
-          <t>Новый класс / VIP-тир.</t>
+          <t>Бонус начислен.</t>
         </is>
       </c>
     </row>
@@ -6912,18 +6872,18 @@
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
-          <t>downgrade</t>
+          <t>bonus_claimed</t>
         </is>
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>event_name · Лояльность</t>
+          <t>event_name · Бонусы</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr"/>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"downgrade"}</t>
+          <t>{"event_name":"bonus_claimed"}</t>
         </is>
       </c>
       <c r="J118" s="7" t="inlineStr">
@@ -6939,7 +6899,7 @@
       <c r="L118" s="7" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr">
         <is>
-          <t>Понижение класса.</t>
+          <t>Бонус активирован игроком.</t>
         </is>
       </c>
     </row>
@@ -6971,18 +6931,18 @@
       </c>
       <c r="F119" s="8" t="inlineStr">
         <is>
-          <t>highlights_pack_opened</t>
+          <t>bonus_completed</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>event_name · Активности</t>
+          <t>event_name · Бонусы</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr"/>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"highlights_pack_opened"}</t>
+          <t>{"event_name":"bonus_completed"}</t>
         </is>
       </c>
       <c r="J119" s="7" t="inlineStr">
@@ -6998,7 +6958,7 @@
       <c r="L119" s="7" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr">
         <is>
-          <t>Открыт пак/кейс.</t>
+          <t>Отыгрыш завершён.</t>
         </is>
       </c>
     </row>
@@ -7030,18 +6990,18 @@
       </c>
       <c r="F120" s="8" t="inlineStr">
         <is>
-          <t>highlights_pack_completed</t>
+          <t>bonus_expired</t>
         </is>
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>event_name · Активности</t>
+          <t>event_name · Бонусы</t>
         </is>
       </c>
       <c r="H120" s="7" t="inlineStr"/>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"highlights_pack_completed"}</t>
+          <t>{"event_name":"bonus_expired"}</t>
         </is>
       </c>
       <c r="J120" s="7" t="inlineStr">
@@ -7057,7 +7017,7 @@
       <c r="L120" s="7" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr">
         <is>
-          <t>Пак завершён.</t>
+          <t>Бонус сгорел.</t>
         </is>
       </c>
     </row>
@@ -7089,18 +7049,18 @@
       </c>
       <c r="F121" s="8" t="inlineStr">
         <is>
-          <t>check_in_done</t>
+          <t>kyc_started</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>event_name · Активности</t>
+          <t>event_name · Верификация</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr"/>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"check_in_done"}</t>
+          <t>{"event_name":"kyc_started"}</t>
         </is>
       </c>
       <c r="J121" s="7" t="inlineStr">
@@ -7116,7 +7076,7 @@
       <c r="L121" s="7" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr">
         <is>
-          <t>Ежедневный чек-ин выполнен.</t>
+          <t>Верификация начата.</t>
         </is>
       </c>
     </row>
@@ -7148,18 +7108,18 @@
       </c>
       <c r="F122" s="8" t="inlineStr">
         <is>
-          <t>mission_completed</t>
+          <t>kyc_approved</t>
         </is>
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>event_name · Активности</t>
+          <t>event_name · Верификация</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr"/>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>{"event_name":"mission_completed"}</t>
+          <t>{"event_name":"kyc_approved"}</t>
         </is>
       </c>
       <c r="J122" s="7" t="inlineStr">
@@ -7175,75 +7135,83 @@
       <c r="L122" s="7" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr">
         <is>
-          <t>Миссия или квест завершён.</t>
+          <t>Верификация пройдена.</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>Telegram</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>POST /api/retention/deeplink</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>Сайт / виджет</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="inlineStr"/>
-      <c r="G123" s="5" t="inlineStr"/>
-      <c r="H123" s="4" t="inlineStr"/>
-      <c r="I123" s="5" t="inlineStr"/>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>нет (публичный) + лимит по IP</t>
-        </is>
-      </c>
-      <c r="K123" s="4" t="inlineStr">
-        <is>
-          <t>Нонс одноразовый, живёт 120 с (настраивается)</t>
-        </is>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>403 bad_widget_key | retention_disabled · 409 no_bot · 401 bad_handshake · 429</t>
-        </is>
-      </c>
-      <c r="M123" s="4" t="inlineStr">
-        <is>
-          <t>Сайт получает одноразовую ссылку в Telegram-бота с профилем игрока.</t>
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>Partner API</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/event</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>Событие</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F123" s="8" t="inlineStr">
+        <is>
+          <t>kyc_rejected</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>event_name · Верификация</t>
+        </is>
+      </c>
+      <c r="H123" s="7" t="inlineStr"/>
+      <c r="I123" s="8" t="inlineStr">
+        <is>
+          <t>{"event_name":"kyc_rejected"}</t>
+        </is>
+      </c>
+      <c r="J123" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K123" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L123" s="7" t="inlineStr"/>
+      <c r="M123" s="7" t="inlineStr">
+        <is>
+          <t>Верификация отклонена.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>POST /api/retention/deeplink</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Событие</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
@@ -7253,52 +7221,56 @@
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>Сайт / виджет</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr">
         <is>
-          <t>widget_key</t>
+          <t>xp_granted</t>
         </is>
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>string (wk_…)</t>
-        </is>
-      </c>
-      <c r="H124" s="7" t="inlineStr">
-        <is>
-          <t>условно</t>
-        </is>
-      </c>
+          <t>event_name · Лояльность</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr"/>
       <c r="I124" s="8" t="inlineStr">
         <is>
-          <t>wk_7f3a…</t>
-        </is>
-      </c>
-      <c r="J124" s="7" t="inlineStr"/>
-      <c r="K124" s="7" t="inlineStr"/>
+          <t>{"event_name":"xp_granted"}</t>
+        </is>
+      </c>
+      <c r="J124" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K124" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L124" s="7" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr">
         <is>
-          <t>Продукт, чей бот открывать.</t>
+          <t>Начислен опыт.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>POST /api/retention/deeplink</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Событие</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
@@ -7308,52 +7280,56 @@
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>Сайт / виджет</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F125" s="8" t="inlineStr">
         <is>
-          <t>signed_context</t>
+          <t>level_up</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>string (подпись)</t>
-        </is>
-      </c>
-      <c r="H125" s="7" t="inlineStr">
-        <is>
-          <t>условно</t>
-        </is>
-      </c>
+          <t>event_name · Лояльность</t>
+        </is>
+      </c>
+      <c r="H125" s="7" t="inlineStr"/>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>eyJpZCI6…​.QkFTRTY0</t>
-        </is>
-      </c>
-      <c r="J125" s="7" t="inlineStr"/>
-      <c r="K125" s="7" t="inlineStr"/>
+          <t>{"event_name":"level_up"}</t>
+        </is>
+      </c>
+      <c r="J125" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K125" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L125" s="7" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr">
         <is>
-          <t>Профиль игрока — те же поля и та же подпись, что в Chat API.</t>
+          <t>Новый уровень.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>POST /api/retention/deeplink</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Событие</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
@@ -7363,52 +7339,56 @@
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>Сайт / виджет</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr">
         <is>
-          <t>escalation</t>
+          <t>class_up</t>
         </is>
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="H126" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
+          <t>event_name · Лояльность</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr"/>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="J126" s="7" t="inlineStr"/>
-      <c r="K126" s="7" t="inlineStr"/>
+          <t>{"event_name":"class_up"}</t>
+        </is>
+      </c>
+      <c r="J126" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K126" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L126" s="7" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr">
         <is>
-          <t>true — точка входа «к менеджеру».</t>
+          <t>Новый класс / VIP-тир.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>POST /api/retention/deeplink</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Событие</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
@@ -7418,162 +7398,174 @@
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>Сайт / виджет</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F127" s="8" t="inlineStr">
         <is>
-          <t>lang</t>
+          <t>downgrade</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>string (код или локаль)</t>
-        </is>
-      </c>
-      <c r="H127" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
+          <t>event_name · Лояльность</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="inlineStr"/>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>ru</t>
-        </is>
-      </c>
-      <c r="J127" s="7" t="inlineStr"/>
-      <c r="K127" s="7" t="inlineStr"/>
+          <t>{"event_name":"downgrade"}</t>
+        </is>
+      </c>
+      <c r="J127" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L127" s="7" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr">
         <is>
-          <t>Язык, в котором откроется бот.</t>
+          <t>Понижение класса.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>POST /api/retention/deeplink</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D128" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Событие</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr">
         <is>
-          <t>deep_link</t>
+          <t>highlights_pack_opened</t>
         </is>
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>string (URL)</t>
-        </is>
-      </c>
-      <c r="H128" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>event_name · Активности</t>
+        </is>
+      </c>
+      <c r="H128" s="7" t="inlineStr"/>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>https://t.me/brand_bot?start=Ax7…</t>
-        </is>
-      </c>
-      <c r="J128" s="7" t="inlineStr"/>
-      <c r="K128" s="7" t="inlineStr"/>
+          <t>{"event_name":"highlights_pack_opened"}</t>
+        </is>
+      </c>
+      <c r="J128" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K128" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L128" s="7" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr">
         <is>
-          <t>Ссылка для кнопки. Нонс погашается при первом /start.</t>
+          <t>Открыт пак/кейс.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>POST /api/retention/deeplink</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D129" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Событие</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F129" s="8" t="inlineStr">
         <is>
-          <t>nonce</t>
+          <t>highlights_pack_completed</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H129" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>event_name · Активности</t>
+        </is>
+      </c>
+      <c r="H129" s="7" t="inlineStr"/>
       <c r="I129" s="8" t="inlineStr">
         <is>
-          <t>Ax7kQ…</t>
-        </is>
-      </c>
-      <c r="J129" s="7" t="inlineStr"/>
-      <c r="K129" s="7" t="inlineStr"/>
+          <t>{"event_name":"highlights_pack_completed"}</t>
+        </is>
+      </c>
+      <c r="J129" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K129" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L129" s="7" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr">
         <is>
-          <t>Тот же одноразовый токен отдельным полем.</t>
+          <t>Пак завершён.</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>Telegram</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>POST /telegram/webhook/{secret}</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>Partner API</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>POST /partner/{product_id}/event</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>Событие</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
@@ -7581,50 +7573,58 @@
           <t>Вход</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>Telegram</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="inlineStr"/>
-      <c r="G130" s="5" t="inlineStr"/>
-      <c r="H130" s="4" t="inlineStr"/>
-      <c r="I130" s="5" t="inlineStr"/>
-      <c r="J130" s="4" t="inlineStr">
-        <is>
-          <t>путь = webhook-токен продукта (роутинг) + заголовок X-Telegram-Bot-Api-Secret-Token</t>
-        </is>
-      </c>
-      <c r="K130" s="4" t="inlineStr">
-        <is>
-          <t>Всегда быстрый 200 (иначе Telegram ретраит); ход ИИ выполняется в фоне</t>
-        </is>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>403 bad_secret_token · неизвестный токен пути → тихий 200</t>
-        </is>
-      </c>
-      <c r="M130" s="4" t="inlineStr">
-        <is>
-          <t>Приём апдейтов Telegram — второй фасад над тем же ИИ-ядром.</t>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F130" s="8" t="inlineStr">
+        <is>
+          <t>check_in_done</t>
+        </is>
+      </c>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t>event_name · Активности</t>
+        </is>
+      </c>
+      <c r="H130" s="7" t="inlineStr"/>
+      <c r="I130" s="8" t="inlineStr">
+        <is>
+          <t>{"event_name":"check_in_done"}</t>
+        </is>
+      </c>
+      <c r="J130" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K130" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L130" s="7" t="inlineStr"/>
+      <c r="M130" s="7" t="inlineStr">
+        <is>
+          <t>Ежедневный чек-ин выполнен.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>Partner API</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>POST /telegram/webhook/{secret}</t>
+          <t>POST /partner/{product_id}/event</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>Заголовок</t>
+          <t>Событие</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
@@ -7634,153 +7634,157 @@
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>Telegram</t>
+          <t>CRM казино</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr">
         <is>
-          <t>X-Telegram-Bot-Api-Secret-Token</t>
+          <t>mission_completed</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H131" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>event_name · Активности</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="inlineStr"/>
       <c r="I131" s="8" t="inlineStr">
         <is>
-          <t>b4c9…</t>
-        </is>
-      </c>
-      <c r="J131" s="7" t="inlineStr"/>
-      <c r="K131" s="7" t="inlineStr"/>
+          <t>{"event_name":"mission_completed"}</t>
+        </is>
+      </c>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;handshake_secret продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L131" s="7" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr">
         <is>
-          <t>Секрет, заданный при регистрации вебхука. Защищает от подделки апдейтов тем, кто узнал URL.</t>
+          <t>Миссия или квест завершён.</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="7" t="inlineStr">
+      <c r="A132" s="4" t="inlineStr">
         <is>
           <t>Telegram</t>
         </is>
       </c>
-      <c r="B132" s="8" t="inlineStr">
-        <is>
-          <t>POST /telegram/webhook/{secret}</t>
-        </is>
-      </c>
-      <c r="C132" s="7" t="inlineStr">
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>POST /api/retention/deeplink</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>Сайт / виджет</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr"/>
+      <c r="G132" s="5" t="inlineStr"/>
+      <c r="H132" s="4" t="inlineStr"/>
+      <c r="I132" s="5" t="inlineStr"/>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>нет (публичный) + лимит по IP</t>
+        </is>
+      </c>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>Нонс одноразовый, живёт 120 с (настраивается) · лимит deeplink:{ip}</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>403 bad_widget_key | retention_disabled · 409 no_bot · 401 bad_handshake · 429</t>
+        </is>
+      </c>
+      <c r="M132" s="4" t="inlineStr">
+        <is>
+          <t>Сайт получает одноразовую ссылку в Telegram-бота с профилем игрока.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/retention/deeplink</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
         <is>
           <t>Поле запроса</t>
         </is>
       </c>
-      <c r="D132" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>Telegram</t>
-        </is>
-      </c>
-      <c r="F132" s="8" t="inlineStr">
-        <is>
-          <t>update</t>
-        </is>
-      </c>
-      <c r="G132" s="8" t="inlineStr">
-        <is>
-          <t>object (Telegram Bot API)</t>
-        </is>
-      </c>
-      <c r="H132" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I132" s="8" t="inlineStr">
-        <is>
-          <t>{"update_id":1,"message":{…}}</t>
-        </is>
-      </c>
-      <c r="J132" s="7" t="inlineStr"/>
-      <c r="K132" s="7" t="inlineStr"/>
-      <c r="L132" s="7" t="inlineStr"/>
-      <c r="M132" s="7" t="inlineStr">
-        <is>
-          <t>Стандартный формат Telegram.</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>POST /admin/login</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
-        </is>
-      </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F133" s="5" t="inlineStr"/>
-      <c r="G133" s="5" t="inlineStr"/>
-      <c r="H133" s="4" t="inlineStr"/>
-      <c r="I133" s="5" t="inlineStr"/>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>нет (публичный)</t>
-        </is>
-      </c>
-      <c r="K133" s="4" t="inlineStr">
-        <is>
-          <t>Лимит попыток входа с IP</t>
-        </is>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>401 · 429</t>
-        </is>
-      </c>
-      <c r="M133" s="4" t="inlineStr">
-        <is>
-          <t>Вход человека-администратора: email + пароль → JWT.</t>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>Сайт / виджет</t>
+        </is>
+      </c>
+      <c r="F133" s="8" t="inlineStr">
+        <is>
+          <t>widget_key</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>string (wk_…)</t>
+        </is>
+      </c>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
+          <t>условно</t>
+        </is>
+      </c>
+      <c r="I133" s="8" t="inlineStr">
+        <is>
+          <t>wk_7f3a…</t>
+        </is>
+      </c>
+      <c r="J133" s="7" t="inlineStr"/>
+      <c r="K133" s="7" t="inlineStr"/>
+      <c r="L133" s="7" t="inlineStr"/>
+      <c r="M133" s="7" t="inlineStr">
+        <is>
+          <t>Продукт, чей бот открывать.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>Admin API</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>POST /admin/login</t>
+          <t>POST /api/retention/deeplink</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
@@ -7795,27 +7799,27 @@
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>Внешняя админка</t>
+          <t>Сайт / виджет</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr">
         <is>
-          <t>email / password</t>
+          <t>signed_context</t>
         </is>
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>string / string</t>
+          <t>string (подпись)</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>условно</t>
         </is>
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
-          <t>ops@brand.com</t>
+          <t>eyJpZCI6…​.QkFTRTY0</t>
         </is>
       </c>
       <c r="J134" s="7" t="inlineStr"/>
@@ -7823,54 +7827,54 @@
       <c r="L134" s="7" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr">
         <is>
-          <t>Учётная запись администратора.</t>
+          <t>Профиль игрока — те же поля и та же подпись, что в Chat API.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>Admin API</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>POST /admin/login</t>
+          <t>POST /api/retention/deeplink</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D135" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Сайт / виджет</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>user_context</t>
         </is>
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>string (JWT)</t>
+          <t>object</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
-          <t>eyJhbGciOiJIUzI1NiJ9…</t>
+          <t>{"full_name":"Andrey"}</t>
         </is>
       </c>
       <c r="J135" s="7" t="inlineStr"/>
@@ -7878,24 +7882,24 @@
       <c r="L135" s="7" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr">
         <is>
-          <t>Админ-токен; продлевается сам при активной работе.</t>
+          <t>Неподписанный профиль — принимается только в dev (как в Chat API); в проде обнуляется.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>Admin API</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>* /admin/*</t>
+          <t>POST /api/retention/deeplink</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>Заголовок</t>
+          <t>Поле запроса</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
@@ -7905,192 +7909,212 @@
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>Внешняя админка</t>
+          <t>Сайт / виджет</t>
         </is>
       </c>
       <c r="F136" s="8" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>escalation</t>
         </is>
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>Bearer &lt;JWT&gt; | Bearer sak_…</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I136" s="8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J136" s="7" t="inlineStr"/>
+      <c r="K136" s="7" t="inlineStr"/>
+      <c r="L136" s="7" t="inlineStr"/>
+      <c r="M136" s="7" t="inlineStr">
+        <is>
+          <t>true — точка входа «к менеджеру».</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/retention/deeplink</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>Сайт / виджет</t>
+        </is>
+      </c>
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t>lang</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>string (код или локаль)</t>
+        </is>
+      </c>
+      <c r="H137" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I137" s="8" t="inlineStr">
+        <is>
+          <t>ru</t>
+        </is>
+      </c>
+      <c r="J137" s="7" t="inlineStr"/>
+      <c r="K137" s="7" t="inlineStr"/>
+      <c r="L137" s="7" t="inlineStr"/>
+      <c r="M137" s="7" t="inlineStr">
+        <is>
+          <t>Язык, в котором откроется бот.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/retention/deeplink</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F138" s="8" t="inlineStr">
+        <is>
+          <t>deep_link</t>
+        </is>
+      </c>
+      <c r="G138" s="8" t="inlineStr">
+        <is>
+          <t>string (URL)</t>
+        </is>
+      </c>
+      <c r="H138" s="7" t="inlineStr">
+        <is>
           <t>да</t>
         </is>
       </c>
-      <c r="I136" s="8" t="inlineStr">
-        <is>
-          <t>Bearer sak_9f2c…</t>
-        </is>
-      </c>
-      <c r="J136" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K136" s="7" t="inlineStr">
-        <is>
-          <t>Сервисный ключ несёт ОДНУ роль в ОДНОМ скоупе (global/partner/product); деактивация действует со следующего запроса</t>
-        </is>
-      </c>
-      <c r="L136" s="7" t="inlineStr">
-        <is>
-          <t>401 unauthorized · 403 forbidden (вне скоупа)</t>
-        </is>
-      </c>
-      <c r="M136" s="7" t="inlineStr">
-        <is>
-          <t>Единая авторизация всего админ-контура. Для машин — ключ sak_…, который выдаётся человеком-админом и показывается ровно один раз.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>GET /admin/structure</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D137" s="10" t="inlineStr">
+      <c r="I138" s="8" t="inlineStr">
+        <is>
+          <t>https://t.me/brand_bot?start=Ax7…</t>
+        </is>
+      </c>
+      <c r="J138" s="7" t="inlineStr"/>
+      <c r="K138" s="7" t="inlineStr"/>
+      <c r="L138" s="7" t="inlineStr"/>
+      <c r="M138" s="7" t="inlineStr">
+        <is>
+          <t>Ссылка для кнопки. Нонс погашается при первом /start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/retention/deeplink</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D139" s="10" t="inlineStr">
         <is>
           <t>Выход</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="inlineStr"/>
-      <c r="G137" s="5" t="inlineStr"/>
-      <c r="H137" s="4" t="inlineStr"/>
-      <c r="I137" s="5" t="inlineStr"/>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K137" s="4" t="inlineStr"/>
-      <c r="L137" s="4" t="inlineStr"/>
-      <c r="M137" s="4" t="inlineStr">
-        <is>
-          <t>Дерево партнёров и продуктов — точка синхронизации справочников с внешними системами.</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>GET /admin/me</t>
-        </is>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D138" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F138" s="5" t="inlineStr"/>
-      <c r="G138" s="5" t="inlineStr"/>
-      <c r="H138" s="4" t="inlineStr"/>
-      <c r="I138" s="5" t="inlineStr"/>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K138" s="4" t="inlineStr"/>
-      <c r="L138" s="4" t="inlineStr"/>
-      <c r="M138" s="4" t="inlineStr">
-        <is>
-          <t>Кто вызывает и какие у него скоупы — для проверки прав на своей стороне.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>POST /admin/partners, PUT /admin/partners/{id}</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D139" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="inlineStr"/>
-      <c r="G139" s="5" t="inlineStr"/>
-      <c r="H139" s="4" t="inlineStr"/>
-      <c r="I139" s="5" t="inlineStr"/>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K139" s="4" t="inlineStr"/>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>401 · 403</t>
-        </is>
-      </c>
-      <c r="M139" s="4" t="inlineStr">
-        <is>
-          <t>Заведение и правка партнёра.</t>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t>nonce</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H139" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I139" s="8" t="inlineStr">
+        <is>
+          <t>Ax7kQ…</t>
+        </is>
+      </c>
+      <c r="J139" s="7" t="inlineStr"/>
+      <c r="K139" s="7" t="inlineStr"/>
+      <c r="L139" s="7" t="inlineStr"/>
+      <c r="M139" s="7" t="inlineStr">
+        <is>
+          <t>Тот же одноразовый токен отдельным полем.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>Admin API</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>POST /admin/products</t>
+          <t>POST /telegram/webhook/{secret}</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -8098,14 +8122,14 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>Вход/Выход</t>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>Внешняя админка</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr"/>
@@ -8114,39 +8138,39 @@
       <c r="I140" s="5" t="inlineStr"/>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+          <t>путь = webhook-токен продукта (роутинг) + заголовок X-Telegram-Bot-Api-Secret-Token</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>Создание продукта автоматически засевает рабочую конфигурацию</t>
+          <t>Всегда быстрый 200 (иначе Telegram ретраит); ход ИИ выполняется в фоне</t>
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>401 · 403</t>
+          <t>403 bad_secret_token · неизвестный токен пути, неактивный продукт или выключенный ретеншен → тихий 200</t>
         </is>
       </c>
       <c r="M140" s="4" t="inlineStr">
         <is>
-          <t>Заведение казино. В ответе — публичный widget_key для встраивания виджета.</t>
+          <t>Приём апдейтов Telegram — второй фасад над тем же ИИ-ядром.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>Admin API</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>PUT /admin/products/{id}</t>
+          <t>POST /telegram/webhook/{secret}</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>Поле запроса</t>
+          <t>Заголовок</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
@@ -8156,51 +8180,47 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>Внешняя админка</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="F141" s="8" t="inlineStr">
         <is>
-          <t>name, active, site_url, turnstile_site_key</t>
+          <t>X-Telegram-Bot-Api-Secret-Token</t>
         </is>
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>string / bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I141" s="8" t="inlineStr">
         <is>
-          <t>{"site_url":"https://brand.com"}</t>
-        </is>
-      </c>
-      <c r="J141" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
+          <t>b4c9…</t>
+        </is>
+      </c>
+      <c r="J141" s="7" t="inlineStr"/>
       <c r="K141" s="7" t="inlineStr"/>
       <c r="L141" s="7" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr">
         <is>
-          <t>Публичная конфигурация продукта.</t>
+          <t>Секрет, заданный при регистрации вебхука. Защищает от подделки апдейтов тем, кто узнал URL.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>Admin API</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>PUT /admin/products/{id}/secrets</t>
+          <t>POST /telegram/webhook/{secret}</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
@@ -8215,43 +8235,35 @@
       </c>
       <c r="E142" s="7" t="inlineStr">
         <is>
-          <t>Внешняя админка</t>
+          <t>Telegram</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr">
         <is>
-          <t>openai_key_primary, openai_key_fallback, handshake_secret, telegram_bot_token, player_api_key, turnstile_secret</t>
+          <t>update</t>
         </is>
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object (Telegram Bot API)</t>
         </is>
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
-          <t>{"handshake_secret":"…"}</t>
-        </is>
-      </c>
-      <c r="J142" s="7" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K142" s="7" t="inlineStr">
-        <is>
-          <t>Только запись: наружу возвращаются лишь флаги «задан/не задан»</t>
-        </is>
-      </c>
+          <t>{"update_id":1,"message":{…}}</t>
+        </is>
+      </c>
+      <c r="J142" s="7" t="inlineStr"/>
+      <c r="K142" s="7" t="inlineStr"/>
       <c r="L142" s="7" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr">
         <is>
-          <t>Секреты продукта. Хранятся зашифрованными; через API не читаются.</t>
+          <t>Стандартный формат Telegram.</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8275,7 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>POST /admin/products/{id}/widget-key</t>
+          <t>POST /admin/login</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -8287,155 +8299,199 @@
       <c r="I143" s="5" t="inlineStr"/>
       <c r="J143" s="4" t="inlineStr">
         <is>
+          <t>нет (публичный)</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>Лимит попыток входа с IP</t>
+        </is>
+      </c>
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>401 · 429</t>
+        </is>
+      </c>
+      <c r="M143" s="4" t="inlineStr">
+        <is>
+          <t>Вход человека-администратора: email + пароль → JWT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>POST /admin/login</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F144" s="8" t="inlineStr">
+        <is>
+          <t>email / password</t>
+        </is>
+      </c>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
+          <t>string / string</t>
+        </is>
+      </c>
+      <c r="H144" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I144" s="8" t="inlineStr">
+        <is>
+          <t>ops@brand.com</t>
+        </is>
+      </c>
+      <c r="J144" s="7" t="inlineStr"/>
+      <c r="K144" s="7" t="inlineStr"/>
+      <c r="L144" s="7" t="inlineStr"/>
+      <c r="M144" s="7" t="inlineStr">
+        <is>
+          <t>Учётная запись администратора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>POST /admin/login</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F145" s="8" t="inlineStr">
+        <is>
+          <t>token / role / email / memberships</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t>string (JWT) / string / string / [{scope,role,…}]</t>
+        </is>
+      </c>
+      <c r="H145" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I145" s="8" t="inlineStr">
+        <is>
+          <t>eyJhbGciOiJIUzI1NiJ9…</t>
+        </is>
+      </c>
+      <c r="J145" s="7" t="inlineStr"/>
+      <c r="K145" s="7" t="inlineStr"/>
+      <c r="L145" s="7" t="inlineStr"/>
+      <c r="M145" s="7" t="inlineStr">
+        <is>
+          <t>Админ-токен (продлевается сам при активной работе) + роль, email и список членств для проверки прав на своей стороне.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>* /admin/*</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>Заголовок</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F146" s="8" t="inlineStr">
+        <is>
+          <t>Authorization</t>
+        </is>
+      </c>
+      <c r="G146" s="8" t="inlineStr">
+        <is>
+          <t>Bearer &lt;JWT&gt; | Bearer sak_…</t>
+        </is>
+      </c>
+      <c r="H146" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I146" s="8" t="inlineStr">
+        <is>
+          <t>Bearer sak_9f2c…</t>
+        </is>
+      </c>
+      <c r="J146" s="7" t="inlineStr">
+        <is>
           <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
         </is>
       </c>
-      <c r="K143" s="4" t="inlineStr"/>
-      <c r="L143" s="4" t="inlineStr"/>
-      <c r="M143" s="4" t="inlineStr">
-        <is>
-          <t>Ротация публичного ключа виджета.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B144" s="5" t="inlineStr">
-        <is>
-          <t>GET /admin/overview, /timeseries, /by-topic, /by-language</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D144" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F144" s="5" t="inlineStr"/>
-      <c r="G144" s="5" t="inlineStr"/>
-      <c r="H144" s="4" t="inlineStr"/>
-      <c r="I144" s="5" t="inlineStr"/>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K144" s="4" t="inlineStr">
-        <is>
-          <t>Параметры периода from/to, скоуп product_id</t>
-        </is>
-      </c>
-      <c r="L144" s="4" t="inlineStr"/>
-      <c r="M144" s="4" t="inlineStr">
-        <is>
-          <t>Метрики поддержки для выгрузки во внешнюю аналитику.</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B145" s="5" t="inlineStr">
-        <is>
-          <t>GET /admin/ai-costs</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D145" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F145" s="5" t="inlineStr"/>
-      <c r="G145" s="5" t="inlineStr"/>
-      <c r="H145" s="4" t="inlineStr"/>
-      <c r="I145" s="5" t="inlineStr"/>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K145" s="4" t="inlineStr">
-        <is>
-          <t>Разрез по типу вызова: chat | agent | review | media</t>
-        </is>
-      </c>
-      <c r="L145" s="4" t="inlineStr"/>
-      <c r="M145" s="4" t="inlineStr">
-        <is>
-          <t>Полные траты на ИИ — сумма сходится со счётом провайдера.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="4" t="inlineStr">
-        <is>
-          <t>Admin API</t>
-        </is>
-      </c>
-      <c r="B146" s="5" t="inlineStr">
-        <is>
-          <t>GET /admin/sessions, /admin/session/{id}</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D146" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>Внешняя админка</t>
-        </is>
-      </c>
-      <c r="F146" s="5" t="inlineStr"/>
-      <c r="G146" s="5" t="inlineStr"/>
-      <c r="H146" s="4" t="inlineStr"/>
-      <c r="I146" s="5" t="inlineStr"/>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
-        </is>
-      </c>
-      <c r="K146" s="4" t="inlineStr">
-        <is>
-          <t>Пагинация page/page_size</t>
-        </is>
-      </c>
-      <c r="L146" s="4" t="inlineStr"/>
-      <c r="M146" s="4" t="inlineStr">
-        <is>
-          <t>Журнал диалогов и полная стенограмма с постоимостью — выгрузка в общее хранилище обращений.</t>
+      <c r="K146" s="7" t="inlineStr">
+        <is>
+          <t>Сервисный ключ несёт ОДНУ роль в ОДНОМ скоупе (global/partner/product); деактивация действует со следующего запроса</t>
+        </is>
+      </c>
+      <c r="L146" s="7" t="inlineStr">
+        <is>
+          <t>401 unauthorized · 403 forbidden (вне скоупа)</t>
+        </is>
+      </c>
+      <c r="M146" s="7" t="inlineStr">
+        <is>
+          <t>Единая авторизация всего админ-контура. Для машин — ключ sak_…, который выдаётся человеком-админом и показывается ровно один раз.</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8503,7 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/audit</t>
+          <t>GET /admin/structure</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -8478,7 +8534,7 @@
       <c r="L147" s="4" t="inlineStr"/>
       <c r="M147" s="4" t="inlineStr">
         <is>
-          <t>Аудит административных изменений — для общего SIEM/комплаенс-контура.</t>
+          <t>Дерево партнёров и продуктов — точка синхронизации справочников с внешними системами.</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8546,7 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/quality/overview, /admin/quality/reviews</t>
+          <t>GET /admin/me</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -8521,7 +8577,7 @@
       <c r="L148" s="4" t="inlineStr"/>
       <c r="M148" s="4" t="inlineStr">
         <is>
-          <t>Оценки качества диалогов (1..5, теги, пробелы в базе знаний).</t>
+          <t>Кто вызывает и какие у него скоупы — для проверки прав на своей стороне.</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8589,7 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>GET /admin/retention/overview, /funnel, /effectiveness</t>
+          <t>POST /admin/partners, PUT /admin/partners/{id}</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -8541,9 +8597,9 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D149" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -8561,10 +8617,14 @@
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr"/>
-      <c r="L149" s="4" t="inlineStr"/>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>401 · 403</t>
+        </is>
+      </c>
       <c r="M149" s="4" t="inlineStr">
         <is>
-          <t>Метрики Telegram-фасада: воронка и результативность касаний.</t>
+          <t>Заведение и правка партнёра.</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8636,7 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>POST /admin/api-keys</t>
+          <t>POST /admin/products</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -8600,12 +8660,12 @@
       <c r="I150" s="5" t="inlineStr"/>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>только человек-админ (ключом ключ не выпустить)</t>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
         </is>
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>Открытый текст ключа возвращается РОВНО ОДИН РАЗ; хранится только хеш</t>
+          <t>Создание продукта автоматически засевает рабочую конфигурацию</t>
         </is>
       </c>
       <c r="L150" s="4" t="inlineStr">
@@ -8615,113 +8675,141 @@
       </c>
       <c r="M150" s="4" t="inlineStr">
         <is>
-          <t>Выпуск сервисного ключа sak_… для внешней системы.</t>
+          <t>Заведение казино. В ответе — публичный widget_key для встраивания виджета.</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="4" t="inlineStr">
+      <c r="A151" s="7" t="inlineStr">
         <is>
           <t>Admin API</t>
         </is>
       </c>
-      <c r="B151" s="5" t="inlineStr">
-        <is>
-          <t>GET /admin/mcp/manifest</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D151" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E151" s="4" t="inlineStr">
+      <c r="B151" s="8" t="inlineStr">
+        <is>
+          <t>PUT /admin/products/{id}</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
         <is>
           <t>Внешняя админка</t>
         </is>
       </c>
-      <c r="F151" s="5" t="inlineStr"/>
-      <c r="G151" s="5" t="inlineStr"/>
-      <c r="H151" s="4" t="inlineStr"/>
-      <c r="I151" s="5" t="inlineStr"/>
-      <c r="J151" s="4" t="inlineStr">
+      <c r="F151" s="8" t="inlineStr">
+        <is>
+          <t>name, active, site_url, turnstile_site_key</t>
+        </is>
+      </c>
+      <c r="G151" s="8" t="inlineStr">
+        <is>
+          <t>string / bool</t>
+        </is>
+      </c>
+      <c r="H151" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I151" s="8" t="inlineStr">
+        <is>
+          <t>{"site_url":"https://brand.com"}</t>
+        </is>
+      </c>
+      <c r="J151" s="7" t="inlineStr">
         <is>
           <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
         </is>
       </c>
-      <c r="K151" s="4" t="inlineStr"/>
-      <c r="L151" s="4" t="inlineStr"/>
-      <c r="M151" s="4" t="inlineStr">
-        <is>
-          <t>Машиночитаемое описание админ-инструментов (MCP) для агентских клиентов.</t>
+      <c r="K151" s="7" t="inlineStr"/>
+      <c r="L151" s="7" t="inlineStr"/>
+      <c r="M151" s="7" t="inlineStr">
+        <is>
+          <t>Публичная конфигурация продукта.</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="4" t="inlineStr">
+      <c r="A152" s="7" t="inlineStr">
         <is>
           <t>Admin API</t>
         </is>
       </c>
-      <c r="B152" s="5" t="inlineStr">
-        <is>
-          <t>GET /openapi.json, /docs, /redoc</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>Эндпойнт</t>
-        </is>
-      </c>
-      <c r="D152" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
-        </is>
-      </c>
-      <c r="E152" s="4" t="inlineStr">
+      <c r="B152" s="8" t="inlineStr">
+        <is>
+          <t>PUT /admin/products/{id}/secrets</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
         <is>
           <t>Внешняя админка</t>
         </is>
       </c>
-      <c r="F152" s="5" t="inlineStr"/>
-      <c r="G152" s="5" t="inlineStr"/>
-      <c r="H152" s="4" t="inlineStr"/>
-      <c r="I152" s="5" t="inlineStr"/>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>нет (публичный)</t>
-        </is>
-      </c>
-      <c r="K152" s="4" t="inlineStr">
-        <is>
-          <t>Отдаётся только если включено на деплое</t>
-        </is>
-      </c>
-      <c r="L152" s="4" t="inlineStr">
-        <is>
-          <t>404, когда выключено</t>
-        </is>
-      </c>
-      <c r="M152" s="4" t="inlineStr">
-        <is>
-          <t>Машиночитаемая схема всего API — для генерации клиентов.</t>
+      <c r="F152" s="8" t="inlineStr">
+        <is>
+          <t>openai_key_primary, openai_key_fallback, handshake_secret, telegram_bot_token, player_api_key, turnstile_secret, partner_out_key, email_api_key</t>
+        </is>
+      </c>
+      <c r="G152" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I152" s="8" t="inlineStr">
+        <is>
+          <t>{"handshake_secret":"…"}</t>
+        </is>
+      </c>
+      <c r="J152" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K152" s="7" t="inlineStr">
+        <is>
+          <t>Только запись: наружу возвращаются лишь флаги «задан/не задан»</t>
+        </is>
+      </c>
+      <c r="L152" s="7" t="inlineStr"/>
+      <c r="M152" s="7" t="inlineStr">
+        <is>
+          <t>Секреты продукта. Хранятся зашифрованными; через API не читаются. partner_out_key — Bearer наших исходящих вызовов в казино (offer-grant, delivery-order); email_api_key — App API key Customer.io.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>Исходящие</t>
+          <t>Admin API</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
+          <t>POST /admin/products/{id}/widget-key</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -8729,14 +8817,14 @@
           <t>Эндпойнт</t>
         </is>
       </c>
-      <c r="D153" s="10" t="inlineStr">
-        <is>
-          <t>Выход</t>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Внешняя админка</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr"/>
@@ -8745,39 +8833,31 @@
       <c r="I153" s="5" t="inlineStr"/>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>Bearer &lt;player_api_key продукта&gt;</t>
-        </is>
-      </c>
-      <c r="K153" s="4" t="inlineStr">
-        <is>
-          <t>Таймаут 8 с · срабатывает, когда снапшот старше часа · только публичные адреса (защита от SSRF, пиннинг IP)</t>
-        </is>
-      </c>
-      <c r="L153" s="4" t="inlineStr">
-        <is>
-          <t>Любая ошибка тиха: остаётся прежний снапшот</t>
-        </is>
-      </c>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K153" s="4" t="inlineStr"/>
+      <c r="L153" s="4" t="inlineStr"/>
       <c r="M153" s="4" t="inlineStr">
         <is>
-          <t>ЛЕНИВОЕ обновление профиля игрока перед ходом бота. Эндпойнт реализует ПАРТНЁР — это требование к чужой системе.</t>
+          <t>Ротация публичного ключа виджета.</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t>Исходящие</t>
-        </is>
-      </c>
-      <c r="B154" s="8" t="inlineStr">
-        <is>
-          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
-        </is>
-      </c>
-      <c r="C154" s="7" t="inlineStr">
-        <is>
-          <t>Поле запроса</t>
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>GET /admin/overview, /timeseries, /by-topic, /by-language</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
@@ -8785,104 +8865,88 @@
           <t>Выход</t>
         </is>
       </c>
-      <c r="E154" s="7" t="inlineStr">
-        <is>
-          <t>Наш сервис</t>
-        </is>
-      </c>
-      <c r="F154" s="8" t="inlineStr">
-        <is>
-          <t>player_id</t>
-        </is>
-      </c>
-      <c r="G154" s="8" t="inlineStr">
-        <is>
-          <t>query string</t>
-        </is>
-      </c>
-      <c r="H154" s="7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I154" s="8" t="inlineStr">
-        <is>
-          <t>1048576</t>
-        </is>
-      </c>
-      <c r="J154" s="7" t="inlineStr"/>
-      <c r="K154" s="7" t="inlineStr"/>
-      <c r="L154" s="7" t="inlineStr"/>
-      <c r="M154" s="7" t="inlineStr">
-        <is>
-          <t>Кого запрашиваем.</t>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr"/>
+      <c r="G154" s="5" t="inlineStr"/>
+      <c r="H154" s="4" t="inlineStr"/>
+      <c r="I154" s="5" t="inlineStr"/>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K154" s="4" t="inlineStr">
+        <is>
+          <t>Параметры периода from/to, скоуп product_id</t>
+        </is>
+      </c>
+      <c r="L154" s="4" t="inlineStr"/>
+      <c r="M154" s="4" t="inlineStr">
+        <is>
+          <t>Метрики поддержки для выгрузки во внешнюю аналитику.</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="7" t="inlineStr">
-        <is>
-          <t>Исходящие</t>
-        </is>
-      </c>
-      <c r="B155" s="8" t="inlineStr">
-        <is>
-          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
-        </is>
-      </c>
-      <c r="C155" s="7" t="inlineStr">
-        <is>
-          <t>Поле ответа</t>
-        </is>
-      </c>
-      <c r="D155" s="9" t="inlineStr">
-        <is>
-          <t>Вход</t>
-        </is>
-      </c>
-      <c r="E155" s="7" t="inlineStr">
-        <is>
-          <t>CRM казино</t>
-        </is>
-      </c>
-      <c r="F155" s="8" t="inlineStr">
-        <is>
-          <t>full_name, email, activation_status, country, balance, vip_level, registration_date, last_login_at, last_played_at, last_deposit_at</t>
-        </is>
-      </c>
-      <c r="G155" s="8" t="inlineStr">
-        <is>
-          <t>JSON-объект</t>
-        </is>
-      </c>
-      <c r="H155" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="I155" s="8" t="inlineStr">
-        <is>
-          <t>{"full_name":"Андрей","balance":"150.00 USDT"}</t>
-        </is>
-      </c>
-      <c r="J155" s="7" t="inlineStr"/>
-      <c r="K155" s="7" t="inlineStr"/>
-      <c r="L155" s="7" t="inlineStr"/>
-      <c r="M155" s="7" t="inlineStr">
-        <is>
-          <t>Ожидаемый ответ партнёра. Лишние поля игнорируются — берётся тот же белый список, что и везде.</t>
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>GET /admin/ai-costs</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D155" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr"/>
+      <c r="G155" s="5" t="inlineStr"/>
+      <c r="H155" s="4" t="inlineStr"/>
+      <c r="I155" s="5" t="inlineStr"/>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>Разрез по типу вызова: chat | agent | review | media</t>
+        </is>
+      </c>
+      <c r="L155" s="4" t="inlineStr"/>
+      <c r="M155" s="4" t="inlineStr">
+        <is>
+          <t>Полные траты на ИИ — сумма сходится со счётом провайдера.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>Исходящие</t>
+          <t>Admin API</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>Telegram Bot API</t>
+          <t>GET /admin/sessions, /admin/session/{id}</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -8897,7 +8961,7 @@
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Внешняя админка</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr"/>
@@ -8906,30 +8970,30 @@
       <c r="I156" s="5" t="inlineStr"/>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>токен бота продукта (хранится зашифрованным)</t>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>Ретраи; недоступный игрок помечается как unreachable</t>
+          <t>Пагинация page/page_size</t>
         </is>
       </c>
       <c r="L156" s="4" t="inlineStr"/>
       <c r="M156" s="4" t="inlineStr">
         <is>
-          <t>sendMessage / sendPhoto / sendVideo / getChatMember / setWebhook.</t>
+          <t>Журнал диалогов и полная стенограмма с постоимостью — выгрузка в общее хранилище обращений.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>Исходящие</t>
+          <t>Admin API</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>OpenAI API</t>
+          <t>GET /admin/audit</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -8944,7 +9008,7 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Наш сервис</t>
+          <t>Внешняя админка</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr"/>
@@ -8953,30 +9017,665 @@
       <c r="I157" s="5" t="inlineStr"/>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>ключ продукта (1–2 шт.), иначе ключ деплоя</t>
-        </is>
-      </c>
-      <c r="K157" s="4" t="inlineStr">
-        <is>
-          <t>Два ключа с автопереключением; предохранитель при сбое провайдера; таймауты по назначению вызова</t>
-        </is>
-      </c>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K157" s="4" t="inlineStr"/>
       <c r="L157" s="4" t="inlineStr"/>
       <c r="M157" s="4" t="inlineStr">
         <is>
+          <t>Аудит административных изменений — для общего SIEM/комплаенс-контура.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>GET /admin/quality/overview, /admin/quality/reviews</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr"/>
+      <c r="G158" s="5" t="inlineStr"/>
+      <c r="H158" s="4" t="inlineStr"/>
+      <c r="I158" s="5" t="inlineStr"/>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K158" s="4" t="inlineStr"/>
+      <c r="L158" s="4" t="inlineStr"/>
+      <c r="M158" s="4" t="inlineStr">
+        <is>
+          <t>Оценки качества диалогов (1..5, теги, пробелы в базе знаний).</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>GET /admin/retention/overview, /timeseries, /funnel, /effectiveness</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D159" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr"/>
+      <c r="G159" s="5" t="inlineStr"/>
+      <c r="H159" s="4" t="inlineStr"/>
+      <c r="I159" s="5" t="inlineStr"/>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K159" s="4" t="inlineStr"/>
+      <c r="L159" s="4" t="inlineStr"/>
+      <c r="M159" s="4" t="inlineStr">
+        <is>
+          <t>Метрики Telegram-фасада: воронка и результативность касаний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>PUT /admin/retention/partner-endpoints</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F160" s="8" t="inlineStr">
+        <is>
+          <t>offer_grant_url, delivery_endpoint_url</t>
+        </is>
+      </c>
+      <c r="G160" s="8" t="inlineStr">
+        <is>
+          <t>string (https URL)</t>
+        </is>
+      </c>
+      <c r="H160" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I160" s="8" t="inlineStr">
+        <is>
+          <t>{"offer_grant_url":"https://cms.brand.com/bonus/grant"}</t>
+        </is>
+      </c>
+      <c r="J160" s="7" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K160" s="7" t="inlineStr">
+        <is>
+          <t>Только публичные адреса (защита от SSRF, пиннинг DNS)</t>
+        </is>
+      </c>
+      <c r="L160" s="7" t="inlineStr"/>
+      <c r="M160" s="7" t="inlineStr">
+        <is>
+          <t>Куда наш сервис шлёт исходящие вызовы казино: выдача бонуса и заказ делегированной доставки (см. область «Исходящие»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>GET|PUT|POST /admin/integration-checklist*</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr"/>
+      <c r="G161" s="5" t="inlineStr"/>
+      <c r="H161" s="4" t="inlineStr"/>
+      <c r="I161" s="5" t="inlineStr"/>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ); запись — только глобальный админ</t>
+        </is>
+      </c>
+      <c r="K161" s="4" t="inlineStr"/>
+      <c r="L161" s="4" t="inlineStr"/>
+      <c r="M161" s="4" t="inlineStr">
+        <is>
+          <t>Деплой-уровневый чек-лист интеграционных зависимостей от внешних команд (бонус-CMS, RG-фид, доставка push, Customer.io, BI): статусы и заметки по каждому пункту.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>GET|PUT /admin/retention/* (оркестратор)</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr"/>
+      <c r="G162" s="5" t="inlineStr"/>
+      <c r="H162" s="4" t="inlineStr"/>
+      <c r="I162" s="5" t="inlineStr"/>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t>Скоуп продукта; RG-аудит и set-status — глобальный админ</t>
+        </is>
+      </c>
+      <c r="L162" s="4" t="inlineStr"/>
+      <c r="M162" s="4" t="inlineStr">
+        <is>
+          <t>Управление оркестратором ретеншена: holdout/uplift, RG-guard, частотные капы и приоритеты, скоринг/когорты, каталог офферов и гранты, journeys, шаблоны сценариев, каналы и журнал доставок. Полный список ручек — /integration-admin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>POST /admin/api-keys</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>Вход/Выход</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr"/>
+      <c r="G163" s="5" t="inlineStr"/>
+      <c r="H163" s="4" t="inlineStr"/>
+      <c r="I163" s="5" t="inlineStr"/>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>только человек-админ (ключом ключ не выпустить)</t>
+        </is>
+      </c>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>Открытый текст ключа возвращается РОВНО ОДИН РАЗ; хранится только хеш</t>
+        </is>
+      </c>
+      <c r="L163" s="4" t="inlineStr">
+        <is>
+          <t>401 · 403</t>
+        </is>
+      </c>
+      <c r="M163" s="4" t="inlineStr">
+        <is>
+          <t>Выпуск сервисного ключа sak_… для внешней системы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>GET /admin/mcp/manifest</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr"/>
+      <c r="G164" s="5" t="inlineStr"/>
+      <c r="H164" s="4" t="inlineStr"/>
+      <c r="I164" s="5" t="inlineStr"/>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;admin JWT&gt; ИЛИ Bearer sak_… (сервисный ключ)</t>
+        </is>
+      </c>
+      <c r="K164" s="4" t="inlineStr"/>
+      <c r="L164" s="4" t="inlineStr"/>
+      <c r="M164" s="4" t="inlineStr">
+        <is>
+          <t>Машиночитаемое описание админ-инструментов (MCP) для агентских клиентов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>Admin API</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>GET /openapi.json, /docs, /redoc</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D165" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>Внешняя админка</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr"/>
+      <c r="G165" s="5" t="inlineStr"/>
+      <c r="H165" s="4" t="inlineStr"/>
+      <c r="I165" s="5" t="inlineStr"/>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>нет (публичный)</t>
+        </is>
+      </c>
+      <c r="K165" s="4" t="inlineStr">
+        <is>
+          <t>Отдаётся только если включено на деплое</t>
+        </is>
+      </c>
+      <c r="L165" s="4" t="inlineStr">
+        <is>
+          <t>404, когда выключено</t>
+        </is>
+      </c>
+      <c r="M165" s="4" t="inlineStr">
+        <is>
+          <t>Машиночитаемая схема всего API — для генерации клиентов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr"/>
+      <c r="G166" s="5" t="inlineStr"/>
+      <c r="H166" s="4" t="inlineStr"/>
+      <c r="I166" s="5" t="inlineStr"/>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>Bearer &lt;player_api_key продукта&gt;</t>
+        </is>
+      </c>
+      <c r="K166" s="4" t="inlineStr">
+        <is>
+          <t>Таймаут 8 с · срабатывает, когда снапшот старше часа · только публичные адреса (защита от SSRF, пиннинг IP)</t>
+        </is>
+      </c>
+      <c r="L166" s="4" t="inlineStr">
+        <is>
+          <t>Любая ошибка тиха: остаётся прежний снапшот</t>
+        </is>
+      </c>
+      <c r="M166" s="4" t="inlineStr">
+        <is>
+          <t>ЛЕНИВОЕ обновление профиля игрока перед ходом бота. Эндпойнт реализует ПАРТНЁР — это требование к чужой системе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="inlineStr">
+        <is>
+          <t>Поле запроса</t>
+        </is>
+      </c>
+      <c r="D167" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F167" s="8" t="inlineStr">
+        <is>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>query string</t>
+        </is>
+      </c>
+      <c r="H167" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I167" s="8" t="inlineStr">
+        <is>
+          <t>1048576</t>
+        </is>
+      </c>
+      <c r="J167" s="7" t="inlineStr"/>
+      <c r="K167" s="7" t="inlineStr"/>
+      <c r="L167" s="7" t="inlineStr"/>
+      <c r="M167" s="7" t="inlineStr">
+        <is>
+          <t>Кого запрашиваем.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>GET &lt;player_api_url&gt; (Player API партнёра)</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t>Поле ответа</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="inlineStr">
+        <is>
+          <t>Вход</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>CRM казино</t>
+        </is>
+      </c>
+      <c r="F168" s="8" t="inlineStr">
+        <is>
+          <t>full_name, email, activation_status, country, balance, vip_level, registration_date, last_login_at, last_played_at, last_deposit_at</t>
+        </is>
+      </c>
+      <c r="G168" s="8" t="inlineStr">
+        <is>
+          <t>JSON-объект</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="I168" s="8" t="inlineStr">
+        <is>
+          <t>{"full_name":"Андрей","balance":"150.00 USDT"}</t>
+        </is>
+      </c>
+      <c r="J168" s="7" t="inlineStr"/>
+      <c r="K168" s="7" t="inlineStr"/>
+      <c r="L168" s="7" t="inlineStr"/>
+      <c r="M168" s="7" t="inlineStr">
+        <is>
+          <t>Ожидаемый ответ партнёра. Лишние поля игнорируются — берётся тот же белый список, что и везде.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>Telegram Bot API</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D169" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr"/>
+      <c r="G169" s="5" t="inlineStr"/>
+      <c r="H169" s="4" t="inlineStr"/>
+      <c r="I169" s="5" t="inlineStr"/>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>токен бота продукта (хранится зашифрованным)</t>
+        </is>
+      </c>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t>Ретраи; недоступный игрок помечается как unreachable</t>
+        </is>
+      </c>
+      <c r="L169" s="4" t="inlineStr"/>
+      <c r="M169" s="4" t="inlineStr">
+        <is>
+          <t>sendMessage / sendPhoto / sendVideo / getChatMember / setWebhook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>Исходящие</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>OpenAI API</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>Эндпойнт</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="inlineStr">
+        <is>
+          <t>Выход</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>Наш сервис</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr"/>
+      <c r="G170" s="5" t="inlineStr"/>
+      <c r="H170" s="4" t="inlineStr"/>
+      <c r="I170" s="5" t="inlineStr"/>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>ключ продукта (1–2 шт.), иначе ключ деплоя</t>
+        </is>
+      </c>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t>Два ключа с автопереключением; предохранитель при сбое провайдера; таймауты по назначению вызова</t>
+        </is>
+      </c>
+      <c r="L170" s="4" t="inlineStr"/>
+      <c r="M170" s="4" t="inlineStr">
+        <is>
           <t>Генерация ответов и фоновые проходы. Каждый вызов логируется с атрибуцией расходов.</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>Файл генерируется из кода: scripts/build_api_reference.py. Живая версия — /integration-reference на самом сервисе.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M157"/>
+  <autoFilter ref="A4:M170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/frontend/api-reference.xlsx
+++ b/frontend/api-reference.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="API" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Переменные текста" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API'!$A$4:$M$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Переменные текста'!$A$4:$H$214</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9678,4 +9680,8876 @@
   <autoFilter ref="A4:M170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H216"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Support Chat — переменные и тексты продукта</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Все переменные и куски текста, из которых собирается общение с игроком: подстановки базы знаний, переменные промпта, копирайт интерфейса и служебные теги. Одна строка — одна текстовая единица, все колонки фильтруются.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Ключ / как пишется в тексте</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Где используется</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Где редактируется</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Скоуп</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Язык значения</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Значение по умолчанию / пример</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>{deposit_methods}</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>USDT (crypto: TRC20/ERC20/BEP20), Visa/Mastercard, local payment methods</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Deposit methods (per market)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>{crypto_networks}</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>TRC20, ERC20, BEP20</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Supported crypto networks</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>{card_deposit}</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Visa, Mastercard (availability depends on market)</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Card availability by market</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>{local_payment_methods}</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>{{LOCAL_PAYMENT_METHODS}} (set per brand/market)</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Local payment systems (per market)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>{min_deposit}</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>10 USDT</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Minimum deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>{max_deposit}</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>1000 USDT</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Maximum deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>{deposit_fee}</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>0% (no deposit fee)</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Deposit fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>{deposit_speed}</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>crypto: after network confirmations (usually minutes); cards: instant</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Deposit crediting speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>{deposit_flow}</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>wallet -&gt; method -&gt; amount -&gt; confirm</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Exact deposit steps (UI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>{currencies}</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Account currencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>{fiat_conversion}</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>applied at the transaction rate, shown before confirmation (test)</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Fiat-to-crypto conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>{decline_reasons}</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>security checks, method/country limits, bank restrictions, incorrect details</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Payment decline reasons/codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>{deposit_address_policy}</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>address tied to account; take the current one from the deposit page before each transfer</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Deposit address policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>{withdrawal_methods}</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>USDT, BTC (crypto); cards/e-wallets where available</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Withdrawal methods (per market)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>{withdrawal_to_source}</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>closed-loop: withdraw to the deposit method</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Return-to-source rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>{min_withdrawal}</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>20 USDT</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Minimum withdrawal</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>{max_withdrawal}</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>1000 USDT per withdrawal</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Maximum withdrawal per transaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>{daily_withdrawal_limit}</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>5000 USDT/day (test)</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Daily withdrawal limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>{withdrawal_period_limits}</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>weekly 20000 USDT, monthly 50000 USDT (test)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Weekly/monthly withdrawal limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>{withdrawal_fee_pct}</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Withdrawal fee, percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>{withdrawal_processing_time}</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>up to 24h (crypto usually faster)</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Withdrawal processing time (SLA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>{withdrawal_flow}</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>wallet -&gt; withdraw -&gt; method -&gt; amount -&gt; details -&gt; confirm</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Exact withdrawal steps (UI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>{cancel_withdrawal_policy}</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>can cancel while Pending via support</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Withdrawal cancellation availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>{withdrawal_taxes}</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>per local jurisdiction; not withheld by the casino</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Withdrawal taxation</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>{kyc_documents}</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>government ID + proof of address + selfie with document</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>KYC document list</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>{kyc_trigger}</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>before first withdrawal</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>Mandatory verification trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>{kyc_sla}</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>up to 24h</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Document review time</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>{kyc_doc_format}</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>JPG/PNG/PDF, clear, full document visible, no glare</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Document format requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>{min_age}</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>18+</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Minimum age</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>{reg_fields}</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>email, password, date of birth, country</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Registration form fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>{editable_profile_fields}</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>contacts (email, phone) editable; KYC-confirmed data (name, DOB) locked</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Editable profile fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>{gdpr_deletion_process}</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>request via support; processed after active bonuses are closed and balance withdrawn</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>Account deletion process (GDPR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>{twofa_methods}</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>authenticator app, email, SMS</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Available 2FA methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>{password_policy}</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>min 8 chars, upper and lower case, a digit and a symbol</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>Password requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>{lockout_time_min}</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>15 minutes</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Lockout after failed logins, minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>{session_timeout_min}</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>30 minutes</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>Session timeout, minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>{min_bet}</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>0.20 USDT</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Minimum bet</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>{max_bet}</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>up to 100 USDT (varies by game/table) (test)</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>Maximum bet</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>{max_win_multiplier}</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>5000x (varies by game) (test)</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Maximum win multiplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>{active_sports}</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>football, basketball, tennis, esports (after sports section launch) (test)</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>Active sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>{providers}</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>NetEnt, Pragmatic Play, Evolution, Play'n GO, Hacksaw Gaming</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>Provider list</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>{provably_fair}</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>available for crash and instant games; verifiable by seed/hash per round</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>Provably Fair for crash/fast games</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>{demo_mode}</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>available for most slots (fun play, no real winnings) (test)</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>Demo mode (fun play)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>{welcome_bonus}</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>100% Match up to 200 USDT + 50 FS (test)</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>Welcome bonus value</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>{welcome_min_deposit}</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>10 USDT</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>Minimum deposit for Welcome bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>{game_weighting}</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>slots 100%, live and table 10%, blackjack and baccarat 0%</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>Game weighting for wagering (table)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>{promo_code_field}</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>Cashier/Deposit page -&gt; 'Promo code' field</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Promo code input field</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>{level_rewards_map}</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>per-level rewards (FS, bonus cash, perks) defined in the Loyalty Engine reward map</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>Level rewards map</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>{vip_thresholds}</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>Player -&gt; Bronze -&gt; Silver -&gt; Gold -&gt; Platinum -&gt; VIP by accumulated XP (50 levels / 6 classes)</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>VIP class thresholds</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>{multi_bonus_policy}</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>one deposit bonus active at a time; Welcome has top priority</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>Multiple-bonus policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>{daily_card_super_prize}</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>Reload 20% on next deposit</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Bonus card super prize</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>{license_info}</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>{{LICENSE_INFO}} (set per brand)</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>License and regulator</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>{restricted_countries}</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>{{RESTRICTED_COUNTRIES}} (set per brand)</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Restricted countries</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>{locales}</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>{{LOCALES}} (set per brand)</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>Site languages</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>{support_languages}</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>Spanish, Portuguese, English</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Support languages</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>{support_channels}</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>24/7 on-site chat, Telegram bot</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>Support channels</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>{app_platforms}</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>iOS, Android (PWA)</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>App platforms (PWA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>{supported_browsers}</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>Chrome, Safari, Opera, Firefox (current versions)</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>Supported browsers</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>{telegram_link_flow}</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>one-time token deep-link on bot subscription</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Telegram linking steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>{referral_reward}</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>10 USDT per 5 friends with KYC, wager x3, 14 days</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>Referral reward</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>{daily_card_days}</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Bonus card length, days</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>{support_hours}</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>24/7</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Support hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>{responsible_gaming_tools}</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>deposit/bet/time limits, self-exclusion, reality-check</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Responsible gaming tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>{mirror_channels}</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>Telegram channel, email newsletter, live bookmarks</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Mirror channels</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>{kyc_address_docs}</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>utility bill or bank statement (recent, with name and address)</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Address verification documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>{liveness_check}</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>selfie with document; short liveness check when required</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>Selfie/liveness verification requirement</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>{source_of_funds}</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>for large withdrawals: payslip / bank statement / proof of crypto origin (test)</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Source-of-funds verification (enhanced review)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>{social_login}</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>Google login available (test)</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>Social/Google login availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>{username_change}</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>username can be changed in profile; KYC-confirmed data stays locked</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Username change availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>{active_promos}</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>dynamic list from Bonuses Module (e.g. Kickstart Monday, Spin Mission Tuesday)</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>Current active promotions list</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>{bonus_optout}</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>yes - deposit without a bonus by declining it at the cashier</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>Deposit without bonus availability (opt-out)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>{welcome_wager_fs}</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>x20</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>Welcome free spins wager</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>{welcome_wager_match}</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>x35 (test)</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Welcome match bonus wager</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>{crash_multibet}</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>2 simultaneous bets per round with separate cash-outs</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>Two-bet support per crash round</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>{feature_buy}</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>available on selected slots (high-risk) (test)</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>Feature buy availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>{live_limits}</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>per table; typically 0.50-5000 USDT (varies) (test)</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>Live table betting limits</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>{new_games_section}</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>'New games' section in the casino catalog</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>New games catalogue section</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>{video_poker}</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>available (e.g. Jacks or Better) (test)</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>Video poker / poker formats availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>{privacy_policy}</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>{{PRIVACY_POLICY_URL}} (set per brand)</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>Privacy policy URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>{terms_url}</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>{{TERMS_URL}} (set per brand)</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>Terms and Conditions URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>{vip_withdrawal_limits}</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>higher limits for VIP (e.g. daily 20000 USDT) (test)</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>Withdrawal limits by status/VIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>{social_links}</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>{{SOCIAL_LINKS}} (set per brand)</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>Official social links and channels</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>{affiliate_program}</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>revenue-share affiliate program; terms via support (test)</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>Affiliate program terms and onboarding</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>{agent_program}</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>agent/partner cooperation program; terms via support (test)</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>Agent/cooperation program terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>{crypto_assets}</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>USDT, BTC, ETH</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Accepted cryptocurrencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>{crypto_confirmations}</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>USDT TRC20: 1; ERC20: 12; BTC: 2 (test)</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>Network confirmations for deposits/withdrawals</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>{deposit_refund}</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>disputed transactions handled via support; no bank chargebacks</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>Deposit refund / chargeback policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>{ewallets}</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>Skrill, Neteller (where available) (test)</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>E-wallets and Apple/Google Pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>{network_fee_policy}</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>network/gas fee paid by the sender; shown before confirmation</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>Network/gas fee payer and policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>{third_party_deposit}</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>own payment instruments only; third-party payments not accepted</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>Third-party deposit policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>{third_party_withdrawal}</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>own details only; no third-party payouts (AML)</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Third-party withdrawal policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>{support_sla}</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>chat under 2 min; email under 24h (test)</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>Support response time target</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>{bet_types}</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>single, accumulator, system (after sports launch)</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Sports bet types (single/accumulator/system)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>{live_betting}</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>in-play betting after the sports section launch</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>Live betting (in-play) availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>{max_payout_sports}</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>50000 USDT cap (after sports launch) (test)</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Maximum sports bet payout</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>{odds_format}</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>decimal (default), fractional, American</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>Supported odds formats</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>Переменные базы знаний</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>{sports_cashout}</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>early cash-out after the sports section launch</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>Sports cash-out (early settlement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Незаполненные значения бренда</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>{{LICENSE_INFO}}</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>переменные: license_info</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>Заглушка в значении по умолчанию: реестр засевается всем продуктам, поэтому имя бренда, ссылка или лицензия проставляются владельцем. Пока стоит заглушка, модель отдаёт её игроку как есть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>Незаполненные значения бренда</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>{{LOCALES}}</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>переменные: locales</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>Заглушка в значении по умолчанию: реестр засевается всем продуктам, поэтому имя бренда, ссылка или лицензия проставляются владельцем. Пока стоит заглушка, модель отдаёт её игроку как есть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>Незаполненные значения бренда</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>{{LOCAL_PAYMENT_METHODS}}</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>переменные: local_payment_methods</t>
+        </is>
+      </c>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>Заглушка в значении по умолчанию: реестр засевается всем продуктам, поэтому имя бренда, ссылка или лицензия проставляются владельцем. Пока стоит заглушка, модель отдаёт её игроку как есть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>Незаполненные значения бренда</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>{{PRIVACY_POLICY_URL}}</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>переменные: privacy_policy</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>Заглушка в значении по умолчанию: реестр засевается всем продуктам, поэтому имя бренда, ссылка или лицензия проставляются владельцем. Пока стоит заглушка, модель отдаёт её игроку как есть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>Незаполненные значения бренда</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>{{RESTRICTED_COUNTRIES}}</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>переменные: restricted_countries</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="inlineStr">
+        <is>
+          <t>Заглушка в значении по умолчанию: реестр засевается всем продуктам, поэтому имя бренда, ссылка или лицензия проставляются владельцем. Пока стоит заглушка, модель отдаёт её игроку как есть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>Незаполненные значения бренда</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>{{SOCIAL_LINKS}}</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>переменные: social_links</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>Заглушка в значении по умолчанию: реестр засевается всем продуктам, поэтому имя бренда, ссылка или лицензия проставляются владельцем. Пока стоит заглушка, модель отдаёт её игроку как есть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>Незаполненные значения бренда</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>{{TERMS_URL}}</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>Knowledge base → Variables</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>переменные: terms_url</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>Заглушка в значении по умолчанию: реестр засевается всем продуктам, поэтому имя бренда, ссылка или лицензия проставляются владельцем. Пока стоит заглушка, модель отдаёт её игроку как есть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Промпт-переменные (поддержка)</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>{persona_name}</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Системный промпт (Layer 1)</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Prompt → Prompt variables</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>Nika</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>Assistant persona name (how the assistant introduces itself)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>Промпт-переменные (поддержка)</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>{brand_name}</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>Системный промпт (Layer 1)</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>Prompt → Prompt variables</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>NikaBet</t>
+        </is>
+      </c>
+      <c r="H110" s="7" t="inlineStr">
+        <is>
+          <t>Brand the assistant supports (used in rules, links policy, refusals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>Промпт-переменные (поддержка)</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>{products}</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>Системный промпт (Layer 1)</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Prompt → Prompt variables</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>casino and sports betting</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="inlineStr">
+        <is>
+          <t>What the brand offers (short parenthetical after the brand name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>Промпт-переменные (поддержка)</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>{persona_role}</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>Системный промпт (Layer 1)</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>Prompt → Prompt variables</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>a lively woman who guides players and works as a customer-support assistant</t>
+        </is>
+      </c>
+      <c r="H112" s="7" t="inlineStr">
+        <is>
+          <t>Who the persona is (the sentence fragment right after the name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>Промпт-переменные (поддержка)</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>{tone_of_voice}</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>Системный промпт (Layer 1)</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>Prompt → Prompt variables</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>This is an international persona, not tied to any single country. Speak informally and warmly, on a first-name basis, with light flirtation - playful and friendly, yet respectful and never over-familiar. Keep it simple and clear, with no jargon or bureaucratic language. Gently but confidently lead the player toward ex…</t>
+        </is>
+      </c>
+      <c r="H113" s="7" t="inlineStr">
+        <is>
+          <t>Tone-of-voice description (the persona paragraph in the system core)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>Промпт-переменные (поддержка)</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>{support_scope}</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>Системный промпт (Layer 1)</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>Prompt → Prompt variables</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>deposits and withdrawals, account and verification, bonuses, betting and games, technical questions</t>
+        </is>
+      </c>
+      <c r="H114" s="7" t="inlineStr">
+        <is>
+          <t>Short list of what product support covers (used in guardrails/refusals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Промпт-переменные (Telegram)</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>retention_persona_name</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Системный промпт (Layer 1)</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Retention → Prompt variables</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>Nika</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>Persona name in the Telegram retention chat В шаблонах ретеншена заполняет базовый плейсхолдер {persona_name} — связь по РЕНДЕРУ, не по значению: правка в поддержке в бота не протекает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>Промпт-переменные (Telegram)</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>retention_persona_role</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>Системный промпт (Layer 1)</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>Retention → Prompt variables</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>a sexy woman assistant who guides players and talks with them in a personal private chat</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>Who the Telegram persona is - the sentence fragment right after the name В шаблонах ретеншена заполняет базовый плейсхолдер {persona_role} — связь по РЕНДЕРУ, не по значению: правка в поддержке в бота не протекает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>Промпт-переменные (Telegram)</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>retention_brand_name</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>Системный промпт (Layer 1)</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>Retention → Prompt variables</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>NikaBet</t>
+        </is>
+      </c>
+      <c r="H117" s="7" t="inlineStr">
+        <is>
+          <t>Brand name as used in the Telegram chat rules and links policy В шаблонах ретеншена заполняет базовый плейсхолдер {brand_name} — связь по РЕНДЕРУ, не по значению: правка в поддержке в бота не протекает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>Промпт-переменные (Telegram)</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>retention_products</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>Системный промпт (Layer 1)</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>Retention → Prompt variables</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>casino and sports betting</t>
+        </is>
+      </c>
+      <c r="H118" s="7" t="inlineStr">
+        <is>
+          <t>What the brand offers, as named in the Telegram chat В шаблонах ретеншена заполняет базовый плейсхолдер {products} — связь по РЕНДЕРУ, не по значению: правка в поддержке в бота не протекает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>Промпт-переменные (Telegram)</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>retention_tone_of_voice</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>Системный промпт (Layer 1)</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>Retention → Prompt variables</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>You are a confident, playful, and attractive woman chatting with users in a private one-on-one conversation. This is an international persona, not tied to any single country. Speak informally, warmly, and on a first-name basis. Be naturally flirty, teasing, charming, and emotionally engaging, making the user feel desi…</t>
+        </is>
+      </c>
+      <c r="H119" s="7" t="inlineStr">
+        <is>
+          <t>Tone-of-voice for the RETENTION (Telegram) persona - bolder and more flirtatious than support; tuned independently В шаблонах ретеншена пишется как {retention_tone_of_voice}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>Widget header title</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>What can we help you with?</t>
+        </is>
+      </c>
+      <c r="H121" s="7" t="inlineStr">
+        <is>
+          <t>Topic picker heading</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H122" s="7" t="inlineStr">
+        <is>
+          <t>The always-available "Other" topic button</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>back</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>Back to topics</t>
+        </is>
+      </c>
+      <c r="H123" s="7" t="inlineStr">
+        <is>
+          <t>Back-to-topics button label (accessibility)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>greeting</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G124" s="8" t="inlineStr">
+        <is>
+          <t>Hi, I'm Nika! How can I help you?</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t>Canned first bubble shown when a topic is picked</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>Type your message…</t>
+        </is>
+      </c>
+      <c r="H125" s="7" t="inlineStr">
+        <is>
+          <t>Message input placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>send</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G126" s="8" t="inlineStr">
+        <is>
+          <t>Send</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr">
+        <is>
+          <t>Send button</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>launcher</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>Open support chat</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t>Launcher button label (accessibility)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G128" s="8" t="inlineStr">
+        <is>
+          <t>Close chat</t>
+        </is>
+      </c>
+      <c r="H128" s="7" t="inlineStr">
+        <is>
+          <t>Close-chat button label (accessibility)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>startError</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t>Could not start chat. Please try again later.</t>
+        </is>
+      </c>
+      <c r="H129" s="7" t="inlineStr">
+        <is>
+          <t>Error shown when the chat could not start</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>sendError</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t>Something went wrong. Please try again.</t>
+        </is>
+      </c>
+      <c r="H130" s="7" t="inlineStr">
+        <is>
+          <t>Error shown when sending a message failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
+          <t>errorRateLimited</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>You're sending messages a bit too fast. Please wait a moment and try again.</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>Shown when the player is sending messages too quickly (429)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>errorTooLong</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t>That message is too long. Please shorten it and send again.</t>
+        </is>
+      </c>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>Shown when the message exceeds the length limit (400)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>errorRejected</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>I can't process that message. Please rephrase it and try again.</t>
+        </is>
+      </c>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
+          <t>Shown when the message was rejected by the content gates (400)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>switching</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G134" s="8" t="inlineStr">
+        <is>
+          <t>Looks like your question is about "{topic}", switching you there…</t>
+        </is>
+      </c>
+      <c r="H134" s="7" t="inlineStr">
+        <is>
+          <t>Topic auto-switch notice; keep the {topic} placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
+          <t>switchStuck</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>I couldn't settle on the right topic for this question. Please rephrase it in a bit more detail.</t>
+        </is>
+      </c>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t>Fallback when the topic auto-switch loops</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>finish</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G136" s="8" t="inlineStr">
+        <is>
+          <t>End chat</t>
+        </is>
+      </c>
+      <c r="H136" s="7" t="inlineStr">
+        <is>
+          <t>The green "finish chat" button</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: виджет</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>Chat ended. Thanks for reaching out!</t>
+        </is>
+      </c>
+      <c r="H137" s="7" t="inlineStr">
+        <is>
+          <t>Note shown after the chat is finished</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>Тексты: ответы сервера</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>escalation_message</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>Ответы сервера в чате</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>I'll connect you with our support team. They can take it from here.</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>Escalation card message (hand-off to a human)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: ответы сервера</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>escalation_button</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>Ответы сервера в чате</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>Contact support</t>
+        </is>
+      </c>
+      <c r="H139" s="7" t="inlineStr">
+        <is>
+          <t>Escalation card contact-button label</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: ответы сервера</t>
+        </is>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>contact_url</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>Ответы сервера в чате</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G140" s="8" t="inlineStr"/>
+      <c r="H140" s="7" t="inlineStr">
+        <is>
+          <t>Escalation contact-button URL for this language (http(s) link). Empty = no button link for this product; only the boot-seeded default product then falls back to the deploy-level CONTACT_FORM_URL env default</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: ответы сервера</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>closing_suggestion</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>Ответы сервера в чате</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>Issue solved.</t>
+        </is>
+      </c>
+      <c r="H141" s="7" t="inlineStr">
+        <is>
+          <t>The declarative closing bubble ("Issue solved.")</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: ответы сервера</t>
+        </is>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>cap_notice_message</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t>Ответы сервера в чате</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G142" s="8" t="inlineStr">
+        <is>
+          <t>Looks like we've been at this for a while and still haven't reached a solution. I can hand your question over to a human right now, or you can finish the chat if there's nothing left to add.</t>
+        </is>
+      </c>
+      <c r="H142" s="7" t="inlineStr">
+        <is>
+          <t>Long-chat notice shown once the conversation reaches the message cap: explains the chat has stalled and offers to escalate or finish</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: ответы сервера</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t>cap_escalate_button</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t>Ответы сервера в чате</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t>Hand over to a human</t>
+        </is>
+      </c>
+      <c r="H143" s="7" t="inlineStr">
+        <is>
+          <t>Long-chat notice button: hand the question over to a human (runs the normal escalation flow)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: ответы сервера</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>cap_finish_button</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t>Ответы сервера в чате</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
+          <t>End chat</t>
+        </is>
+      </c>
+      <c r="H144" s="7" t="inlineStr">
+        <is>
+          <t>Long-chat notice button: finish the chat</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: ответы сервера</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>low_content_reply</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t>Ответы сервера в чате</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t>Could you describe your question in a sentence or two? I didn't catch a question I can help with.</t>
+        </is>
+      </c>
+      <c r="H145" s="7" t="inlineStr">
+        <is>
+          <t>Nudge for a message with nothing to answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: ответы сервера</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>model_error_reply</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>Ответы сервера в чате</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G146" s="8" t="inlineStr">
+        <is>
+          <t>Sorry, I'm having a brief technical hiccup. Please send your message again in a moment.</t>
+        </is>
+      </c>
+      <c r="H146" s="7" t="inlineStr">
+        <is>
+          <t>Nudge shown on a transient model failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>rtn_need_deeplink</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>⚠️ Please open this chat from your account on the site so I know who you are.</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>Shown when someone opens the bot without a valid site deeplink</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t>rtn_subscribe_prompt</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G148" s="8" t="inlineStr">
+        <is>
+          <t>📢 Subscribe to our channel to continue, then tap "I subscribed".</t>
+        </is>
+      </c>
+      <c r="H148" s="7" t="inlineStr">
+        <is>
+          <t>Channel-subscription gate message shown before any menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="inlineStr">
+        <is>
+          <t>rtn_btn_open_channel</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t>📢 Open channel</t>
+        </is>
+      </c>
+      <c r="H149" s="7" t="inlineStr">
+        <is>
+          <t>Button: open the channel</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>rtn_btn_check_sub</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t>✅ I subscribed</t>
+        </is>
+      </c>
+      <c r="H150" s="7" t="inlineStr">
+        <is>
+          <t>Button: I subscribed / re-check</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B151" s="8" t="inlineStr">
+        <is>
+          <t>rtn_not_subscribed</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G151" s="8" t="inlineStr">
+        <is>
+          <t>⚠️ I don't see your subscription yet. Subscribe to the channel and tap "I subscribed" again.</t>
+        </is>
+      </c>
+      <c r="H151" s="7" t="inlineStr">
+        <is>
+          <t>Shown when the re-check still finds no subscription</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B152" s="8" t="inlineStr">
+        <is>
+          <t>rtn_menu_greeting</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G152" s="8" t="inlineStr">
+        <is>
+          <t>Hi, {name}! 👋 It's {persona} - I'm so glad you made it here. Now we can talk right here in Telegram.</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="inlineStr">
+        <is>
+          <t>Persona greeting above the entry menu when the player's name is known; keep the {persona} and {name} placeholders</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="inlineStr">
+        <is>
+          <t>rtn_menu_greeting_noname</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t>Hi! 👋 It's {persona} - I'm so glad you made it here. Now we can talk right here in Telegram.</t>
+        </is>
+      </c>
+      <c r="H153" s="7" t="inlineStr">
+        <is>
+          <t>Persona greeting above the entry menu when no name is known; keep the {persona} placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>rtn_menu_prompt</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G154" s="8" t="inlineStr">
+        <is>
+          <t>How would you like to continue? 👇</t>
+        </is>
+      </c>
+      <c r="H154" s="7" t="inlineStr">
+        <is>
+          <t>Menu heading shown after the subscription gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="inlineStr">
+        <is>
+          <t>rtn_btn_manager</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G155" s="8" t="inlineStr">
+        <is>
+          <t>👤 Talk to a manager</t>
+        </is>
+      </c>
+      <c r="H155" s="7" t="inlineStr">
+        <is>
+          <t>Button: go to a manager (escalation entry only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B156" s="8" t="inlineStr">
+        <is>
+          <t>rtn_btn_nika</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G156" s="8" t="inlineStr">
+        <is>
+          <t>💬 Chat with {persona}</t>
+        </is>
+      </c>
+      <c r="H156" s="7" t="inlineStr">
+        <is>
+          <t>Button: chat with Nika</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B157" s="8" t="inlineStr">
+        <is>
+          <t>rtn_manager_intro</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D157" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G157" s="8" t="inlineStr">
+        <is>
+          <t>Here is your manager: {manager}. 🦸 Just message them and they'll take it from here.</t>
+        </is>
+      </c>
+      <c r="H157" s="7" t="inlineStr">
+        <is>
+          <t>Message before the manager link; keep the {manager} placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>rtn_manager_none</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G158" s="8" t="inlineStr">
+        <is>
+          <t>All our managers are busy right now. ⏳ Please try again a little later.</t>
+        </is>
+      </c>
+      <c r="H158" s="7" t="inlineStr">
+        <is>
+          <t>Shown when no manager is available in the pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B159" s="8" t="inlineStr">
+        <is>
+          <t>rtn_handoff_support</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G159" s="8" t="inlineStr">
+        <is>
+          <t>Our support team on the site handles that best. 👩‍💻 Reach out to them there and they'll sort it out for you.</t>
+        </is>
+      </c>
+      <c r="H159" s="7" t="inlineStr">
+        <is>
+          <t>Route-out fallback when only the site option (or nothing) is available: sends the player back to support on the site</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>rtn_handoff_title</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G160" s="8" t="inlineStr">
+        <is>
+          <t>I'll hand you over to the right people 😎</t>
+        </is>
+      </c>
+      <c r="H160" s="7" t="inlineStr">
+        <is>
+          <t>Bold headline of the hand-off CHOICE message (shown when both the manager and the site support destinations are available)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B161" s="8" t="inlineStr">
+        <is>
+          <t>rtn_handoff_choice</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G161" s="8" t="inlineStr">
+        <is>
+          <t>Choose what works best for you: your personal manager right here in Telegram, or the support chat on the site. Either way, they'll take care of everything. 👇</t>
+        </is>
+      </c>
+      <c r="H161" s="7" t="inlineStr">
+        <is>
+          <t>Body of the hand-off choice message under the headline: explains the two buttons - the personal manager in Telegram and the support chat on the site</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B162" s="8" t="inlineStr">
+        <is>
+          <t>rtn_btn_site_support</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G162" s="8" t="inlineStr">
+        <is>
+          <t>🌐 Support on the site</t>
+        </is>
+      </c>
+      <c r="H162" s="7" t="inlineStr">
+        <is>
+          <t>Button: open the site (its support chat) on a hand-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B163" s="8" t="inlineStr">
+        <is>
+          <t>rtn_nika_start</t>
+        </is>
+      </c>
+      <c r="C163" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G163" s="8" t="inlineStr">
+        <is>
+          <t>Well then, I'm all yours. 😉 What are you up to today?</t>
+        </is>
+      </c>
+      <c r="H163" s="7" t="inlineStr">
+        <is>
+          <t>First line when the player opens the Nika chat. The menu message just greeted the player by name, so this must NOT greet again - it is a conversation opener, not a hello</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
+          <t>rtn_rate_limited</t>
+        </is>
+      </c>
+      <c r="C164" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t>Wow, you're fast! 😱 Give me a moment to catch my breath - I'll answer in a couple of minutes.</t>
+        </is>
+      </c>
+      <c r="H164" s="7" t="inlineStr">
+        <is>
+          <t>One-time notice when a player hits the Telegram rate limit (further blocked messages in the same window stay silent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
+        <is>
+          <t>rtn_low_content_reply</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t>Tell me a bit more! 🤔 I want to hear what's on your mind.</t>
+        </is>
+      </c>
+      <c r="H165" s="7" t="inlineStr">
+        <is>
+          <t>Nudge for a Telegram message with nothing to answer (model-free)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
+          <t>rtn_incoming_media_reply</t>
+        </is>
+      </c>
+      <c r="C166" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G166" s="8" t="inlineStr">
+        <is>
+          <t>I can't open photos and videos here, sadly. 🙈 Tell me in words - what am I missing?</t>
+        </is>
+      </c>
+      <c r="H166" s="7" t="inlineStr">
+        <is>
+          <t>In-persona reply when the player sends a photo/video/file (the bot cannot view attachments; model-free)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>rtn_injection_reply</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>Let's just talk like people do. 😊 So, what's on your mind today?</t>
+        </is>
+      </c>
+      <c r="H167" s="7" t="inlineStr">
+        <is>
+          <t>Deflection for an injection/jailbreak attempt in Telegram (model-free)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>rtn_photo_caption</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G168" s="8" t="inlineStr">
+        <is>
+          <t>This one is just for you. 😘</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="inlineStr">
+        <is>
+          <t>Fallback photo caption when the model returned a photo with no text (one of three variants, picked at random)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t>rtn_photo_caption_2</t>
+        </is>
+      </c>
+      <c r="C169" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
+          <t>Caught this moment for you. 😉</t>
+        </is>
+      </c>
+      <c r="H169" s="7" t="inlineStr">
+        <is>
+          <t>Second fallback photo caption variant (picked at random)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>rtn_photo_caption_3</t>
+        </is>
+      </c>
+      <c r="C170" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G170" s="8" t="inlineStr">
+        <is>
+          <t>So you don't forget what I look like. 😏</t>
+        </is>
+      </c>
+      <c r="H170" s="7" t="inlineStr">
+        <is>
+          <t>Third fallback photo caption variant (picked at random)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
+        <is>
+          <t>rtn_video_caption</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G171" s="8" t="inlineStr">
+        <is>
+          <t>Here's my video - just for you. 😘</t>
+        </is>
+      </c>
+      <c r="H171" s="7" t="inlineStr">
+        <is>
+          <t>Fallback video caption when the model returned a video with no text (one of three variants, picked at random)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>rtn_video_caption_2</t>
+        </is>
+      </c>
+      <c r="C172" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G172" s="8" t="inlineStr">
+        <is>
+          <t>Filmed a little something for you. 😉</t>
+        </is>
+      </c>
+      <c r="H172" s="7" t="inlineStr">
+        <is>
+          <t>Second fallback video caption variant (picked at random)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B173" s="8" t="inlineStr">
+        <is>
+          <t>rtn_video_caption_3</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G173" s="8" t="inlineStr">
+        <is>
+          <t>A moment of me, in motion this time. 😏</t>
+        </is>
+      </c>
+      <c r="H173" s="7" t="inlineStr">
+        <is>
+          <t>Third fallback video caption variant (picked at random)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
+          <t>rtn_ping_header</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G174" s="8" t="inlineStr">
+        <is>
+          <t>✨ Hey, it's {persona}</t>
+        </is>
+      </c>
+      <c r="H174" s="7" t="inlineStr">
+        <is>
+          <t>Short header line shown in italics above every proactive ping message; an event reaction appends its occasion phrase (rtn_trig_*) on the SAME line; keep the {persona} placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B175" s="8" t="inlineStr">
+        <is>
+          <t>rtn_trig_deposit_confirmed</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G175" s="8" t="inlineStr">
+        <is>
+          <t>Thank you for the deposit{detail}!</t>
+        </is>
+      </c>
+      <c r="H175" s="7" t="inlineStr">
+        <is>
+          <t>Header occasion phrase after a confirmed deposit; optional {detail} carries the amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B176" s="8" t="inlineStr">
+        <is>
+          <t>rtn_trig_deposit_failed</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G176" s="8" t="inlineStr">
+        <is>
+          <t>I saw your payment didn't go through</t>
+        </is>
+      </c>
+      <c r="H176" s="7" t="inlineStr">
+        <is>
+          <t>Header occasion phrase after a failed deposit attempt</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B177" s="8" t="inlineStr">
+        <is>
+          <t>rtn_trig_withdrawal_settled</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G177" s="8" t="inlineStr">
+        <is>
+          <t>Congrats on your payout{detail}!</t>
+        </is>
+      </c>
+      <c r="H177" s="7" t="inlineStr">
+        <is>
+          <t>Header occasion phrase after a settled withdrawal; optional {detail} carries the amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B178" s="8" t="inlineStr">
+        <is>
+          <t>rtn_trig_level_up</t>
+        </is>
+      </c>
+      <c r="C178" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G178" s="8" t="inlineStr">
+        <is>
+          <t>Congrats on the new level{detail}!</t>
+        </is>
+      </c>
+      <c r="H178" s="7" t="inlineStr">
+        <is>
+          <t>Header occasion phrase after a loyalty level-up; optional {detail} carries the new level</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="inlineStr">
+        <is>
+          <t>rtn_trig_class_up</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G179" s="8" t="inlineStr">
+        <is>
+          <t>Congrats, a whole new class{detail}!</t>
+        </is>
+      </c>
+      <c r="H179" s="7" t="inlineStr">
+        <is>
+          <t>Header occasion phrase after a loyalty class-up; optional {detail} carries the new class</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B180" s="8" t="inlineStr">
+        <is>
+          <t>rtn_trig_kyc_approved</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G180" s="8" t="inlineStr">
+        <is>
+          <t>Your verification is approved!</t>
+        </is>
+      </c>
+      <c r="H180" s="7" t="inlineStr">
+        <is>
+          <t>Header occasion phrase after account verification is approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>rtn_trig_bonus_completed</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G181" s="8" t="inlineStr">
+        <is>
+          <t>Bonus completed{detail}, congrats!</t>
+        </is>
+      </c>
+      <c r="H181" s="7" t="inlineStr">
+        <is>
+          <t>Header occasion phrase after a bonus is wagered through; optional {detail} carries the bonus type</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="inlineStr">
+        <is>
+          <t>rtn_trig_bonus_expired</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G182" s="8" t="inlineStr">
+        <is>
+          <t>Your bonus{detail} expired unused</t>
+        </is>
+      </c>
+      <c r="H182" s="7" t="inlineStr">
+        <is>
+          <t>Header occasion phrase after a bonus expired unused; optional {detail} carries the bonus type</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B183" s="8" t="inlineStr">
+        <is>
+          <t>rtn_pings_stopped</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F183" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G183" s="8" t="inlineStr">
+        <is>
+          <t>Got it, I won't message you first anymore. 🛑 Send /resume if you change your mind - I'll be around.</t>
+        </is>
+      </c>
+      <c r="H183" s="7" t="inlineStr">
+        <is>
+          <t>Confirmation after /stop: the bot will no longer message first</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="7" t="inlineStr">
+        <is>
+          <t>Тексты: Telegram-бот</t>
+        </is>
+      </c>
+      <c r="B184" s="8" t="inlineStr">
+        <is>
+          <t>rtn_pings_resumed</t>
+        </is>
+      </c>
+      <c r="C184" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G184" s="8" t="inlineStr">
+        <is>
+          <t>I'm so glad you're back! 🥳 I'll drop you a line from time to time.</t>
+        </is>
+      </c>
+      <c r="H184" s="7" t="inlineStr">
+        <is>
+          <t>Confirmation after /resume: proactive messages are back on</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>Плейсхолдеры внутри текстов</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>{detail}</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>Виджет на сайте / Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>ключи: rtn_trig_bonus_completed, rtn_trig_bonus_expired, rtn_trig_class_up, rtn_trig_deposit_confirmed, rtn_trig_level_up, rtn_trig_withdrawal_settled</t>
+        </is>
+      </c>
+      <c r="H185" s="4" t="inlineStr">
+        <is>
+          <t>Деталь события (сумма, уровень, тип бонуса); может быть пустой. Плейсхолдер обязан сохраниться при переводе — иначе подстановка потеряется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t>Плейсхолдеры внутри текстов</t>
+        </is>
+      </c>
+      <c r="B186" s="8" t="inlineStr">
+        <is>
+          <t>{manager}</t>
+        </is>
+      </c>
+      <c r="C186" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте / Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G186" s="8" t="inlineStr">
+        <is>
+          <t>ключи: rtn_manager_intro</t>
+        </is>
+      </c>
+      <c r="H186" s="7" t="inlineStr">
+        <is>
+          <t>Ссылка или контакт назначенного менеджера. Плейсхолдер обязан сохраниться при переводе — иначе подстановка потеряется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>Плейсхолдеры внутри текстов</t>
+        </is>
+      </c>
+      <c r="B187" s="8" t="inlineStr">
+        <is>
+          <t>{name}</t>
+        </is>
+      </c>
+      <c r="C187" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте / Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G187" s="8" t="inlineStr">
+        <is>
+          <t>ключи: rtn_menu_greeting</t>
+        </is>
+      </c>
+      <c r="H187" s="7" t="inlineStr">
+        <is>
+          <t>Имя игрока из профиля. Плейсхолдер обязан сохраниться при переводе — иначе подстановка потеряется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="7" t="inlineStr">
+        <is>
+          <t>Плейсхолдеры внутри текстов</t>
+        </is>
+      </c>
+      <c r="B188" s="8" t="inlineStr">
+        <is>
+          <t>{persona}</t>
+        </is>
+      </c>
+      <c r="C188" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте / Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G188" s="8" t="inlineStr">
+        <is>
+          <t>ключи: rtn_btn_nika, rtn_menu_greeting, rtn_menu_greeting_noname, rtn_ping_header</t>
+        </is>
+      </c>
+      <c r="H188" s="7" t="inlineStr">
+        <is>
+          <t>Имя персоны — подставляется из промпт-переменных. Плейсхолдер обязан сохраниться при переводе — иначе подстановка потеряется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="7" t="inlineStr">
+        <is>
+          <t>Плейсхолдеры внутри текстов</t>
+        </is>
+      </c>
+      <c r="B189" s="8" t="inlineStr">
+        <is>
+          <t>{topic}</t>
+        </is>
+      </c>
+      <c r="C189" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте / Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G189" s="8" t="inlineStr">
+        <is>
+          <t>ключи: switching</t>
+        </is>
+      </c>
+      <c r="H189" s="7" t="inlineStr">
+        <is>
+          <t>Название темы, на которую переключается чат. Плейсхолдер обязан сохраниться при переводе — иначе подстановка потеряется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>Управляющие теги модели</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>[[ESCALATE]]</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>Ответ модели (служебный тег)</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>код prompts.py (редеплой)</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>деплой (общий)</t>
+        </is>
+      </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr">
+        <is>
+          <t>[[ESCALATE]]</t>
+        </is>
+      </c>
+      <c r="H190" s="4" t="inlineStr">
+        <is>
+          <t>Передача вопроса человеку. Бэкенд вырезает тег, закрывает сессию и показывает карточку контакта (или диплинк в Telegram-бота). Тег вырезается из ответа и игроку не показывается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="7" t="inlineStr">
+        <is>
+          <t>Управляющие теги модели</t>
+        </is>
+      </c>
+      <c r="B191" s="8" t="inlineStr">
+        <is>
+          <t>[[TOPIC:slug]]</t>
+        </is>
+      </c>
+      <c r="C191" s="7" t="inlineStr">
+        <is>
+          <t>Ответ модели (служебный тег)</t>
+        </is>
+      </c>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>код prompts.py (редеплой)</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>деплой (общий)</t>
+        </is>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G191" s="8" t="inlineStr">
+        <is>
+          <t>[[TOPIC:withdrawals]]</t>
+        </is>
+      </c>
+      <c r="H191" s="7" t="inlineStr">
+        <is>
+          <t>Вопрос относится к другой теме. Бэкенд подавляет текст ответа (он сгенерирован без нужной базы знаний), переключает тему и переспрашивает исходный вопрос. Тег вырезается из ответа и игроку не показывается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="7" t="inlineStr">
+        <is>
+          <t>Управляющие теги модели</t>
+        </is>
+      </c>
+      <c r="B192" s="8" t="inlineStr">
+        <is>
+          <t>[[SUGGEST: a | b]]</t>
+        </is>
+      </c>
+      <c r="C192" s="7" t="inlineStr">
+        <is>
+          <t>Ответ модели (служебный тег)</t>
+        </is>
+      </c>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>код prompts.py (редеплой)</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>деплой (общий)</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G192" s="8" t="inlineStr">
+        <is>
+          <t>[[SUGGEST: Какие лимиты на вывод? | Сколько идут выплаты?]]</t>
+        </is>
+      </c>
+      <c r="H192" s="7" t="inlineStr">
+        <is>
+          <t>До двух уточняющих вопросов от лица игрока — кнопки в один тап. Опция «Проблема решена.» добавляется сервером, а не моделью. Тег вырезается из ответа и игроку не показывается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>Управляющие теги модели</t>
+        </is>
+      </c>
+      <c r="B193" s="8" t="inlineStr">
+        <is>
+          <t>[[RESOLVED]]</t>
+        </is>
+      </c>
+      <c r="C193" s="7" t="inlineStr">
+        <is>
+          <t>Ответ модели (служебный тег)</t>
+        </is>
+      </c>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>код prompts.py (редеплой)</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>деплой (общий)</t>
+        </is>
+      </c>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G193" s="8" t="inlineStr">
+        <is>
+          <t>[[RESOLVED]]</t>
+        </is>
+      </c>
+      <c r="H193" s="7" t="inlineStr">
+        <is>
+          <t>Вопрос закрыт — виджет показывает зелёную кнопку завершения чата. Тег вырезается из ответа и игроку не показывается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t>Управляющие теги модели</t>
+        </is>
+      </c>
+      <c r="B194" s="8" t="inlineStr">
+        <is>
+          <t>[[LANG:xx]]</t>
+        </is>
+      </c>
+      <c r="C194" s="7" t="inlineStr">
+        <is>
+          <t>Ответ модели (служебный тег)</t>
+        </is>
+      </c>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>код prompts.py (редеплой)</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>деплой (общий)</t>
+        </is>
+      </c>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G194" s="8" t="inlineStr">
+        <is>
+          <t>[[LANG:ru]]</t>
+        </is>
+      </c>
+      <c r="H194" s="7" t="inlineStr">
+        <is>
+          <t>Язык, на котором модель ответила. Бэкенд запоминает его на сессии, интерфейс переключается следом за игроком. Тег вырезается из ответа и игроку не показывается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t>Управляющие теги модели</t>
+        </is>
+      </c>
+      <c r="B195" s="8" t="inlineStr">
+        <is>
+          <t>[[PHOTO:id]]</t>
+        </is>
+      </c>
+      <c r="C195" s="7" t="inlineStr">
+        <is>
+          <t>Ответ модели (служебный тег)</t>
+        </is>
+      </c>
+      <c r="D195" s="7" t="inlineStr">
+        <is>
+          <t>код prompts.py (редеплой)</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t>деплой (общий)</t>
+        </is>
+      </c>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G195" s="8" t="inlineStr">
+        <is>
+          <t>[[PHOTO:42]]</t>
+        </is>
+      </c>
+      <c r="H195" s="7" t="inlineStr">
+        <is>
+          <t>Только Telegram: отправить фото/видео с этим id из списка кандидатов, показанного модели. Id проверяется по разрешённому набору. Тег вырезается из ответа и игроку не показывается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="7" t="inlineStr">
+        <is>
+          <t>Управляющие теги модели</t>
+        </is>
+      </c>
+      <c r="B196" s="8" t="inlineStr">
+        <is>
+          <t>[[LINK:url]]</t>
+        </is>
+      </c>
+      <c r="C196" s="7" t="inlineStr">
+        <is>
+          <t>Ответ модели (служебный тег)</t>
+        </is>
+      </c>
+      <c r="D196" s="7" t="inlineStr">
+        <is>
+          <t>код prompts.py (редеплой)</t>
+        </is>
+      </c>
+      <c r="E196" s="7" t="inlineStr">
+        <is>
+          <t>деплой (общий)</t>
+        </is>
+      </c>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G196" s="8" t="inlineStr">
+        <is>
+          <t>[[LINK:https://brand.com/cashier]]</t>
+        </is>
+      </c>
+      <c r="H196" s="7" t="inlineStr">
+        <is>
+          <t>Только Telegram: подставить кнопку на страницу из карты сайта. Адрес вне карты сайта отбрасывается. Тег вырезается из ответа и игроку не показывается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="7" t="inlineStr">
+        <is>
+          <t>Управляющие теги модели</t>
+        </is>
+      </c>
+      <c r="B197" s="8" t="inlineStr">
+        <is>
+          <t>[[STAGE_UP]]</t>
+        </is>
+      </c>
+      <c r="C197" s="7" t="inlineStr">
+        <is>
+          <t>Ответ модели (служебный тег)</t>
+        </is>
+      </c>
+      <c r="D197" s="7" t="inlineStr">
+        <is>
+          <t>код prompts.py (редеплой)</t>
+        </is>
+      </c>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t>деплой (общий)</t>
+        </is>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G197" s="8" t="inlineStr">
+        <is>
+          <t>[[STAGE_UP]]</t>
+        </is>
+      </c>
+      <c r="H197" s="7" t="inlineStr">
+        <is>
+          <t>Только Telegram: подсказка, что игрок готов к следующей ступени откровенности. Решение принимает бэкенд, а не модель. Тег вырезается из ответа и игроку не показывается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t>Управляющие теги модели</t>
+        </is>
+      </c>
+      <c r="B198" s="8" t="inlineStr">
+        <is>
+          <t>[[HANDOFF]]</t>
+        </is>
+      </c>
+      <c r="C198" s="7" t="inlineStr">
+        <is>
+          <t>Ответ модели (служебный тег)</t>
+        </is>
+      </c>
+      <c r="D198" s="7" t="inlineStr">
+        <is>
+          <t>код prompts.py (редеплой)</t>
+        </is>
+      </c>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t>деплой (общий)</t>
+        </is>
+      </c>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G198" s="8" t="inlineStr">
+        <is>
+          <t>[[HANDOFF]]</t>
+        </is>
+      </c>
+      <c r="H198" s="7" t="inlineStr">
+        <is>
+          <t>Только Telegram: всплыл вопрос поддержки/жалоба — бот уводит игрока к менеджеру или в чат поддержки на сайте. Тег вырезается из ответа и игроку не показывается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>Крупные тексты и справочники</t>
+        </is>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
+          <t>Тексты тем базы знаний</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>Тексты базы знаний</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>Knowledge base → тексты тем</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t>JSON-документ вопрос-ответ на тему</t>
+        </is>
+      </c>
+      <c r="H199" s="4" t="inlineStr">
+        <is>
+          <t>Содержимое ответов (Layer 2): грузится только по выбранной теме. Внутри можно ставить {переменные} из реестра выше.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="7" t="inlineStr">
+        <is>
+          <t>Крупные тексты и справочники</t>
+        </is>
+      </c>
+      <c r="B200" s="8" t="inlineStr">
+        <is>
+          <t>Названия тем</t>
+        </is>
+      </c>
+      <c r="C200" s="7" t="inlineStr">
+        <is>
+          <t>Виджет на сайте</t>
+        </is>
+      </c>
+      <c r="D200" s="7" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="E200" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G200" s="8" t="inlineStr">
+        <is>
+          <t>Депозиты / Выводы / Бонусы …</t>
+        </is>
+      </c>
+      <c r="H200" s="7" t="inlineStr">
+        <is>
+          <t>Заголовки кнопок выбора темы — по одному на язык. Каноническое английское название темы редактируется вместе с самой темой.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="7" t="inlineStr">
+        <is>
+          <t>Крупные тексты и справочники</t>
+        </is>
+      </c>
+      <c r="B201" s="8" t="inlineStr">
+        <is>
+          <t>База знаний Telegram-бота</t>
+        </is>
+      </c>
+      <c r="C201" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>Retention → Knowledge base</t>
+        </is>
+      </c>
+      <c r="E201" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G201" s="8" t="inlineStr">
+        <is>
+          <t>один документ на продукт</t>
+        </is>
+      </c>
+      <c r="H201" s="7" t="inlineStr">
+        <is>
+          <t>Отдельный от поддержки KB-документ ретеншен-персоны. Те же {переменные} реестра подставляются и в него.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="7" t="inlineStr">
+        <is>
+          <t>Крупные тексты и справочники</t>
+        </is>
+      </c>
+      <c r="B202" s="8" t="inlineStr">
+        <is>
+          <t>Карта сайта (title / url / purpose)</t>
+        </is>
+      </c>
+      <c r="C202" s="7" t="inlineStr">
+        <is>
+          <t>Оба промпта (чат + Telegram)</t>
+        </is>
+      </c>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>Common → Site map</t>
+        </is>
+      </c>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G202" s="8" t="inlineStr">
+        <is>
+          <t>{"title":"Cashier","url":"https://brand.com/cashier","purpose":"deposits and withdrawals"}</t>
+        </is>
+      </c>
+      <c r="H202" s="7" t="inlineStr">
+        <is>
+          <t>Единственный список страниц, на которые обоим ботам разрешено ставить ссылки. Пустой список = блока в промпте нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t>Крупные тексты и справочники</t>
+        </is>
+      </c>
+      <c r="B203" s="8" t="inlineStr">
+        <is>
+          <t>Ключевые слова эскалации</t>
+        </is>
+      </c>
+      <c r="C203" s="7" t="inlineStr">
+        <is>
+          <t>Сообщение игрока (до вызова модели)</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>Common → Escalation keywords</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>мультиязычно</t>
+        </is>
+      </c>
+      <c r="G203" s="8" t="inlineStr">
+        <is>
+          <t>high_risk_keywords · human_request_keywords</t>
+        </is>
+      </c>
+      <c r="H203" s="7" t="inlineStr">
+        <is>
+          <t>Два списка основ слов: жалоба/мошенничество/юридическая угроза и явная просьба человека. Сканируют сообщение игрока, поэтому мультиязычны и на английский не проверяются.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="7" t="inlineStr">
+        <is>
+          <t>Крупные тексты и справочники</t>
+        </is>
+      </c>
+      <c r="B204" s="8" t="inlineStr">
+        <is>
+          <t>Тест-профиль игрока</t>
+        </is>
+      </c>
+      <c r="C204" s="7" t="inlineStr">
+        <is>
+          <t>Промпт, данные хода (Layer 3)</t>
+        </is>
+      </c>
+      <c r="D204" s="7" t="inlineStr">
+        <is>
+          <t>Common → Test profile</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t>глобально + продукт</t>
+        </is>
+      </c>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G204" s="8" t="inlineStr">
+        <is>
+          <t>{"full_name":"Andrey Petrov","vip_level":"Gold"}</t>
+        </is>
+      </c>
+      <c r="H204" s="7" t="inlineStr">
+        <is>
+          <t>Профиль, который подставляется в предпросмотр промпта, чтобы видеть персонализацию без живой сессии.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="7" t="inlineStr">
+        <is>
+          <t>Крупные тексты и справочники</t>
+        </is>
+      </c>
+      <c r="B205" s="8" t="inlineStr">
+        <is>
+          <t>Шаблоны сценариев ретеншена</t>
+        </is>
+      </c>
+      <c r="C205" s="7" t="inlineStr">
+        <is>
+          <t>Telegram-бот</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>Retention → Scenarios</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G205" s="8" t="inlineStr">
+        <is>
+          <t>persona_brief (по умолчанию) | verbatim</t>
+        </is>
+      </c>
+      <c r="H205" s="7" t="inlineStr">
+        <is>
+          <t>Шаг journey задаёт НАМЕРЕНИЕ, текст пишет персона. Точный текст используется только при явном флаге verbatim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
+          <t>Крупные тексты и справочники</t>
+        </is>
+      </c>
+      <c r="B206" s="8" t="inlineStr">
+        <is>
+          <t>Формулировки промпта (SYSTEM_CORE, директивы, запрещённые темы, теги качества)</t>
+        </is>
+      </c>
+      <c r="C206" s="7" t="inlineStr">
+        <is>
+          <t>Системный промпт (Layer 1)</t>
+        </is>
+      </c>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>код prompts.py (редеплой)</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>деплой (общий)</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>английский (проверяется)</t>
+        </is>
+      </c>
+      <c r="G206" s="8" t="inlineStr">
+        <is>
+          <t>prompts.py</t>
+        </is>
+      </c>
+      <c r="H206" s="7" t="inlineStr">
+        <is>
+          <t>Сами формулировки промпта — единственный источник правды и НЕ редактируются из админки: бренд уникализируется переменными выше.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>Поля профиля игрока в промпте</t>
+        </is>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>Промпт, данные хода (Layer 3)</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>приходит из CRM казино</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G207" s="5" t="inlineStr"/>
+      <c r="H207" s="4" t="inlineStr">
+        <is>
+          <t>Идентификатор игрока в казино. Белый список: всё остальное из профиля до модели не доходит. Контракт передачи — на /integration-reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="7" t="inlineStr">
+        <is>
+          <t>Поля профиля игрока в промпте</t>
+        </is>
+      </c>
+      <c r="B208" s="8" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C208" s="7" t="inlineStr">
+        <is>
+          <t>Промпт, данные хода (Layer 3)</t>
+        </is>
+      </c>
+      <c r="D208" s="7" t="inlineStr">
+        <is>
+          <t>приходит из CRM казино</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G208" s="8" t="inlineStr"/>
+      <c r="H208" s="7" t="inlineStr">
+        <is>
+          <t>Полное имя. Из него берётся ИМЯ для приветствия в первом ответе; без имени приветствия нет вообще. Белый список: всё остальное из профиля до модели не доходит. Контракт передачи — на /integration-reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="7" t="inlineStr">
+        <is>
+          <t>Поля профиля игрока в промпте</t>
+        </is>
+      </c>
+      <c r="B209" s="8" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="inlineStr">
+        <is>
+          <t>Промпт, данные хода (Layer 3)</t>
+        </is>
+      </c>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>приходит из CRM казино</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G209" s="8" t="inlineStr"/>
+      <c r="H209" s="7" t="inlineStr">
+        <is>
+          <t>Почта игрока. Белый список: всё остальное из профиля до модели не доходит. Контракт передачи — на /integration-reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="7" t="inlineStr">
+        <is>
+          <t>Поля профиля игрока в промпте</t>
+        </is>
+      </c>
+      <c r="B210" s="8" t="inlineStr">
+        <is>
+          <t>activation_status</t>
+        </is>
+      </c>
+      <c r="C210" s="7" t="inlineStr">
+        <is>
+          <t>Промпт, данные хода (Layer 3)</t>
+        </is>
+      </c>
+      <c r="D210" s="7" t="inlineStr">
+        <is>
+          <t>приходит из CRM казино</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F210" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G210" s="8" t="inlineStr"/>
+      <c r="H210" s="7" t="inlineStr">
+        <is>
+          <t>Статус активации/верификации. Белый список: всё остальное из профиля до модели не доходит. Контракт передачи — на /integration-reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="7" t="inlineStr">
+        <is>
+          <t>Поля профиля игрока в промпте</t>
+        </is>
+      </c>
+      <c r="B211" s="8" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="C211" s="7" t="inlineStr">
+        <is>
+          <t>Промпт, данные хода (Layer 3)</t>
+        </is>
+      </c>
+      <c r="D211" s="7" t="inlineStr">
+        <is>
+          <t>приходит из CRM казино</t>
+        </is>
+      </c>
+      <c r="E211" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G211" s="8" t="inlineStr"/>
+      <c r="H211" s="7" t="inlineStr">
+        <is>
+          <t>Страна. Белый список: всё остальное из профиля до модели не доходит. Контракт передачи — на /integration-reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="7" t="inlineStr">
+        <is>
+          <t>Поля профиля игрока в промпте</t>
+        </is>
+      </c>
+      <c r="B212" s="8" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="C212" s="7" t="inlineStr">
+        <is>
+          <t>Промпт, данные хода (Layer 3)</t>
+        </is>
+      </c>
+      <c r="D212" s="7" t="inlineStr">
+        <is>
+          <t>приходит из CRM казино</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G212" s="8" t="inlineStr"/>
+      <c r="H212" s="7" t="inlineStr">
+        <is>
+          <t>Баланс строкой, вместе с валютой. Белый список: всё остальное из профиля до модели не доходит. Контракт передачи — на /integration-reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="7" t="inlineStr">
+        <is>
+          <t>Поля профиля игрока в промпте</t>
+        </is>
+      </c>
+      <c r="B213" s="8" t="inlineStr">
+        <is>
+          <t>vip_level</t>
+        </is>
+      </c>
+      <c r="C213" s="7" t="inlineStr">
+        <is>
+          <t>Промпт, данные хода (Layer 3)</t>
+        </is>
+      </c>
+      <c r="D213" s="7" t="inlineStr">
+        <is>
+          <t>приходит из CRM казино</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F213" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G213" s="8" t="inlineStr"/>
+      <c r="H213" s="7" t="inlineStr">
+        <is>
+          <t>VIP-класс. Белый список: всё остальное из профиля до модели не доходит. Контракт передачи — на /integration-reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="7" t="inlineStr">
+        <is>
+          <t>Поля профиля игрока в промпте</t>
+        </is>
+      </c>
+      <c r="B214" s="8" t="inlineStr">
+        <is>
+          <t>registration_date</t>
+        </is>
+      </c>
+      <c r="C214" s="7" t="inlineStr">
+        <is>
+          <t>Промпт, данные хода (Layer 3)</t>
+        </is>
+      </c>
+      <c r="D214" s="7" t="inlineStr">
+        <is>
+          <t>приходит из CRM казино</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="inlineStr">
+        <is>
+          <t>продукт</t>
+        </is>
+      </c>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G214" s="8" t="inlineStr"/>
+      <c r="H214" s="7" t="inlineStr">
+        <is>
+          <t>Дата регистрации. Белый список: всё остальное из профиля до модели не доходит. Контракт передачи — на /integration-reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Лист генерируется из кода: scripts/build_api_reference.py (данные — scripts/text_variables.py). Живая версия — /integration-variables на самом сервисе.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:H214"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/frontend/api-reference.xlsx
+++ b/frontend/api-reference.xlsx
@@ -18171,7 +18171,7 @@
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>Retention → Scenarios</t>
+          <t>Retention → Orchestrator → Templates</t>
         </is>
       </c>
       <c r="E205" s="7" t="inlineStr">
